--- a/fixtures.xlsx
+++ b/fixtures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee16c21b72f3fde9/Documents/Football Fortunes/All data/Data/Riku/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{B8C29E7A-327B-47C1-9684-CF8070176274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AA036A7-2149-408E-99D5-B0AD0ACFA210}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{C5562B89-06A1-4F87-A869-008A45895D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2189C752-2F04-481F-B61A-A027BE1A78E3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="268">
   <si>
     <t>Div</t>
   </si>
@@ -246,6 +246,12 @@
     <t>EC</t>
   </si>
   <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>Leicester</t>
+  </si>
+  <si>
     <t>E3</t>
   </si>
   <si>
@@ -255,6 +261,9 @@
     <t>Referee</t>
   </si>
   <si>
+    <t>P1</t>
+  </si>
+  <si>
     <t>BFEH</t>
   </si>
   <si>
@@ -387,115 +396,445 @@
     <t>LBCA</t>
   </si>
   <si>
+    <t>Luton</t>
+  </si>
+  <si>
+    <t>AFC Wimbledon</t>
+  </si>
+  <si>
+    <t>Peterboro</t>
+  </si>
+  <si>
+    <t>Blackpool</t>
+  </si>
+  <si>
+    <t>Stevenage</t>
+  </si>
+  <si>
+    <t>Bradford</t>
+  </si>
+  <si>
+    <t>Wycombe</t>
+  </si>
+  <si>
+    <t>Burton</t>
+  </si>
+  <si>
+    <t>Mansfield</t>
+  </si>
+  <si>
+    <t>Doncaster</t>
+  </si>
+  <si>
+    <t>Exeter</t>
+  </si>
+  <si>
+    <t>Huddersfield</t>
+  </si>
+  <si>
     <t>Leyton Orient</t>
   </si>
   <si>
+    <t>Lincoln</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Plymouth</t>
+  </si>
+  <si>
+    <t>Barnsley</t>
+  </si>
+  <si>
+    <t>Rotherham</t>
+  </si>
+  <si>
     <t>Wigan</t>
   </si>
   <si>
+    <t>Northampton</t>
+  </si>
+  <si>
+    <t>Stockport</t>
+  </si>
+  <si>
+    <t>Bolton</t>
+  </si>
+  <si>
+    <t>Accrington</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Barnet</t>
+  </si>
+  <si>
+    <t>Fleetwood Town</t>
+  </si>
+  <si>
+    <t>Bristol Rvs</t>
+  </si>
+  <si>
+    <t>Harrogate</t>
+  </si>
+  <si>
     <t>Cambridge</t>
   </si>
   <si>
+    <t>Cheltenham</t>
+  </si>
+  <si>
+    <t>Chesterfield</t>
+  </si>
+  <si>
+    <t>Barrow</t>
+  </si>
+  <si>
+    <t>Colchester</t>
+  </si>
+  <si>
+    <t>Tranmere</t>
+  </si>
+  <si>
+    <t>Grimsby</t>
+  </si>
+  <si>
+    <t>Crawley Town</t>
+  </si>
+  <si>
+    <t>Milton Keynes Dons</t>
+  </si>
+  <si>
+    <t>Oldham</t>
+  </si>
+  <si>
+    <t>Salford</t>
+  </si>
+  <si>
+    <t>Crewe</t>
+  </si>
+  <si>
+    <t>Shrewsbury</t>
+  </si>
+  <si>
+    <t>Bromley</t>
+  </si>
+  <si>
+    <t>Walsall</t>
+  </si>
+  <si>
     <t>Swindon</t>
   </si>
   <si>
+    <t>Newport County</t>
+  </si>
+  <si>
+    <t>Notts County</t>
+  </si>
+  <si>
     <t>M Corlett</t>
   </si>
   <si>
+    <t>S Stockbridge</t>
+  </si>
+  <si>
+    <t>E Duckworth</t>
+  </si>
+  <si>
+    <t>B Speedie</t>
+  </si>
+  <si>
+    <t>M Woods</t>
+  </si>
+  <si>
+    <t>D Bourne</t>
+  </si>
+  <si>
+    <t>E Bell</t>
+  </si>
+  <si>
+    <t>O Yates</t>
+  </si>
+  <si>
+    <t>C Brook</t>
+  </si>
+  <si>
+    <t>C Hicks</t>
+  </si>
+  <si>
+    <t>D Rock</t>
+  </si>
+  <si>
+    <t>S Jackson</t>
+  </si>
+  <si>
+    <t>N Hair</t>
+  </si>
+  <si>
+    <t>O Mackey</t>
+  </si>
+  <si>
+    <t>Birmingham</t>
+  </si>
+  <si>
+    <t>Charlton</t>
+  </si>
+  <si>
+    <t>Watford</t>
+  </si>
+  <si>
+    <t>Coventry</t>
+  </si>
+  <si>
+    <t>Hull</t>
+  </si>
+  <si>
+    <t>Wrexham</t>
+  </si>
+  <si>
+    <t>Norwich</t>
+  </si>
+  <si>
+    <t>Millwall</t>
+  </si>
+  <si>
+    <t>Oxford</t>
+  </si>
+  <si>
+    <t>Portsmouth</t>
+  </si>
+  <si>
+    <t>QPR</t>
+  </si>
+  <si>
+    <t>Preston</t>
+  </si>
+  <si>
+    <t>Stoke</t>
+  </si>
+  <si>
+    <t>Derby</t>
+  </si>
+  <si>
+    <t>West Brom</t>
+  </si>
+  <si>
+    <t>Blackburn</t>
+  </si>
+  <si>
+    <t>Middlesbrough</t>
+  </si>
+  <si>
+    <t>Swansea</t>
+  </si>
+  <si>
+    <t>Sheffield United</t>
+  </si>
+  <si>
+    <t>Bristol City</t>
+  </si>
+  <si>
+    <t>Sheffield Weds</t>
+  </si>
+  <si>
     <t>Altrincham</t>
   </si>
   <si>
+    <t>Aldershot</t>
+  </si>
+  <si>
+    <t>Boreham Wood</t>
+  </si>
+  <si>
+    <t>Rochdale</t>
+  </si>
+  <si>
+    <t>Brackley Town</t>
+  </si>
+  <si>
+    <t>Eastleigh</t>
+  </si>
+  <si>
+    <t>Braintree Town</t>
+  </si>
+  <si>
+    <t>Halifax</t>
+  </si>
+  <si>
+    <t>Gateshead</t>
+  </si>
+  <si>
     <t>Southend</t>
   </si>
   <si>
+    <t>Solihull</t>
+  </si>
+  <si>
+    <t>Forest Green</t>
+  </si>
+  <si>
+    <t>Tamworth</t>
+  </si>
+  <si>
+    <t>Scunthorpe</t>
+  </si>
+  <si>
     <t>Wealdstone</t>
   </si>
   <si>
+    <t>Truro</t>
+  </si>
+  <si>
     <t>Woking</t>
   </si>
   <si>
+    <t>Carlisle</t>
+  </si>
+  <si>
     <t>Yeovil</t>
   </si>
   <si>
     <t>Hartlepool</t>
   </si>
   <si>
+    <t>York</t>
+  </si>
+  <si>
+    <t>Sutton</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>S Martin</t>
+  </si>
+  <si>
+    <t>R Madley</t>
+  </si>
+  <si>
+    <t>D Whitestone</t>
+  </si>
+  <si>
+    <t>O Langford</t>
+  </si>
+  <si>
     <t>T Reeves</t>
   </si>
   <si>
-    <t>A Farmer</t>
-  </si>
-  <si>
-    <t>A Byrne</t>
-  </si>
-  <si>
-    <t>Burgos</t>
-  </si>
-  <si>
-    <t>Cultural Leonesa</t>
-  </si>
-  <si>
-    <t>Valladolid</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
-    <t>Santander</t>
+    <t>A Humphries</t>
+  </si>
+  <si>
+    <t>J Durkin</t>
+  </si>
+  <si>
+    <t>M Barlow</t>
+  </si>
+  <si>
+    <t>L Swabey</t>
+  </si>
+  <si>
+    <t>W Davis</t>
+  </si>
+  <si>
+    <t>N Smith</t>
+  </si>
+  <si>
+    <t>W Cartmel</t>
+  </si>
+  <si>
+    <t>I Searle</t>
+  </si>
+  <si>
+    <t>B Atkinson</t>
+  </si>
+  <si>
+    <t>R Massey-Ellis</t>
+  </si>
+  <si>
+    <t>A Miller</t>
+  </si>
+  <si>
+    <t>Boston Utd</t>
+  </si>
+  <si>
+    <t>A Backhouse</t>
+  </si>
+  <si>
+    <t>T Nield</t>
+  </si>
+  <si>
+    <t>L Smith</t>
+  </si>
+  <si>
+    <t>J Busby</t>
+  </si>
+  <si>
+    <t>M Coy</t>
+  </si>
+  <si>
+    <t>R Ricardo</t>
+  </si>
+  <si>
+    <t>S Parkinson</t>
+  </si>
+  <si>
+    <t>K Dowle</t>
+  </si>
+  <si>
+    <t>G Rhodes</t>
   </si>
   <si>
     <t>Castellon</t>
   </si>
   <si>
-    <t>Malaga</t>
-  </si>
-  <si>
     <t>Eibar</t>
   </si>
   <si>
     <t>Granada</t>
   </si>
   <si>
-    <t>La Coruna</t>
-  </si>
-  <si>
     <t>Sociedad B</t>
   </si>
   <si>
     <t>Zaragoza</t>
   </si>
   <si>
-    <t>Cadiz</t>
-  </si>
-  <si>
-    <t>Mirandes</t>
-  </si>
-  <si>
-    <t>Huesca</t>
-  </si>
-  <si>
     <t>Leganes</t>
   </si>
   <si>
     <t>Las Palmas</t>
   </si>
   <si>
-    <t>Andorra</t>
-  </si>
-  <si>
-    <t>Sp Gijon</t>
-  </si>
-  <si>
-    <t>Cordoba</t>
-  </si>
-  <si>
     <t>Almeria</t>
   </si>
   <si>
-    <t>Albacete</t>
-  </si>
-  <si>
-    <t>C Walchester</t>
+    <t>B Toner</t>
+  </si>
+  <si>
+    <t>D Drysdale</t>
+  </si>
+  <si>
+    <t>M Salisbury</t>
+  </si>
+  <si>
+    <t>Morecambe</t>
+  </si>
+  <si>
+    <t>L Sandoe</t>
+  </si>
+  <si>
+    <t>M Burgin</t>
+  </si>
+  <si>
+    <t>W Finnie</t>
+  </si>
+  <si>
+    <t>C Breakspear</t>
   </si>
 </sst>
 </file>
@@ -1367,15 +1706,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="208" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="208"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="146" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="146"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2024,15 +2362,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64032AAF-94ED-49C7-B015-7ECD08F95F34}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:DJ17"/>
+  <dimension ref="A1:DJ52"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.26953125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.90625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.36328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" style="1" customWidth="1"/>
     <col min="7" max="8" width="6.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="5.7265625" style="1" bestFit="1" customWidth="1"/>
@@ -2042,7 +2380,10 @@
     <col min="16" max="18" width="4.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="5.08984375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="27" width="4.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="29" width="4.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="4.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="32" width="5.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -2108,7 +2449,7 @@
     <col min="115" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:114" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:114" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2125,7 +2466,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>4</v>
@@ -2137,31 +2478,31 @@
         <v>6</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="O1" s="8" t="s">
         <v>93</v>
       </c>
+      <c r="M1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>96</v>
+      </c>
       <c r="P1" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>7</v>
@@ -2173,22 +2514,22 @@
         <v>9</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AB1" s="5" t="s">
         <v>10</v>
@@ -2199,13 +2540,13 @@
       <c r="AD1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AE1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="AF1" s="8" t="s">
+      <c r="AF1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="AG1" s="8" t="s">
+      <c r="AG1" s="7" t="s">
         <v>16</v>
       </c>
       <c r="AH1" s="5" t="s">
@@ -2218,13 +2559,13 @@
         <v>19</v>
       </c>
       <c r="AK1" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AL1" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AM1" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AN1" s="5" t="s">
         <v>20</v>
@@ -2232,10 +2573,10 @@
       <c r="AO1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AP1" s="8" t="s">
+      <c r="AP1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="AQ1" s="8" t="s">
+      <c r="AQ1" s="7" t="s">
         <v>23</v>
       </c>
       <c r="AR1" s="5" t="s">
@@ -2251,10 +2592,10 @@
         <v>27</v>
       </c>
       <c r="AV1" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AW1" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AX1" s="5" t="s">
         <v>28</v>
@@ -2265,10 +2606,10 @@
       <c r="AZ1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="BA1" s="8" t="s">
+      <c r="BA1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="BB1" s="8" t="s">
+      <c r="BB1" s="7" t="s">
         <v>32</v>
       </c>
       <c r="BC1" s="5" t="s">
@@ -2284,10 +2625,10 @@
         <v>36</v>
       </c>
       <c r="BG1" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BH1" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="BI1" s="5" t="s">
         <v>37</v>
@@ -2299,31 +2640,31 @@
         <v>39</v>
       </c>
       <c r="BL1" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="BM1" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BN1" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BO1" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="BP1" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="BQ1" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BR1" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="BS1" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="BT1" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="BU1" s="5" t="s">
         <v>40</v>
@@ -2335,22 +2676,22 @@
         <v>42</v>
       </c>
       <c r="BX1" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="BY1" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="BZ1" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="CA1" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="CB1" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="CC1" s="8" t="s">
         <v>117</v>
+      </c>
+      <c r="CA1" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="CB1" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="CC1" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="CD1" s="5" t="s">
         <v>43</v>
@@ -2376,17 +2717,17 @@
       <c r="CK1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="CL1" s="8" t="s">
+      <c r="CL1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="CM1" s="8" t="s">
-        <v>83</v>
+      <c r="CM1" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="CN1" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="CO1" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="CP1" s="5" t="s">
         <v>52</v>
@@ -2409,14 +2750,14 @@
       <c r="CV1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="CW1" s="8" t="s">
+      <c r="CW1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="CX1" s="8" t="s">
-        <v>81</v>
+      <c r="CX1" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="CY1" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="CZ1" s="5" t="s">
         <v>60</v>
@@ -2446,75 +2787,73 @@
         <v>68</v>
       </c>
       <c r="DI1" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="DJ1" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>69</v>
+      <c r="A2" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="B2" s="2">
         <v>46114</v>
       </c>
       <c r="C2" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>129</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="F2"/>
       <c r="G2">
-        <v>2.2000000000000002</v>
+        <v>1.96</v>
       </c>
       <c r="H2">
         <v>3.1</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
-        <v>2.2999999999999998</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="M2">
-        <v>2.2000000000000002</v>
+        <v>1.89</v>
       </c>
       <c r="N2">
         <v>3.25</v>
       </c>
       <c r="O2">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q2">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="S2">
-        <v>2.2999999999999998</v>
+        <v>1.95</v>
       </c>
       <c r="T2">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U2">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="V2"/>
       <c r="W2"/>
@@ -2526,31 +2865,31 @@
       <c r="AC2"/>
       <c r="AD2"/>
       <c r="AE2">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AF2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AG2">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH2">
-        <v>2.2599999999999998</v>
+        <v>1.95</v>
       </c>
       <c r="AI2">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="AJ2">
-        <v>3.03</v>
+        <v>3.94</v>
       </c>
       <c r="AK2">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="AL2">
         <v>3.2</v>
       </c>
       <c r="AM2">
-        <v>3.1</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AN2">
         <v>2.15</v>
@@ -2561,28 +2900,28 @@
       <c r="AP2"/>
       <c r="AQ2"/>
       <c r="AR2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AS2">
+        <v>1.67</v>
+      </c>
+      <c r="AT2">
         <v>2.15</v>
       </c>
-      <c r="AS2">
-        <v>1.73</v>
-      </c>
-      <c r="AT2">
-        <v>2.08</v>
-      </c>
       <c r="AU2">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AV2">
-        <v>2.14</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="AW2">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AX2">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AY2">
-        <v>2.0299999999999998</v>
+        <v>1.98</v>
       </c>
       <c r="AZ2">
         <v>1.83</v>
@@ -2590,83 +2929,81 @@
       <c r="BA2"/>
       <c r="BB2"/>
       <c r="BC2">
-        <v>2.0299999999999998</v>
+        <v>2</v>
       </c>
       <c r="BD2">
         <v>1.83</v>
       </c>
       <c r="BE2">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BF2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BG2"/>
       <c r="BH2"/>
     </row>
     <row r="3" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>71</v>
+      <c r="A3" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="B3" s="2">
         <v>46114</v>
       </c>
       <c r="C3" s="3">
-        <v>0.83333333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>252</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>122</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="F3"/>
       <c r="G3">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="J3">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="K3">
+        <v>3.75</v>
+      </c>
+      <c r="L3">
+        <v>3.3</v>
+      </c>
+      <c r="M3">
+        <v>1.83</v>
+      </c>
+      <c r="N3">
+        <v>3.7</v>
+      </c>
+      <c r="O3">
+        <v>3.65</v>
+      </c>
+      <c r="P3">
+        <v>1.95</v>
+      </c>
+      <c r="Q3">
+        <v>3.7</v>
+      </c>
+      <c r="R3">
+        <v>3.2</v>
+      </c>
+      <c r="S3">
+        <v>1.95</v>
+      </c>
+      <c r="T3">
         <v>3.6</v>
       </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>1.73</v>
-      </c>
-      <c r="N3">
-        <v>3.6</v>
-      </c>
-      <c r="O3">
-        <v>4.3</v>
-      </c>
-      <c r="P3">
-        <v>1.65</v>
-      </c>
-      <c r="Q3">
-        <v>3.6</v>
-      </c>
-      <c r="R3">
-        <v>4.75</v>
-      </c>
-      <c r="S3">
-        <v>1.7</v>
-      </c>
-      <c r="T3">
-        <v>3.75</v>
-      </c>
       <c r="U3">
-        <v>4.5999999999999996</v>
+        <v>3.25</v>
       </c>
       <c r="V3"/>
       <c r="W3"/>
@@ -2678,151 +3015,145 @@
       <c r="AC3"/>
       <c r="AD3"/>
       <c r="AE3">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF3">
         <v>3.75</v>
       </c>
       <c r="AG3">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="AH3">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="AI3">
-        <v>3.61</v>
+        <v>3.7</v>
       </c>
       <c r="AJ3">
-        <v>4.6399999999999997</v>
+        <v>3.3</v>
       </c>
       <c r="AK3">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AL3">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AM3">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="AN3">
-        <v>2.0299999999999998</v>
+        <v>1.57</v>
       </c>
       <c r="AO3">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AP3"/>
       <c r="AQ3"/>
       <c r="AR3">
-        <v>2.0299999999999998</v>
+        <v>1.6</v>
       </c>
       <c r="AS3">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="AT3">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="AU3">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="AV3">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AW3">
-        <v>1.85</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="AX3">
-        <v>-0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="AY3">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AZ3">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BA3"/>
       <c r="BB3"/>
       <c r="BC3">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BD3">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="BE3">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BF3">
-        <v>1.84</v>
-      </c>
-      <c r="BG3">
-        <v>1.97</v>
-      </c>
-      <c r="BH3">
-        <v>1.91</v>
-      </c>
+        <v>1.79</v>
+      </c>
+      <c r="BG3"/>
+      <c r="BH3"/>
     </row>
     <row r="4" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>70</v>
+      <c r="A4" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="B4" s="2">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C4" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>255</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="F4"/>
       <c r="G4">
-        <v>1.38</v>
+        <v>2.82</v>
       </c>
       <c r="H4">
-        <v>4.0999999999999996</v>
+        <v>3.1</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="J4">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="K4">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="M4">
-        <v>1.35</v>
+        <v>2.7</v>
       </c>
       <c r="N4">
-        <v>4.5999999999999996</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>7</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="P4">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
-        <v>4.4000000000000004</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>2.65</v>
       </c>
       <c r="T4">
-        <v>4.4000000000000004</v>
+        <v>3.1</v>
       </c>
       <c r="U4">
-        <v>6.75</v>
+        <v>2.5</v>
       </c>
       <c r="V4"/>
       <c r="W4"/>
@@ -2834,151 +3165,145 @@
       <c r="AC4"/>
       <c r="AD4"/>
       <c r="AE4">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="AF4">
-        <v>4.5999999999999996</v>
+        <v>3.2</v>
       </c>
       <c r="AG4">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH4">
-        <v>1.36</v>
+        <v>2.72</v>
       </c>
       <c r="AI4">
-        <v>4.3600000000000003</v>
+        <v>3.08</v>
       </c>
       <c r="AJ4">
-        <v>7.67</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="AK4">
-        <v>1.39</v>
+        <v>2.9</v>
       </c>
       <c r="AL4">
-        <v>4.9000000000000004</v>
+        <v>3.1</v>
       </c>
       <c r="AM4">
-        <v>10</v>
+        <v>2.66</v>
       </c>
       <c r="AN4">
-        <v>1.85</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AO4">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AP4"/>
       <c r="AQ4"/>
       <c r="AR4">
-        <v>1.85</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AS4">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="AT4">
-        <v>1.77</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="AU4">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AV4">
-        <v>1.87</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="AW4">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="AX4">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="AY4">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AZ4">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BA4"/>
       <c r="BB4"/>
       <c r="BC4">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BD4">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BE4">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="BF4">
-        <v>1.87</v>
-      </c>
-      <c r="BG4">
-        <v>1.91</v>
-      </c>
-      <c r="BH4">
-        <v>1.94</v>
-      </c>
+        <v>1.78</v>
+      </c>
+      <c r="BG4"/>
+      <c r="BH4"/>
     </row>
     <row r="5" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
-        <v>70</v>
+      <c r="A5" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="B5" s="2">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C5" s="3">
-        <v>0.82291666666666663</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>257</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>130</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="F5"/>
       <c r="G5">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="H5">
         <v>3.3</v>
       </c>
       <c r="I5">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="K5">
+        <v>3.25</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>1.8</v>
+      </c>
+      <c r="N5">
         <v>3.4</v>
       </c>
-      <c r="L5">
-        <v>2.5</v>
-      </c>
-      <c r="M5">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="N5">
-        <v>3.35</v>
-      </c>
       <c r="O5">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q5">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="S5">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="T5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.4500000000000002</v>
+        <v>3.7</v>
       </c>
       <c r="V5"/>
       <c r="W5"/>
@@ -2990,151 +3315,147 @@
       <c r="AC5"/>
       <c r="AD5"/>
       <c r="AE5">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AF5">
         <v>3.4</v>
       </c>
       <c r="AG5">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="AH5">
-        <v>2.4900000000000002</v>
+        <v>1.9</v>
       </c>
       <c r="AI5">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="AJ5">
-        <v>2.52</v>
+        <v>3.88</v>
       </c>
       <c r="AK5">
-        <v>2.74</v>
+        <v>2.04</v>
       </c>
       <c r="AL5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AM5">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="AN5">
-        <v>1.75</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AO5">
-        <v>2.0499999999999998</v>
+        <v>1.65</v>
       </c>
       <c r="AP5"/>
       <c r="AQ5"/>
       <c r="AR5">
-        <v>1.75</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AS5">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AT5">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="AU5">
-        <v>2.0699999999999998</v>
+        <v>1.65</v>
       </c>
       <c r="AV5">
-        <v>1.79</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="AW5">
-        <v>2.1800000000000002</v>
+        <v>1.67</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AY5">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AZ5">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="BA5"/>
       <c r="BB5"/>
       <c r="BC5">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BD5">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="BE5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BF5">
-        <v>1.84</v>
-      </c>
-      <c r="BG5">
-        <v>1.94</v>
-      </c>
-      <c r="BH5">
-        <v>1.93</v>
-      </c>
+        <v>1.83</v>
+      </c>
+      <c r="BG5"/>
+      <c r="BH5"/>
     </row>
     <row r="6" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>70</v>
+      <c r="A6" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="B6" s="2">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C6" s="3">
         <v>0.82291666666666663</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="G6">
-        <v>1.9</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H6">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I6">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>1.91</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="M6">
-        <v>1.95</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N6">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="R6">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="S6">
-        <v>1.9</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="T6">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="V6"/>
       <c r="W6"/>
@@ -3146,149 +3467,147 @@
       <c r="AC6"/>
       <c r="AD6"/>
       <c r="AE6">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AF6">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AG6">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="AH6">
-        <v>1.91</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="AI6">
-        <v>3.47</v>
+        <v>3.21</v>
       </c>
       <c r="AJ6">
-        <v>3.48</v>
+        <v>3.03</v>
       </c>
       <c r="AK6">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="AL6">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AM6">
-        <v>4.0999999999999996</v>
+        <v>3.1</v>
       </c>
       <c r="AN6">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AO6">
-        <v>2.0499999999999998</v>
+        <v>1.67</v>
       </c>
       <c r="AP6"/>
       <c r="AQ6"/>
       <c r="AR6">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AS6">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AT6">
+        <v>2.08</v>
+      </c>
+      <c r="AU6">
+        <v>1.68</v>
+      </c>
+      <c r="AV6">
+        <v>2.14</v>
+      </c>
+      <c r="AW6">
         <v>1.72</v>
       </c>
-      <c r="AU6">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="AV6">
-        <v>1.76</v>
-      </c>
-      <c r="AW6">
-        <v>2.2400000000000002</v>
-      </c>
       <c r="AX6">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="AY6">
-        <v>1.93</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AZ6">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="BA6"/>
       <c r="BB6"/>
       <c r="BC6">
-        <v>1.93</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="BD6">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="BE6">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="BF6">
-        <v>1.81</v>
-      </c>
-      <c r="BG6">
-        <v>1.94</v>
-      </c>
-      <c r="BH6">
-        <v>2.0099999999999998</v>
-      </c>
+        <v>1.77</v>
+      </c>
+      <c r="BG6"/>
+      <c r="BH6"/>
     </row>
     <row r="7" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>72</v>
+      <c r="A7" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="B7" s="2">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C7" s="3">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F7"/>
+        <v>164</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>167</v>
+      </c>
       <c r="G7">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="K7">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>2.5499999999999998</v>
+        <v>1.73</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="P7">
-        <v>2.2999999999999998</v>
+        <v>1.65</v>
       </c>
       <c r="Q7">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R7">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="S7">
-        <v>2.4500000000000002</v>
+        <v>1.7</v>
       </c>
       <c r="T7">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="U7">
-        <v>2.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="V7"/>
       <c r="W7"/>
@@ -3300,37 +3619,37 @@
       <c r="AC7"/>
       <c r="AD7"/>
       <c r="AE7">
-        <v>2.5499999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="AF7">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AG7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH7">
-        <v>2.41</v>
+        <v>1.69</v>
       </c>
       <c r="AI7">
-        <v>3.21</v>
+        <v>3.61</v>
       </c>
       <c r="AJ7">
-        <v>2.75</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="AK7">
-        <v>2.58</v>
+        <v>1.75</v>
       </c>
       <c r="AL7">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AM7">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="AN7">
         <v>2.0299999999999998</v>
       </c>
       <c r="AO7">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AP7"/>
       <c r="AQ7"/>
@@ -3338,111 +3657,113 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="AS7">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AT7">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AU7">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AV7">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AW7">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="AY7">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AZ7">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="BA7"/>
       <c r="BB7"/>
       <c r="BC7">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="BD7">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="BE7">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="BF7">
-        <v>2.0299999999999998</v>
+        <v>1.84</v>
       </c>
       <c r="BG7">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="BH7">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="8" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>72</v>
+      <c r="A8" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="B8" s="2">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="C8" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="E8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F8"/>
+        <v>188</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>243</v>
+      </c>
       <c r="G8">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="H8">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I8">
+        <v>4.5</v>
+      </c>
+      <c r="J8">
+        <v>1.73</v>
+      </c>
+      <c r="K8">
+        <v>3.75</v>
+      </c>
+      <c r="L8">
+        <v>4.5</v>
+      </c>
+      <c r="M8">
+        <v>1.72</v>
+      </c>
+      <c r="N8">
+        <v>3.85</v>
+      </c>
+      <c r="O8">
+        <v>4.5</v>
+      </c>
+      <c r="P8">
+        <v>1.7</v>
+      </c>
+      <c r="Q8">
+        <v>3.9</v>
+      </c>
+      <c r="R8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S8">
+        <v>1.73</v>
+      </c>
+      <c r="T8">
         <v>4</v>
       </c>
-      <c r="J8">
-        <v>1.9</v>
-      </c>
-      <c r="K8">
-        <v>3.5</v>
-      </c>
-      <c r="L8">
-        <v>3.6</v>
-      </c>
-      <c r="M8">
-        <v>1.94</v>
-      </c>
-      <c r="N8">
-        <v>3.5</v>
-      </c>
-      <c r="O8">
-        <v>3.5</v>
-      </c>
-      <c r="P8">
-        <v>1.83</v>
-      </c>
-      <c r="Q8">
-        <v>3.5</v>
-      </c>
-      <c r="R8">
-        <v>3.8</v>
-      </c>
-      <c r="S8">
-        <v>1.87</v>
-      </c>
-      <c r="T8">
-        <v>3.4</v>
-      </c>
       <c r="U8">
-        <v>3.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="V8"/>
       <c r="W8"/>
@@ -3454,149 +3775,151 @@
       <c r="AC8"/>
       <c r="AD8"/>
       <c r="AE8">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AF8">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AG8">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AH8">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AI8">
-        <v>3.49</v>
+        <v>3.85</v>
       </c>
       <c r="AJ8">
-        <v>3.73</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="AK8">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="AL8">
-        <v>3.75</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AM8">
-        <v>4.2</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AN8">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AO8">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AP8"/>
       <c r="AQ8"/>
       <c r="AR8">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AS8">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AT8">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AU8">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="AV8">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AW8">
-        <v>2.06</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="AX8">
-        <v>-0.5</v>
+        <v>-0.75</v>
       </c>
       <c r="AY8">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AZ8">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="BA8"/>
       <c r="BB8"/>
       <c r="BC8">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="BD8">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="BE8">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="BF8">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BG8">
+        <v>2</v>
+      </c>
+      <c r="BH8">
         <v>1.97</v>
-      </c>
-      <c r="BH8">
-        <v>2.02</v>
       </c>
     </row>
     <row r="9" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
-        <v>72</v>
+      <c r="A9" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="B9" s="2">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="C9" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="E9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F9"/>
+        <v>196</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>246</v>
+      </c>
       <c r="G9">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="H9">
-        <v>4.0999999999999996</v>
+        <v>3.3</v>
       </c>
       <c r="I9">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="J9">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="L9">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="M9">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="N9">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="O9">
-        <v>5.25</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="P9">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q9">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R9">
-        <v>5.75</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="S9">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="T9">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
-        <v>5.25</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="V9"/>
       <c r="W9"/>
@@ -3608,149 +3931,151 @@
       <c r="AC9"/>
       <c r="AD9"/>
       <c r="AE9">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AF9">
-        <v>4.0999999999999996</v>
+        <v>3.4</v>
       </c>
       <c r="AG9">
-        <v>6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AH9">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AI9">
-        <v>3.89</v>
+        <v>3.37</v>
       </c>
       <c r="AJ9">
-        <v>5.57</v>
+        <v>4.41</v>
       </c>
       <c r="AK9">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AL9">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="AM9">
-        <v>6.4</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AN9">
-        <v>1.85</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AO9">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AP9"/>
       <c r="AQ9"/>
       <c r="AR9">
-        <v>1.91</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="AS9">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AT9">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AU9">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AV9">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="AW9">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="AX9">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AY9">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AZ9">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BA9"/>
       <c r="BB9"/>
       <c r="BC9">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BD9">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BE9">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BF9">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BG9">
-        <v>2.0699999999999998</v>
+        <v>1.97</v>
       </c>
       <c r="BH9">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="10" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
-        <v>72</v>
+      <c r="A10" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="B10" s="2">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C10" s="3">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="E10" t="s">
-        <v>138</v>
-      </c>
-      <c r="F10"/>
+        <v>200</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>260</v>
+      </c>
       <c r="G10">
-        <v>2.25</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H10">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="J10">
-        <v>2.2999999999999998</v>
+        <v>2.5</v>
       </c>
       <c r="K10">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L10">
         <v>2.8</v>
       </c>
       <c r="M10">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="N10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O10">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="P10">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
         <v>2.88</v>
       </c>
       <c r="S10">
-        <v>2.2999999999999998</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="T10">
         <v>3.25</v>
       </c>
       <c r="U10">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V10"/>
       <c r="W10"/>
@@ -3762,149 +4087,151 @@
       <c r="AC10"/>
       <c r="AD10"/>
       <c r="AE10">
-        <v>2.2999999999999998</v>
+        <v>2.57</v>
       </c>
       <c r="AF10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AG10">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AH10">
-        <v>2.2400000000000002</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="AI10">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AJ10">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AK10">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="AL10">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AM10">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AN10">
-        <v>1.9</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AO10">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AP10"/>
       <c r="AQ10"/>
       <c r="AR10">
-        <v>1.91</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="AS10">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AT10">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="AU10">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AV10">
-        <v>1.94</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="AW10">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AX10">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>2.0299999999999998</v>
+        <v>1.8</v>
       </c>
       <c r="AZ10">
-        <v>1.78</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="BA10"/>
       <c r="BB10"/>
       <c r="BC10">
-        <v>2.0299999999999998</v>
+        <v>1.81</v>
       </c>
       <c r="BD10">
-        <v>1.83</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="BE10">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="BF10">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="BG10">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="BH10">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="11" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D11" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="2">
-        <v>46113</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D11" t="s">
-        <v>132</v>
-      </c>
       <c r="E11" t="s">
-        <v>135</v>
-      </c>
-      <c r="F11"/>
+        <v>192</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>170</v>
+      </c>
       <c r="G11">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I11">
-        <v>5.25</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="J11">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="K11">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L11">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="M11">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="N11">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O11">
-        <v>4.25</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="P11">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q11">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R11">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="S11">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V11"/>
       <c r="W11"/>
@@ -3916,63 +4243,63 @@
       <c r="AC11"/>
       <c r="AD11"/>
       <c r="AE11">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AF11">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AG11">
-        <v>5.33</v>
+        <v>4.2</v>
       </c>
       <c r="AH11">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AI11">
-        <v>3.14</v>
+        <v>3.57</v>
       </c>
       <c r="AJ11">
-        <v>4.5599999999999996</v>
+        <v>3.99</v>
       </c>
       <c r="AK11">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AL11">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="AM11">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AN11">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AO11">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AP11"/>
       <c r="AQ11"/>
       <c r="AR11">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AS11">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AT11">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="AU11">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="AV11">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="AW11">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AX11">
         <v>-0.5</v>
       </c>
       <c r="AY11">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AZ11">
         <v>1.98</v>
@@ -3980,81 +4307,87 @@
       <c r="BA11"/>
       <c r="BB11"/>
       <c r="BC11">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="BD11">
         <v>1.98</v>
       </c>
       <c r="BE11">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="BF11">
-        <v>1.91</v>
-      </c>
-      <c r="BG11"/>
-      <c r="BH11"/>
+        <v>1.89</v>
+      </c>
+      <c r="BG11">
+        <v>1.92</v>
+      </c>
+      <c r="BH11">
+        <v>2.06</v>
+      </c>
     </row>
     <row r="12" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
-        <v>72</v>
+      <c r="A12" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="B12" s="2">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C12" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
-      </c>
-      <c r="F12"/>
+        <v>190</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>226</v>
+      </c>
       <c r="G12">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="H12">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="K12">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
         <v>3.75</v>
       </c>
       <c r="M12">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="N12">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O12">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q12">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="R12">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S12">
         <v>2</v>
       </c>
       <c r="T12">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U12">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="V12"/>
       <c r="W12"/>
@@ -4066,149 +4399,151 @@
       <c r="AC12"/>
       <c r="AD12"/>
       <c r="AE12">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AF12">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="AG12">
         <v>4</v>
       </c>
       <c r="AH12">
+        <v>1.94</v>
+      </c>
+      <c r="AI12">
+        <v>3.47</v>
+      </c>
+      <c r="AJ12">
+        <v>3.8</v>
+      </c>
+      <c r="AK12">
         <v>2</v>
       </c>
-      <c r="AI12">
-        <v>3.09</v>
-      </c>
-      <c r="AJ12">
-        <v>3.72</v>
-      </c>
-      <c r="AK12">
-        <v>2.14</v>
-      </c>
       <c r="AL12">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AM12">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="AN12">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="AO12">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AP12"/>
       <c r="AQ12"/>
       <c r="AR12">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="AS12">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AT12">
-        <v>2.2200000000000002</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="AU12">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AV12">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="AW12">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AX12">
         <v>-0.5</v>
       </c>
       <c r="AY12">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AZ12">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="BA12"/>
       <c r="BB12"/>
       <c r="BC12">
+        <v>1.98</v>
+      </c>
+      <c r="BD12">
+        <v>1.88</v>
+      </c>
+      <c r="BE12">
+        <v>1.9</v>
+      </c>
+      <c r="BF12">
+        <v>1.82</v>
+      </c>
+      <c r="BG12">
         <v>2</v>
       </c>
-      <c r="BD12">
-        <v>1.8</v>
-      </c>
-      <c r="BE12">
+      <c r="BH12">
         <v>1.98</v>
-      </c>
-      <c r="BF12">
-        <v>1.74</v>
-      </c>
-      <c r="BG12">
-        <v>2.14</v>
-      </c>
-      <c r="BH12">
-        <v>1.83</v>
       </c>
     </row>
     <row r="13" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
-        <v>72</v>
+      <c r="A13" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="B13" s="2">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C13" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="E13" t="s">
-        <v>150</v>
-      </c>
-      <c r="F13"/>
+        <v>185</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>229</v>
+      </c>
       <c r="G13">
-        <v>1.91</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H13">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I13">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="J13">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="K13">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L13">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="M13">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="N13">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O13">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="P13">
-        <v>1.93</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="Q13">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R13">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="S13">
-        <v>1.98</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="T13">
         <v>3.4</v>
       </c>
       <c r="U13">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="V13"/>
       <c r="W13"/>
@@ -4220,149 +4555,151 @@
       <c r="AC13"/>
       <c r="AD13"/>
       <c r="AE13">
-        <v>2</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="AF13">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AG13">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AH13">
-        <v>1.94</v>
+        <v>2.46</v>
       </c>
       <c r="AI13">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="AJ13">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="AK13">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="AL13">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="AM13">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AO13">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AP13"/>
       <c r="AQ13"/>
       <c r="AR13">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AS13">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AT13">
-        <v>1.76</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AU13">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AV13">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AW13">
+        <v>1.84</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>1.78</v>
+      </c>
+      <c r="AZ13">
         <v>2.1</v>
-      </c>
-      <c r="AX13">
-        <v>-0.5</v>
-      </c>
-      <c r="AY13">
-        <v>1.98</v>
-      </c>
-      <c r="AZ13">
-        <v>1.83</v>
       </c>
       <c r="BA13"/>
       <c r="BB13"/>
       <c r="BC13">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="BD13">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="BE13">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="BF13">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="BG13">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="BH13">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="14" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
-        <v>72</v>
+      <c r="A14" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="B14" s="2">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C14" s="3">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="E14" t="s">
-        <v>140</v>
-      </c>
-      <c r="F14"/>
+        <v>183</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>248</v>
+      </c>
       <c r="G14">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="H14">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="I14">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="K14">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="L14">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="M14">
-        <v>1.89</v>
+        <v>2.7</v>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="P14">
-        <v>1.95</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q14">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="S14">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="T14">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="V14"/>
       <c r="W14"/>
@@ -4374,145 +4711,151 @@
       <c r="AC14"/>
       <c r="AD14"/>
       <c r="AE14">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AF14">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AG14">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AH14">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="AI14">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AJ14">
-        <v>3.94</v>
+        <v>2.63</v>
       </c>
       <c r="AK14">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="AL14">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AM14">
-        <v>4.5999999999999996</v>
+        <v>2.8</v>
       </c>
       <c r="AN14">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AO14">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AP14"/>
       <c r="AQ14"/>
       <c r="AR14">
-        <v>2.2000000000000002</v>
+        <v>1.91</v>
       </c>
       <c r="AS14">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AT14">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AU14">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AV14">
-        <v>2.2799999999999998</v>
+        <v>1.95</v>
       </c>
       <c r="AW14">
-        <v>1.66</v>
+        <v>2.04</v>
       </c>
       <c r="AX14">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AY14">
+        <v>1.88</v>
+      </c>
+      <c r="AZ14">
         <v>1.98</v>
-      </c>
-      <c r="AZ14">
-        <v>1.83</v>
       </c>
       <c r="BA14"/>
       <c r="BB14"/>
       <c r="BC14">
+        <v>1.88</v>
+      </c>
+      <c r="BD14">
+        <v>1.98</v>
+      </c>
+      <c r="BE14">
+        <v>1.84</v>
+      </c>
+      <c r="BF14">
+        <v>1.92</v>
+      </c>
+      <c r="BG14">
+        <v>1.93</v>
+      </c>
+      <c r="BH14">
         <v>2</v>
       </c>
-      <c r="BD14">
-        <v>1.83</v>
-      </c>
-      <c r="BE14">
-        <v>1.92</v>
-      </c>
-      <c r="BF14">
-        <v>1.78</v>
-      </c>
-      <c r="BG14"/>
-      <c r="BH14"/>
     </row>
     <row r="15" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>72</v>
+      <c r="A15" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="B15" s="2">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C15" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="E15" t="s">
-        <v>152</v>
-      </c>
-      <c r="F15"/>
+        <v>198</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>228</v>
+      </c>
       <c r="G15">
         <v>1.96</v>
       </c>
       <c r="H15">
+        <v>3.6</v>
+      </c>
+      <c r="I15">
+        <v>3.5</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>3.6</v>
+      </c>
+      <c r="L15">
+        <v>3.6</v>
+      </c>
+      <c r="M15">
+        <v>1.88</v>
+      </c>
+      <c r="N15">
+        <v>3.6</v>
+      </c>
+      <c r="O15">
+        <v>3.9</v>
+      </c>
+      <c r="P15">
+        <v>2</v>
+      </c>
+      <c r="Q15">
+        <v>3.5</v>
+      </c>
+      <c r="R15">
+        <v>3.6</v>
+      </c>
+      <c r="S15">
+        <v>1.98</v>
+      </c>
+      <c r="T15">
+        <v>3.5</v>
+      </c>
+      <c r="U15">
         <v>3.75</v>
-      </c>
-      <c r="I15">
-        <v>3.3</v>
-      </c>
-      <c r="J15">
-        <v>1.91</v>
-      </c>
-      <c r="K15">
-        <v>3.75</v>
-      </c>
-      <c r="L15">
-        <v>3.3</v>
-      </c>
-      <c r="M15">
-        <v>1.83</v>
-      </c>
-      <c r="N15">
-        <v>3.7</v>
-      </c>
-      <c r="O15">
-        <v>3.65</v>
-      </c>
-      <c r="P15">
-        <v>1.95</v>
-      </c>
-      <c r="Q15">
-        <v>3.7</v>
-      </c>
-      <c r="R15">
-        <v>3.2</v>
-      </c>
-      <c r="S15">
-        <v>1.95</v>
-      </c>
-      <c r="T15">
-        <v>3.6</v>
-      </c>
-      <c r="U15">
-        <v>3.25</v>
       </c>
       <c r="V15"/>
       <c r="W15"/>
@@ -4527,142 +4870,148 @@
         <v>2</v>
       </c>
       <c r="AF15">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="AG15">
+        <v>3.95</v>
+      </c>
+      <c r="AH15">
+        <v>1.96</v>
+      </c>
+      <c r="AI15">
+        <v>3.55</v>
+      </c>
+      <c r="AJ15">
         <v>3.65</v>
-      </c>
-      <c r="AH15">
-        <v>1.92</v>
-      </c>
-      <c r="AI15">
-        <v>3.7</v>
-      </c>
-      <c r="AJ15">
-        <v>3.3</v>
       </c>
       <c r="AK15">
         <v>2.1</v>
       </c>
       <c r="AL15">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AM15">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AN15">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AO15">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AP15"/>
       <c r="AQ15"/>
       <c r="AR15">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AS15">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AT15">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="AU15">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="AV15">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="AW15">
-        <v>2.3199999999999998</v>
+        <v>1.98</v>
       </c>
       <c r="AX15">
         <v>-0.5</v>
       </c>
       <c r="AY15">
-        <v>2</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AZ15">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BA15"/>
       <c r="BB15"/>
       <c r="BC15">
-        <v>2</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="BD15">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BE15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BF15">
-        <v>1.79</v>
-      </c>
-      <c r="BG15"/>
-      <c r="BH15"/>
+        <v>1.81</v>
+      </c>
+      <c r="BG15">
+        <v>2.1</v>
+      </c>
+      <c r="BH15">
+        <v>1.87</v>
+      </c>
     </row>
     <row r="16" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
-        <v>72</v>
+      <c r="A16" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="B16" s="2">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C16" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
-      </c>
-      <c r="F16"/>
+        <v>201</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>262</v>
+      </c>
       <c r="G16">
-        <v>2.82</v>
+        <v>1.3</v>
       </c>
       <c r="H16">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="I16">
-        <v>2.5499999999999998</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="K16">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="M16">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="O16">
-        <v>2.5499999999999998</v>
+        <v>8.5</v>
       </c>
       <c r="P16">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="Q16">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="R16">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>2.65</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>8.25</v>
       </c>
       <c r="V16"/>
       <c r="W16"/>
@@ -4674,145 +5023,151 @@
       <c r="AC16"/>
       <c r="AD16"/>
       <c r="AE16">
-        <v>2.83</v>
+        <v>1.36</v>
       </c>
       <c r="AF16">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="AG16">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>2.72</v>
+        <v>1.31</v>
       </c>
       <c r="AI16">
-        <v>3.08</v>
+        <v>5.03</v>
       </c>
       <c r="AJ16">
-        <v>2.5099999999999998</v>
+        <v>9.56</v>
       </c>
       <c r="AK16">
-        <v>2.9</v>
+        <v>1.35</v>
       </c>
       <c r="AL16">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="AM16">
-        <v>2.66</v>
+        <v>11.5</v>
       </c>
       <c r="AN16">
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="AO16">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AP16"/>
       <c r="AQ16"/>
       <c r="AR16">
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="AS16">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AT16">
-        <v>2.1800000000000002</v>
+        <v>1.72</v>
       </c>
       <c r="AU16">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="AV16">
-        <v>2.2799999999999998</v>
+        <v>1.79</v>
       </c>
       <c r="AW16">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AY16">
-        <v>2</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AZ16">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BA16"/>
       <c r="BB16"/>
       <c r="BC16">
-        <v>2</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="BD16">
+        <v>1.87</v>
+      </c>
+      <c r="BE16">
+        <v>1.92</v>
+      </c>
+      <c r="BF16">
         <v>1.8</v>
       </c>
-      <c r="BE16">
-        <v>1.94</v>
-      </c>
-      <c r="BF16">
-        <v>1.78</v>
-      </c>
-      <c r="BG16"/>
-      <c r="BH16"/>
+      <c r="BG16">
+        <v>2.04</v>
+      </c>
+      <c r="BH16">
+        <v>1.92</v>
+      </c>
     </row>
     <row r="17" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
-        <v>72</v>
+      <c r="A17" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="B17" s="2">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C17" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="E17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F17"/>
+        <v>186</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="G17">
-        <v>1.91</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="H17">
         <v>3.3</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J17">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="K17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="M17">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="N17">
+        <v>3.3</v>
+      </c>
+      <c r="O17">
         <v>3.4</v>
       </c>
-      <c r="O17">
-        <v>4.2</v>
-      </c>
       <c r="P17">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R17">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="S17">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U17">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="V17"/>
       <c r="W17"/>
@@ -4824,90 +5179,5544 @@
       <c r="AC17"/>
       <c r="AD17"/>
       <c r="AE17">
-        <v>2</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="AF17">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AG17">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AH17">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AI17">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="AJ17">
-        <v>3.88</v>
+        <v>3.43</v>
       </c>
       <c r="AK17">
-        <v>2.04</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AL17">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AM17">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AN17">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="AO17">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AP17"/>
       <c r="AQ17"/>
       <c r="AR17">
-        <v>2.2000000000000002</v>
+        <v>2.14</v>
       </c>
       <c r="AS17">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AT17">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AU17">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AV17">
-        <v>2.2200000000000002</v>
+        <v>2.16</v>
       </c>
       <c r="AW17">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AX17">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="AY17">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AZ17">
-        <v>1.83</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="BA17"/>
       <c r="BB17"/>
       <c r="BC17">
+        <v>1.8</v>
+      </c>
+      <c r="BD17">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BE17">
+        <v>1.77</v>
+      </c>
+      <c r="BF17">
+        <v>1.99</v>
+      </c>
+      <c r="BG17">
+        <v>1.89</v>
+      </c>
+      <c r="BH17">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="18" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D18" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G18">
+        <v>1.53</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18">
+        <v>6</v>
+      </c>
+      <c r="J18">
+        <v>1.6</v>
+      </c>
+      <c r="K18">
+        <v>4</v>
+      </c>
+      <c r="L18">
+        <v>5.5</v>
+      </c>
+      <c r="M18">
+        <v>1.6</v>
+      </c>
+      <c r="N18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O18">
+        <v>5.25</v>
+      </c>
+      <c r="P18">
+        <v>1.57</v>
+      </c>
+      <c r="Q18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="R18">
+        <v>5.5</v>
+      </c>
+      <c r="S18">
+        <v>1.6</v>
+      </c>
+      <c r="T18">
+        <v>4.33</v>
+      </c>
+      <c r="U18">
+        <v>5</v>
+      </c>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18"/>
+      <c r="AA18"/>
+      <c r="AB18"/>
+      <c r="AC18"/>
+      <c r="AD18"/>
+      <c r="AE18">
+        <v>1.61</v>
+      </c>
+      <c r="AF18">
+        <v>4.33</v>
+      </c>
+      <c r="AG18">
+        <v>6</v>
+      </c>
+      <c r="AH18">
+        <v>1.57</v>
+      </c>
+      <c r="AI18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AJ18">
+        <v>5.39</v>
+      </c>
+      <c r="AK18">
+        <v>1.63</v>
+      </c>
+      <c r="AL18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AM18">
+        <v>6.2</v>
+      </c>
+      <c r="AN18">
+        <v>1.73</v>
+      </c>
+      <c r="AO18">
+        <v>2.1</v>
+      </c>
+      <c r="AP18"/>
+      <c r="AQ18"/>
+      <c r="AR18">
+        <v>1.73</v>
+      </c>
+      <c r="AS18">
+        <v>2.16</v>
+      </c>
+      <c r="AT18">
+        <v>1.68</v>
+      </c>
+      <c r="AU18">
+        <v>2.11</v>
+      </c>
+      <c r="AV18">
+        <v>1.77</v>
+      </c>
+      <c r="AW18">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AX18">
+        <v>-1</v>
+      </c>
+      <c r="AY18">
+        <v>2</v>
+      </c>
+      <c r="AZ18">
+        <v>1.85</v>
+      </c>
+      <c r="BA18"/>
+      <c r="BB18"/>
+      <c r="BC18">
+        <v>2</v>
+      </c>
+      <c r="BD18">
+        <v>1.86</v>
+      </c>
+      <c r="BE18">
+        <v>1.94</v>
+      </c>
+      <c r="BF18">
+        <v>1.81</v>
+      </c>
+      <c r="BG18">
+        <v>2.04</v>
+      </c>
+      <c r="BH18">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H19">
+        <v>3.4</v>
+      </c>
+      <c r="I19">
+        <v>3.1</v>
+      </c>
+      <c r="J19">
+        <v>2.25</v>
+      </c>
+      <c r="K19">
+        <v>3.5</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>2.06</v>
+      </c>
+      <c r="N19">
+        <v>3.55</v>
+      </c>
+      <c r="O19">
+        <v>3.25</v>
+      </c>
+      <c r="P19">
+        <v>2.25</v>
+      </c>
+      <c r="Q19">
+        <v>3.5</v>
+      </c>
+      <c r="R19">
+        <v>3</v>
+      </c>
+      <c r="S19">
+        <v>2.15</v>
+      </c>
+      <c r="T19">
+        <v>3.6</v>
+      </c>
+      <c r="U19">
+        <v>3</v>
+      </c>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19"/>
+      <c r="AA19"/>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
+      <c r="AE19">
+        <v>2.25</v>
+      </c>
+      <c r="AF19">
+        <v>3.6</v>
+      </c>
+      <c r="AG19">
+        <v>3.25</v>
+      </c>
+      <c r="AH19">
+        <v>2.19</v>
+      </c>
+      <c r="AI19">
+        <v>3.51</v>
+      </c>
+      <c r="AJ19">
+        <v>3.02</v>
+      </c>
+      <c r="AK19">
+        <v>2.34</v>
+      </c>
+      <c r="AL19">
+        <v>3.65</v>
+      </c>
+      <c r="AM19">
+        <v>3.25</v>
+      </c>
+      <c r="AN19">
+        <v>1.8</v>
+      </c>
+      <c r="AO19">
+        <v>2</v>
+      </c>
+      <c r="AP19"/>
+      <c r="AQ19"/>
+      <c r="AR19">
+        <v>1.8</v>
+      </c>
+      <c r="AS19">
+        <v>2.06</v>
+      </c>
+      <c r="AT19">
+        <v>1.76</v>
+      </c>
+      <c r="AU19">
         <v>1.98</v>
       </c>
-      <c r="BD17">
+      <c r="AV19">
+        <v>1.85</v>
+      </c>
+      <c r="AW19">
+        <v>2.04</v>
+      </c>
+      <c r="AX19">
+        <v>-0.25</v>
+      </c>
+      <c r="AY19">
+        <v>1.98</v>
+      </c>
+      <c r="AZ19">
+        <v>1.88</v>
+      </c>
+      <c r="BA19"/>
+      <c r="BB19"/>
+      <c r="BC19">
+        <v>1.98</v>
+      </c>
+      <c r="BD19">
+        <v>1.88</v>
+      </c>
+      <c r="BE19">
+        <v>1.91</v>
+      </c>
+      <c r="BF19">
+        <v>1.81</v>
+      </c>
+      <c r="BG19">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="BH19">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G20">
+        <v>2.1</v>
+      </c>
+      <c r="H20">
+        <v>3.4</v>
+      </c>
+      <c r="I20">
+        <v>3.2</v>
+      </c>
+      <c r="J20">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K20">
+        <v>3.5</v>
+      </c>
+      <c r="L20">
+        <v>3.1</v>
+      </c>
+      <c r="M20">
+        <v>2.1</v>
+      </c>
+      <c r="N20">
+        <v>3.4</v>
+      </c>
+      <c r="O20">
+        <v>3.25</v>
+      </c>
+      <c r="P20">
+        <v>2.15</v>
+      </c>
+      <c r="Q20">
+        <v>3.5</v>
+      </c>
+      <c r="R20">
+        <v>3.2</v>
+      </c>
+      <c r="S20">
+        <v>2.15</v>
+      </c>
+      <c r="T20">
+        <v>3.5</v>
+      </c>
+      <c r="U20">
+        <v>3.1</v>
+      </c>
+      <c r="V20"/>
+      <c r="W20"/>
+      <c r="X20"/>
+      <c r="Y20"/>
+      <c r="Z20"/>
+      <c r="AA20"/>
+      <c r="AB20"/>
+      <c r="AC20"/>
+      <c r="AD20"/>
+      <c r="AE20">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AF20">
+        <v>3.6</v>
+      </c>
+      <c r="AG20">
+        <v>3.3</v>
+      </c>
+      <c r="AH20">
+        <v>2.13</v>
+      </c>
+      <c r="AI20">
+        <v>3.44</v>
+      </c>
+      <c r="AJ20">
+        <v>3.18</v>
+      </c>
+      <c r="AK20">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AL20">
+        <v>3.65</v>
+      </c>
+      <c r="AM20">
+        <v>3.4</v>
+      </c>
+      <c r="AN20">
+        <v>1.85</v>
+      </c>
+      <c r="AO20">
+        <v>1.95</v>
+      </c>
+      <c r="AP20"/>
+      <c r="AQ20"/>
+      <c r="AR20">
+        <v>1.85</v>
+      </c>
+      <c r="AS20">
+        <v>2</v>
+      </c>
+      <c r="AT20">
+        <v>1.8</v>
+      </c>
+      <c r="AU20">
+        <v>1.93</v>
+      </c>
+      <c r="AV20">
         <v>1.92</v>
       </c>
-      <c r="BE17">
+      <c r="AW20">
+        <v>2.04</v>
+      </c>
+      <c r="AX20">
+        <v>-0.25</v>
+      </c>
+      <c r="AY20">
+        <v>1.9</v>
+      </c>
+      <c r="AZ20">
+        <v>1.95</v>
+      </c>
+      <c r="BA20"/>
+      <c r="BB20"/>
+      <c r="BC20">
+        <v>1.9</v>
+      </c>
+      <c r="BD20">
+        <v>1.95</v>
+      </c>
+      <c r="BE20">
+        <v>1.85</v>
+      </c>
+      <c r="BF20">
         <v>1.87</v>
       </c>
-      <c r="BF17">
+      <c r="BG20">
+        <v>1.95</v>
+      </c>
+      <c r="BH20">
+        <v>2.0299999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D21" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G21">
+        <v>1.37</v>
+      </c>
+      <c r="H21">
+        <v>4.5</v>
+      </c>
+      <c r="I21">
+        <v>7.5</v>
+      </c>
+      <c r="J21">
+        <v>1.4</v>
+      </c>
+      <c r="K21">
+        <v>4.33</v>
+      </c>
+      <c r="L21">
+        <v>8</v>
+      </c>
+      <c r="M21">
+        <v>1.41</v>
+      </c>
+      <c r="N21">
+        <v>4.5</v>
+      </c>
+      <c r="O21">
+        <v>7</v>
+      </c>
+      <c r="P21">
+        <v>1.4</v>
+      </c>
+      <c r="Q21">
+        <v>4.5</v>
+      </c>
+      <c r="R21">
+        <v>8</v>
+      </c>
+      <c r="S21">
+        <v>1.42</v>
+      </c>
+      <c r="T21">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U21">
+        <v>6.75</v>
+      </c>
+      <c r="V21"/>
+      <c r="W21"/>
+      <c r="X21"/>
+      <c r="Y21"/>
+      <c r="Z21"/>
+      <c r="AA21"/>
+      <c r="AB21"/>
+      <c r="AC21"/>
+      <c r="AD21"/>
+      <c r="AE21">
+        <v>1.42</v>
+      </c>
+      <c r="AF21">
+        <v>5</v>
+      </c>
+      <c r="AG21">
+        <v>9</v>
+      </c>
+      <c r="AH21">
+        <v>1.39</v>
+      </c>
+      <c r="AI21">
+        <v>4.51</v>
+      </c>
+      <c r="AJ21">
+        <v>7.64</v>
+      </c>
+      <c r="AK21">
+        <v>1.43</v>
+      </c>
+      <c r="AL21">
+        <v>4.7</v>
+      </c>
+      <c r="AM21">
+        <v>10</v>
+      </c>
+      <c r="AN21">
+        <v>1.8</v>
+      </c>
+      <c r="AO21">
+        <v>2</v>
+      </c>
+      <c r="AP21"/>
+      <c r="AQ21"/>
+      <c r="AR21">
         <v>1.83</v>
       </c>
-      <c r="BG17"/>
-      <c r="BH17"/>
+      <c r="AS21">
+        <v>2.1</v>
+      </c>
+      <c r="AT21">
+        <v>1.75</v>
+      </c>
+      <c r="AU21">
+        <v>1.98</v>
+      </c>
+      <c r="AV21">
+        <v>1.86</v>
+      </c>
+      <c r="AW21">
+        <v>2.06</v>
+      </c>
+      <c r="AX21">
+        <v>-1.25</v>
+      </c>
+      <c r="AY21">
+        <v>1.95</v>
+      </c>
+      <c r="AZ21">
+        <v>1.9</v>
+      </c>
+      <c r="BA21"/>
+      <c r="BB21"/>
+      <c r="BC21">
+        <v>1.95</v>
+      </c>
+      <c r="BD21">
+        <v>1.9</v>
+      </c>
+      <c r="BE21">
+        <v>1.87</v>
+      </c>
+      <c r="BF21">
+        <v>1.85</v>
+      </c>
+      <c r="BG21">
+        <v>1.95</v>
+      </c>
+      <c r="BH21">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="G22">
+        <v>2.1</v>
+      </c>
+      <c r="H22">
+        <v>3.5</v>
+      </c>
+      <c r="I22">
+        <v>3.2</v>
+      </c>
+      <c r="J22">
+        <v>2.1</v>
+      </c>
+      <c r="K22">
+        <v>3.6</v>
+      </c>
+      <c r="L22">
+        <v>3.25</v>
+      </c>
+      <c r="M22">
+        <v>2.12</v>
+      </c>
+      <c r="N22">
+        <v>3.4</v>
+      </c>
+      <c r="O22">
+        <v>3.15</v>
+      </c>
+      <c r="P22">
+        <v>2.15</v>
+      </c>
+      <c r="Q22">
+        <v>3.5</v>
+      </c>
+      <c r="R22">
+        <v>3.2</v>
+      </c>
+      <c r="S22">
+        <v>2.1</v>
+      </c>
+      <c r="T22">
+        <v>3.6</v>
+      </c>
+      <c r="U22">
+        <v>3.1</v>
+      </c>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22">
+        <v>2.15</v>
+      </c>
+      <c r="AF22">
+        <v>3.6</v>
+      </c>
+      <c r="AG22">
+        <v>3.25</v>
+      </c>
+      <c r="AH22">
+        <v>2.1</v>
+      </c>
+      <c r="AI22">
+        <v>3.51</v>
+      </c>
+      <c r="AJ22">
+        <v>3.19</v>
+      </c>
+      <c r="AK22">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AL22">
+        <v>3.6</v>
+      </c>
+      <c r="AM22">
+        <v>3.3</v>
+      </c>
+      <c r="AN22">
+        <v>1.8</v>
+      </c>
+      <c r="AO22">
+        <v>2</v>
+      </c>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+      <c r="AR22">
+        <v>1.8</v>
+      </c>
+      <c r="AS22">
+        <v>2.1</v>
+      </c>
+      <c r="AT22">
+        <v>1.75</v>
+      </c>
+      <c r="AU22">
+        <v>1.99</v>
+      </c>
+      <c r="AV22">
+        <v>1.82</v>
+      </c>
+      <c r="AW22">
+        <v>2.12</v>
+      </c>
+      <c r="AX22">
+        <v>-0.25</v>
+      </c>
+      <c r="AY22">
+        <v>1.88</v>
+      </c>
+      <c r="AZ22">
+        <v>1.98</v>
+      </c>
+      <c r="BA22"/>
+      <c r="BB22"/>
+      <c r="BC22">
+        <v>1.88</v>
+      </c>
+      <c r="BD22">
+        <v>1.98</v>
+      </c>
+      <c r="BE22">
+        <v>1.8</v>
+      </c>
+      <c r="BF22">
+        <v>1.92</v>
+      </c>
+      <c r="BG22">
+        <v>1.94</v>
+      </c>
+      <c r="BH22">
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D23" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G23">
+        <v>1.71</v>
+      </c>
+      <c r="H23">
+        <v>3.6</v>
+      </c>
+      <c r="I23">
+        <v>4.5</v>
+      </c>
+      <c r="J23">
+        <v>1.8</v>
+      </c>
+      <c r="K23">
+        <v>3.6</v>
+      </c>
+      <c r="L23">
+        <v>4.5</v>
+      </c>
+      <c r="M23">
+        <v>1.77</v>
+      </c>
+      <c r="N23">
+        <v>3.65</v>
+      </c>
+      <c r="O23">
+        <v>4.2</v>
+      </c>
+      <c r="P23">
+        <v>1.8</v>
+      </c>
+      <c r="Q23">
+        <v>3.6</v>
+      </c>
+      <c r="R23">
+        <v>4.33</v>
+      </c>
+      <c r="S23">
+        <v>1.78</v>
+      </c>
+      <c r="T23">
+        <v>3.7</v>
+      </c>
+      <c r="U23">
+        <v>4.2</v>
+      </c>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23"/>
+      <c r="Z23"/>
+      <c r="AA23"/>
+      <c r="AB23"/>
+      <c r="AC23"/>
+      <c r="AD23"/>
+      <c r="AE23">
+        <v>1.81</v>
+      </c>
+      <c r="AF23">
+        <v>3.8</v>
+      </c>
+      <c r="AG23">
+        <v>4.5</v>
+      </c>
+      <c r="AH23">
+        <v>1.78</v>
+      </c>
+      <c r="AI23">
+        <v>3.6</v>
+      </c>
+      <c r="AJ23">
+        <v>4.3</v>
+      </c>
+      <c r="AK23">
+        <v>1.89</v>
+      </c>
+      <c r="AL23">
+        <v>3.8</v>
+      </c>
+      <c r="AM23">
+        <v>4.7</v>
+      </c>
+      <c r="AN23">
+        <v>1.95</v>
+      </c>
+      <c r="AO23">
+        <v>1.85</v>
+      </c>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+      <c r="AR23">
+        <v>2</v>
+      </c>
+      <c r="AS23">
+        <v>1.86</v>
+      </c>
+      <c r="AT23">
+        <v>1.92</v>
+      </c>
+      <c r="AU23">
+        <v>1.81</v>
+      </c>
+      <c r="AV23">
+        <v>2</v>
+      </c>
+      <c r="AW23">
+        <v>1.84</v>
+      </c>
+      <c r="AX23">
+        <v>-0.5</v>
+      </c>
+      <c r="AY23">
+        <v>1.78</v>
+      </c>
+      <c r="AZ23">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BA23"/>
+      <c r="BB23"/>
+      <c r="BC23">
+        <v>1.8</v>
+      </c>
+      <c r="BD23">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BE23">
+        <v>1.74</v>
+      </c>
+      <c r="BF23">
+        <v>1.97</v>
+      </c>
+      <c r="BG23">
+        <v>1.89</v>
+      </c>
+      <c r="BH23">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G24">
+        <v>1.42</v>
+      </c>
+      <c r="H24">
+        <v>4.33</v>
+      </c>
+      <c r="I24">
+        <v>7</v>
+      </c>
+      <c r="J24">
+        <v>1.44</v>
+      </c>
+      <c r="K24">
+        <v>4.33</v>
+      </c>
+      <c r="L24">
+        <v>7.5</v>
+      </c>
+      <c r="M24">
+        <v>1.43</v>
+      </c>
+      <c r="N24">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="O24">
+        <v>7</v>
+      </c>
+      <c r="P24">
+        <v>1.44</v>
+      </c>
+      <c r="Q24">
+        <v>4.33</v>
+      </c>
+      <c r="R24">
+        <v>7</v>
+      </c>
+      <c r="S24">
+        <v>1.49</v>
+      </c>
+      <c r="T24">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="U24">
+        <v>6</v>
+      </c>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
+      <c r="Y24"/>
+      <c r="Z24"/>
+      <c r="AA24"/>
+      <c r="AB24"/>
+      <c r="AC24"/>
+      <c r="AD24"/>
+      <c r="AE24">
+        <v>1.49</v>
+      </c>
+      <c r="AF24">
+        <v>4.75</v>
+      </c>
+      <c r="AG24">
+        <v>7.6</v>
+      </c>
+      <c r="AH24">
+        <v>1.43</v>
+      </c>
+      <c r="AI24">
+        <v>4.38</v>
+      </c>
+      <c r="AJ24">
+        <v>6.93</v>
+      </c>
+      <c r="AK24">
+        <v>1.48</v>
+      </c>
+      <c r="AL24">
+        <v>4.7</v>
+      </c>
+      <c r="AM24">
+        <v>8.4</v>
+      </c>
+      <c r="AN24">
+        <v>1.83</v>
+      </c>
+      <c r="AO24">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AP24"/>
+      <c r="AQ24"/>
+      <c r="AR24">
+        <v>1.83</v>
+      </c>
+      <c r="AS24">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AT24">
+        <v>1.77</v>
+      </c>
+      <c r="AU24">
+        <v>1.97</v>
+      </c>
+      <c r="AV24">
+        <v>1.82</v>
+      </c>
+      <c r="AW24">
+        <v>2.1</v>
+      </c>
+      <c r="AX24">
+        <v>-1.25</v>
+      </c>
+      <c r="AY24">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AZ24">
+        <v>1.8</v>
+      </c>
+      <c r="BA24"/>
+      <c r="BB24"/>
+      <c r="BC24">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BD24">
+        <v>1.8</v>
+      </c>
+      <c r="BE24">
+        <v>1.96</v>
+      </c>
+      <c r="BF24">
+        <v>1.77</v>
+      </c>
+      <c r="BG24">
+        <v>2.02</v>
+      </c>
+      <c r="BH24">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G25">
+        <v>1.61</v>
+      </c>
+      <c r="H25">
+        <v>4</v>
+      </c>
+      <c r="I25">
+        <v>4.75</v>
+      </c>
+      <c r="J25">
+        <v>1.62</v>
+      </c>
+      <c r="K25">
+        <v>4.2</v>
+      </c>
+      <c r="L25">
+        <v>5</v>
+      </c>
+      <c r="M25">
+        <v>1.61</v>
+      </c>
+      <c r="N25">
+        <v>4.2</v>
+      </c>
+      <c r="O25">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P25">
+        <v>1.65</v>
+      </c>
+      <c r="Q25">
+        <v>4.2</v>
+      </c>
+      <c r="R25">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S25">
+        <v>1.63</v>
+      </c>
+      <c r="T25">
+        <v>4.2</v>
+      </c>
+      <c r="U25">
+        <v>4.5</v>
+      </c>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+      <c r="Y25"/>
+      <c r="Z25"/>
+      <c r="AA25"/>
+      <c r="AB25"/>
+      <c r="AC25"/>
+      <c r="AD25"/>
+      <c r="AE25">
+        <v>1.65</v>
+      </c>
+      <c r="AF25">
+        <v>4.25</v>
+      </c>
+      <c r="AG25">
+        <v>5</v>
+      </c>
+      <c r="AH25">
+        <v>1.62</v>
+      </c>
+      <c r="AI25">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="AJ25">
+        <v>4.66</v>
+      </c>
+      <c r="AK25">
+        <v>1.69</v>
+      </c>
+      <c r="AL25">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AM25">
+        <v>4.8</v>
+      </c>
+      <c r="AN25">
+        <v>1.53</v>
+      </c>
+      <c r="AO25">
+        <v>2.4</v>
+      </c>
+      <c r="AP25"/>
+      <c r="AQ25"/>
+      <c r="AR25">
+        <v>1.53</v>
+      </c>
+      <c r="AS25">
+        <v>2.5</v>
+      </c>
+      <c r="AT25">
+        <v>1.49</v>
+      </c>
+      <c r="AU25">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="AV25">
+        <v>1.55</v>
+      </c>
+      <c r="AW25">
+        <v>2.48</v>
+      </c>
+      <c r="AX25">
+        <v>-0.75</v>
+      </c>
+      <c r="AY25">
+        <v>1.83</v>
+      </c>
+      <c r="AZ25">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BA25"/>
+      <c r="BB25"/>
+      <c r="BC25">
+        <v>1.83</v>
+      </c>
+      <c r="BD25">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BE25">
+        <v>1.77</v>
+      </c>
+      <c r="BF25">
+        <v>1.97</v>
+      </c>
+      <c r="BG25">
+        <v>1.85</v>
+      </c>
+      <c r="BH25">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" t="s">
+        <v>142</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="G26">
+        <v>2.25</v>
+      </c>
+      <c r="H26">
+        <v>3.5</v>
+      </c>
+      <c r="I26">
+        <v>2.82</v>
+      </c>
+      <c r="J26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K26">
+        <v>3.75</v>
+      </c>
+      <c r="L26">
+        <v>2.8</v>
+      </c>
+      <c r="M26">
+        <v>2.33</v>
+      </c>
+      <c r="N26">
+        <v>3.55</v>
+      </c>
+      <c r="O26">
+        <v>2.75</v>
+      </c>
+      <c r="P26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Q26">
+        <v>3.6</v>
+      </c>
+      <c r="R26">
+        <v>2.88</v>
+      </c>
+      <c r="S26">
+        <v>2.37</v>
+      </c>
+      <c r="T26">
+        <v>3.7</v>
+      </c>
+      <c r="U26">
+        <v>2.6</v>
+      </c>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+      <c r="Y26"/>
+      <c r="Z26"/>
+      <c r="AA26"/>
+      <c r="AB26"/>
+      <c r="AC26"/>
+      <c r="AD26"/>
+      <c r="AE26">
+        <v>2.37</v>
+      </c>
+      <c r="AF26">
+        <v>3.75</v>
+      </c>
+      <c r="AG26">
+        <v>2.88</v>
+      </c>
+      <c r="AH26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AI26">
+        <v>3.63</v>
+      </c>
+      <c r="AJ26">
+        <v>2.75</v>
+      </c>
+      <c r="AK26">
+        <v>2.4</v>
+      </c>
+      <c r="AL26">
+        <v>3.75</v>
+      </c>
+      <c r="AM26">
+        <v>2.94</v>
+      </c>
+      <c r="AN26">
+        <v>1.65</v>
+      </c>
+      <c r="AO26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AP26"/>
+      <c r="AQ26"/>
+      <c r="AR26">
+        <v>1.65</v>
+      </c>
+      <c r="AS26">
+        <v>2.4</v>
+      </c>
+      <c r="AT26">
+        <v>1.6</v>
+      </c>
+      <c r="AU26">
+        <v>2.21</v>
+      </c>
+      <c r="AV26">
+        <v>1.68</v>
+      </c>
+      <c r="AW26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AX26">
+        <v>-0.25</v>
+      </c>
+      <c r="AY26">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ26">
+        <v>1.83</v>
+      </c>
+      <c r="BA26"/>
+      <c r="BB26"/>
+      <c r="BC26">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD26">
+        <v>1.83</v>
+      </c>
+      <c r="BE26">
+        <v>1.98</v>
+      </c>
+      <c r="BF26">
+        <v>1.76</v>
+      </c>
+      <c r="BG26">
+        <v>2.08</v>
+      </c>
+      <c r="BH26">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27">
+        <v>3.3</v>
+      </c>
+      <c r="H27">
+        <v>3.1</v>
+      </c>
+      <c r="I27">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J27">
+        <v>3.25</v>
+      </c>
+      <c r="K27">
+        <v>3.1</v>
+      </c>
+      <c r="L27">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M27">
+        <v>3.05</v>
+      </c>
+      <c r="N27">
+        <v>3.05</v>
+      </c>
+      <c r="O27">
+        <v>2.35</v>
+      </c>
+      <c r="P27">
+        <v>3.4</v>
+      </c>
+      <c r="Q27">
+        <v>3.1</v>
+      </c>
+      <c r="R27">
+        <v>2.25</v>
+      </c>
+      <c r="S27">
+        <v>3.2</v>
+      </c>
+      <c r="T27">
+        <v>3.2</v>
+      </c>
+      <c r="U27">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+      <c r="Y27"/>
+      <c r="Z27"/>
+      <c r="AA27"/>
+      <c r="AB27"/>
+      <c r="AC27"/>
+      <c r="AD27"/>
+      <c r="AE27">
+        <v>3.6</v>
+      </c>
+      <c r="AF27">
+        <v>3.3</v>
+      </c>
+      <c r="AG27">
+        <v>2.35</v>
+      </c>
+      <c r="AH27">
+        <v>3.27</v>
+      </c>
+      <c r="AI27">
+        <v>3.09</v>
+      </c>
+      <c r="AJ27">
+        <v>2.25</v>
+      </c>
+      <c r="AK27">
+        <v>3.65</v>
+      </c>
+      <c r="AL27">
+        <v>3.15</v>
+      </c>
+      <c r="AM27">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AN27">
+        <v>2.4</v>
+      </c>
+      <c r="AO27">
+        <v>1.53</v>
+      </c>
+      <c r="AP27"/>
+      <c r="AQ27"/>
+      <c r="AR27">
+        <v>2.42</v>
+      </c>
+      <c r="AS27">
+        <v>1.57</v>
+      </c>
+      <c r="AT27">
+        <v>2.33</v>
+      </c>
+      <c r="AU27">
+        <v>1.55</v>
+      </c>
+      <c r="AV27">
+        <v>2.46</v>
+      </c>
+      <c r="AW27">
+        <v>1.6</v>
+      </c>
+      <c r="AX27">
+        <v>0.25</v>
+      </c>
+      <c r="AY27">
+        <v>1.93</v>
+      </c>
+      <c r="AZ27">
+        <v>1.93</v>
+      </c>
+      <c r="BA27"/>
+      <c r="BB27"/>
+      <c r="BC27">
+        <v>1.93</v>
+      </c>
+      <c r="BD27">
+        <v>1.93</v>
+      </c>
+      <c r="BE27">
+        <v>1.86</v>
+      </c>
+      <c r="BF27">
+        <v>1.86</v>
+      </c>
+      <c r="BG27">
+        <v>1.97</v>
+      </c>
+      <c r="BH27">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D28" t="s">
+        <v>141</v>
+      </c>
+      <c r="E28" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G28">
+        <v>2.15</v>
+      </c>
+      <c r="H28">
+        <v>3.4</v>
+      </c>
+      <c r="I28">
+        <v>3.1</v>
+      </c>
+      <c r="J28">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K28">
+        <v>3.5</v>
+      </c>
+      <c r="L28">
+        <v>3.1</v>
+      </c>
+      <c r="M28">
+        <v>2.08</v>
+      </c>
+      <c r="N28">
+        <v>3.4</v>
+      </c>
+      <c r="O28">
+        <v>3.3</v>
+      </c>
+      <c r="P28">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q28">
+        <v>3.5</v>
+      </c>
+      <c r="R28">
+        <v>3.1</v>
+      </c>
+      <c r="S28">
+        <v>2.15</v>
+      </c>
+      <c r="T28">
+        <v>3.5</v>
+      </c>
+      <c r="U28">
+        <v>3.1</v>
+      </c>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+      <c r="Y28"/>
+      <c r="Z28"/>
+      <c r="AA28"/>
+      <c r="AB28"/>
+      <c r="AC28"/>
+      <c r="AD28"/>
+      <c r="AE28">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AF28">
+        <v>3.7</v>
+      </c>
+      <c r="AG28">
+        <v>3.3</v>
+      </c>
+      <c r="AH28">
+        <v>2.15</v>
+      </c>
+      <c r="AI28">
+        <v>3.46</v>
+      </c>
+      <c r="AJ28">
+        <v>3.12</v>
+      </c>
+      <c r="AK28">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AL28">
+        <v>3.7</v>
+      </c>
+      <c r="AM28">
+        <v>3.1</v>
+      </c>
+      <c r="AN28">
+        <v>1.83</v>
+      </c>
+      <c r="AO28">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AP28"/>
+      <c r="AQ28"/>
+      <c r="AR28">
+        <v>1.83</v>
+      </c>
+      <c r="AS28">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AT28">
+        <v>1.78</v>
+      </c>
+      <c r="AU28">
+        <v>1.96</v>
+      </c>
+      <c r="AV28">
+        <v>1.79</v>
+      </c>
+      <c r="AW28">
+        <v>2.06</v>
+      </c>
+      <c r="AX28">
+        <v>-0.25</v>
+      </c>
+      <c r="AY28">
+        <v>1.95</v>
+      </c>
+      <c r="AZ28">
+        <v>1.9</v>
+      </c>
+      <c r="BA28"/>
+      <c r="BB28"/>
+      <c r="BC28">
+        <v>1.95</v>
+      </c>
+      <c r="BD28">
+        <v>1.9</v>
+      </c>
+      <c r="BE28">
+        <v>1.87</v>
+      </c>
+      <c r="BF28">
+        <v>1.85</v>
+      </c>
+      <c r="BG28">
+        <v>1.98</v>
+      </c>
+      <c r="BH28">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D29" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G29">
+        <v>3.4</v>
+      </c>
+      <c r="H29">
+        <v>3.2</v>
+      </c>
+      <c r="I29">
+        <v>2.1</v>
+      </c>
+      <c r="J29">
+        <v>3.3</v>
+      </c>
+      <c r="K29">
+        <v>3.4</v>
+      </c>
+      <c r="L29">
+        <v>2.15</v>
+      </c>
+      <c r="M29">
+        <v>3.2</v>
+      </c>
+      <c r="N29">
+        <v>3.3</v>
+      </c>
+      <c r="O29">
+        <v>2.08</v>
+      </c>
+      <c r="P29">
+        <v>3.4</v>
+      </c>
+      <c r="Q29">
+        <v>3.3</v>
+      </c>
+      <c r="R29">
+        <v>2.15</v>
+      </c>
+      <c r="S29">
+        <v>3.4</v>
+      </c>
+      <c r="T29">
+        <v>3.4</v>
+      </c>
+      <c r="U29">
+        <v>2.1</v>
+      </c>
+      <c r="V29"/>
+      <c r="W29"/>
+      <c r="X29"/>
+      <c r="Y29"/>
+      <c r="Z29"/>
+      <c r="AA29"/>
+      <c r="AB29"/>
+      <c r="AC29"/>
+      <c r="AD29"/>
+      <c r="AE29">
+        <v>3.4</v>
+      </c>
+      <c r="AF29">
+        <v>3.5</v>
+      </c>
+      <c r="AG29">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AH29">
+        <v>3.31</v>
+      </c>
+      <c r="AI29">
+        <v>3.31</v>
+      </c>
+      <c r="AJ29">
+        <v>2.12</v>
+      </c>
+      <c r="AK29">
+        <v>3.45</v>
+      </c>
+      <c r="AL29">
+        <v>3.5</v>
+      </c>
+      <c r="AM29">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AN29">
+        <v>2.08</v>
+      </c>
+      <c r="AO29">
+        <v>1.73</v>
+      </c>
+      <c r="AP29"/>
+      <c r="AQ29"/>
+      <c r="AR29">
+        <v>2.1</v>
+      </c>
+      <c r="AS29">
+        <v>1.83</v>
+      </c>
+      <c r="AT29">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="AU29">
+        <v>1.74</v>
+      </c>
+      <c r="AV29">
+        <v>2.1</v>
+      </c>
+      <c r="AW29">
+        <v>1.76</v>
+      </c>
+      <c r="AX29">
+        <v>0.25</v>
+      </c>
+      <c r="AY29">
+        <v>1.98</v>
+      </c>
+      <c r="AZ29">
+        <v>1.88</v>
+      </c>
+      <c r="BA29"/>
+      <c r="BB29"/>
+      <c r="BC29">
+        <v>1.98</v>
+      </c>
+      <c r="BD29">
+        <v>1.88</v>
+      </c>
+      <c r="BE29">
+        <v>1.91</v>
+      </c>
+      <c r="BF29">
+        <v>1.81</v>
+      </c>
+      <c r="BG29">
+        <v>2</v>
+      </c>
+      <c r="BH29">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D30" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G30">
+        <v>1.96</v>
+      </c>
+      <c r="H30">
+        <v>3.4</v>
+      </c>
+      <c r="I30">
+        <v>3.6</v>
+      </c>
+      <c r="J30">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K30">
+        <v>3.5</v>
+      </c>
+      <c r="L30">
+        <v>3.5</v>
+      </c>
+      <c r="M30">
+        <v>2.06</v>
+      </c>
+      <c r="N30">
+        <v>3.4</v>
+      </c>
+      <c r="O30">
+        <v>3.25</v>
+      </c>
+      <c r="P30">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="Q30">
+        <v>3.5</v>
+      </c>
+      <c r="R30">
+        <v>3.5</v>
+      </c>
+      <c r="S30">
+        <v>2.1</v>
+      </c>
+      <c r="T30">
+        <v>3.4</v>
+      </c>
+      <c r="U30">
+        <v>3.3</v>
+      </c>
+      <c r="V30"/>
+      <c r="W30"/>
+      <c r="X30"/>
+      <c r="Y30"/>
+      <c r="Z30"/>
+      <c r="AA30"/>
+      <c r="AB30"/>
+      <c r="AC30"/>
+      <c r="AD30"/>
+      <c r="AE30">
+        <v>2.1</v>
+      </c>
+      <c r="AF30">
+        <v>3.7</v>
+      </c>
+      <c r="AG30">
+        <v>3.6</v>
+      </c>
+      <c r="AH30">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AI30">
+        <v>3.43</v>
+      </c>
+      <c r="AJ30">
+        <v>3.4</v>
+      </c>
+      <c r="AK30">
+        <v>2.1</v>
+      </c>
+      <c r="AL30">
+        <v>3.7</v>
+      </c>
+      <c r="AM30">
+        <v>3.6</v>
+      </c>
+      <c r="AN30">
+        <v>1.88</v>
+      </c>
+      <c r="AO30">
+        <v>1.98</v>
+      </c>
+      <c r="AP30"/>
+      <c r="AQ30"/>
+      <c r="AR30">
+        <v>1.91</v>
+      </c>
+      <c r="AS30">
+        <v>1.98</v>
+      </c>
+      <c r="AT30">
+        <v>1.81</v>
+      </c>
+      <c r="AU30">
+        <v>1.9</v>
+      </c>
+      <c r="AV30">
+        <v>1.98</v>
+      </c>
+      <c r="AW30">
+        <v>1.99</v>
+      </c>
+      <c r="AX30">
+        <v>-0.25</v>
+      </c>
+      <c r="AY30">
+        <v>1.75</v>
+      </c>
+      <c r="AZ30">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BA30"/>
+      <c r="BB30"/>
+      <c r="BC30">
+        <v>1.8</v>
+      </c>
+      <c r="BD30">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BE30">
+        <v>1.74</v>
+      </c>
+      <c r="BF30">
+        <v>1.99</v>
+      </c>
+      <c r="BG30">
+        <v>1.84</v>
+      </c>
+      <c r="BH30">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D31" t="s">
+        <v>147</v>
+      </c>
+      <c r="E31" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="G31">
+        <v>2.15</v>
+      </c>
+      <c r="H31">
+        <v>3.25</v>
+      </c>
+      <c r="I31">
+        <v>3.25</v>
+      </c>
+      <c r="J31">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K31">
+        <v>3.3</v>
+      </c>
+      <c r="L31">
+        <v>3.25</v>
+      </c>
+      <c r="M31">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="N31">
+        <v>3.2</v>
+      </c>
+      <c r="O31">
+        <v>2.95</v>
+      </c>
+      <c r="P31">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q31">
+        <v>3.3</v>
+      </c>
+      <c r="R31">
+        <v>3.25</v>
+      </c>
+      <c r="S31">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T31">
+        <v>3.3</v>
+      </c>
+      <c r="U31">
+        <v>3.1</v>
+      </c>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+      <c r="Y31"/>
+      <c r="Z31"/>
+      <c r="AA31"/>
+      <c r="AB31"/>
+      <c r="AC31"/>
+      <c r="AD31"/>
+      <c r="AE31">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AF31">
+        <v>3.3</v>
+      </c>
+      <c r="AG31">
+        <v>3.33</v>
+      </c>
+      <c r="AH31">
+        <v>2.19</v>
+      </c>
+      <c r="AI31">
+        <v>3.25</v>
+      </c>
+      <c r="AJ31">
+        <v>3.2</v>
+      </c>
+      <c r="AK31">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AL31">
+        <v>3.3</v>
+      </c>
+      <c r="AM31">
+        <v>3.4</v>
+      </c>
+      <c r="AN31">
+        <v>2.08</v>
+      </c>
+      <c r="AO31">
+        <v>1.73</v>
+      </c>
+      <c r="AP31"/>
+      <c r="AQ31"/>
+      <c r="AR31">
+        <v>2.1</v>
+      </c>
+      <c r="AS31">
+        <v>1.8</v>
+      </c>
+      <c r="AT31">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="AU31">
+        <v>1.73</v>
+      </c>
+      <c r="AV31">
+        <v>2.1</v>
+      </c>
+      <c r="AW31">
+        <v>1.75</v>
+      </c>
+      <c r="AX31">
+        <v>-0.25</v>
+      </c>
+      <c r="AY31">
+        <v>1.9</v>
+      </c>
+      <c r="AZ31">
+        <v>1.95</v>
+      </c>
+      <c r="BA31"/>
+      <c r="BB31"/>
+      <c r="BC31">
+        <v>1.9</v>
+      </c>
+      <c r="BD31">
+        <v>1.95</v>
+      </c>
+      <c r="BE31">
+        <v>1.84</v>
+      </c>
+      <c r="BF31">
+        <v>1.88</v>
+      </c>
+      <c r="BG31">
+        <v>1.96</v>
+      </c>
+      <c r="BH31">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D32" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32">
+        <v>1.53</v>
+      </c>
+      <c r="H32">
+        <v>4</v>
+      </c>
+      <c r="I32">
+        <v>5.5</v>
+      </c>
+      <c r="J32">
+        <v>1.57</v>
+      </c>
+      <c r="K32">
+        <v>4.2</v>
+      </c>
+      <c r="L32">
+        <v>5.5</v>
+      </c>
+      <c r="M32">
+        <v>1.6</v>
+      </c>
+      <c r="N32">
+        <v>3.95</v>
+      </c>
+      <c r="O32">
+        <v>4.75</v>
+      </c>
+      <c r="P32">
+        <v>1.55</v>
+      </c>
+      <c r="Q32">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="R32">
+        <v>5.75</v>
+      </c>
+      <c r="S32">
+        <v>1.58</v>
+      </c>
+      <c r="T32">
+        <v>4.2</v>
+      </c>
+      <c r="U32">
+        <v>5</v>
+      </c>
+      <c r="V32"/>
+      <c r="W32"/>
+      <c r="X32"/>
+      <c r="Y32"/>
+      <c r="Z32"/>
+      <c r="AA32"/>
+      <c r="AB32"/>
+      <c r="AC32"/>
+      <c r="AD32"/>
+      <c r="AE32">
+        <v>1.6</v>
+      </c>
+      <c r="AF32">
+        <v>4.5</v>
+      </c>
+      <c r="AG32">
+        <v>5.75</v>
+      </c>
+      <c r="AH32">
+        <v>1.56</v>
+      </c>
+      <c r="AI32">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="AJ32">
+        <v>5.28</v>
+      </c>
+      <c r="AK32">
+        <v>1.59</v>
+      </c>
+      <c r="AL32">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AM32">
+        <v>5.9</v>
+      </c>
+      <c r="AN32">
+        <v>1.73</v>
+      </c>
+      <c r="AO32">
+        <v>2.08</v>
+      </c>
+      <c r="AP32"/>
+      <c r="AQ32"/>
+      <c r="AR32">
+        <v>1.73</v>
+      </c>
+      <c r="AS32">
+        <v>2.25</v>
+      </c>
+      <c r="AT32">
+        <v>1.68</v>
+      </c>
+      <c r="AU32">
+        <v>2.09</v>
+      </c>
+      <c r="AV32">
+        <v>1.74</v>
+      </c>
+      <c r="AW32">
+        <v>2.12</v>
+      </c>
+      <c r="AX32">
+        <v>-1</v>
+      </c>
+      <c r="AY32">
+        <v>1.98</v>
+      </c>
+      <c r="AZ32">
+        <v>1.88</v>
+      </c>
+      <c r="BA32"/>
+      <c r="BB32"/>
+      <c r="BC32">
+        <v>1.98</v>
+      </c>
+      <c r="BD32">
+        <v>1.88</v>
+      </c>
+      <c r="BE32">
+        <v>1.91</v>
+      </c>
+      <c r="BF32">
+        <v>1.81</v>
+      </c>
+      <c r="BG32">
+        <v>1.98</v>
+      </c>
+      <c r="BH32">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D33" t="s">
+        <v>153</v>
+      </c>
+      <c r="E33" t="s">
+        <v>158</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G33">
+        <v>2.7</v>
+      </c>
+      <c r="H33">
+        <v>3.2</v>
+      </c>
+      <c r="I33">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="J33">
+        <v>2.75</v>
+      </c>
+      <c r="K33">
+        <v>3.25</v>
+      </c>
+      <c r="L33">
+        <v>2.6</v>
+      </c>
+      <c r="M33">
+        <v>2.75</v>
+      </c>
+      <c r="N33">
+        <v>3.15</v>
+      </c>
+      <c r="O33">
+        <v>2.48</v>
+      </c>
+      <c r="P33">
+        <v>2.8</v>
+      </c>
+      <c r="Q33">
+        <v>3.2</v>
+      </c>
+      <c r="R33">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="S33">
+        <v>2.8</v>
+      </c>
+      <c r="T33">
+        <v>3.25</v>
+      </c>
+      <c r="U33">
+        <v>2.4</v>
+      </c>
+      <c r="V33"/>
+      <c r="W33"/>
+      <c r="X33"/>
+      <c r="Y33"/>
+      <c r="Z33"/>
+      <c r="AA33"/>
+      <c r="AB33"/>
+      <c r="AC33"/>
+      <c r="AD33"/>
+      <c r="AE33">
+        <v>2.8</v>
+      </c>
+      <c r="AF33">
+        <v>3.25</v>
+      </c>
+      <c r="AG33">
+        <v>2.66</v>
+      </c>
+      <c r="AH33">
+        <v>2.76</v>
+      </c>
+      <c r="AI33">
+        <v>3.15</v>
+      </c>
+      <c r="AJ33">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="AK33">
+        <v>2.82</v>
+      </c>
+      <c r="AL33">
+        <v>3.2</v>
+      </c>
+      <c r="AM33">
+        <v>2.72</v>
+      </c>
+      <c r="AN33">
+        <v>2.25</v>
+      </c>
+      <c r="AO33">
+        <v>1.62</v>
+      </c>
+      <c r="AP33"/>
+      <c r="AQ33"/>
+      <c r="AR33">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AS33">
+        <v>1.68</v>
+      </c>
+      <c r="AT33">
+        <v>2.19</v>
+      </c>
+      <c r="AU33">
+        <v>1.62</v>
+      </c>
+      <c r="AV33">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AW33">
+        <v>1.65</v>
+      </c>
+      <c r="AX33">
+        <v>0</v>
+      </c>
+      <c r="AY33">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ33">
+        <v>1.83</v>
+      </c>
+      <c r="BA33"/>
+      <c r="BB33"/>
+      <c r="BC33">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD33">
+        <v>1.83</v>
+      </c>
+      <c r="BE33">
+        <v>1.93</v>
+      </c>
+      <c r="BF33">
+        <v>1.79</v>
+      </c>
+      <c r="BG33">
+        <v>1.97</v>
+      </c>
+      <c r="BH33">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D34" t="s">
+        <v>155</v>
+      </c>
+      <c r="E34" t="s">
+        <v>148</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="G34">
+        <v>1.51</v>
+      </c>
+      <c r="H34">
+        <v>4</v>
+      </c>
+      <c r="I34">
+        <v>5.75</v>
+      </c>
+      <c r="J34">
+        <v>1.53</v>
+      </c>
+      <c r="K34">
+        <v>4.2</v>
+      </c>
+      <c r="L34">
+        <v>6</v>
+      </c>
+      <c r="M34">
+        <v>1.49</v>
+      </c>
+      <c r="N34">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O34">
+        <v>6</v>
+      </c>
+      <c r="P34">
+        <v>1.53</v>
+      </c>
+      <c r="Q34">
+        <v>4.2</v>
+      </c>
+      <c r="R34">
+        <v>5.75</v>
+      </c>
+      <c r="S34">
+        <v>1.55</v>
+      </c>
+      <c r="T34">
+        <v>4.33</v>
+      </c>
+      <c r="U34">
+        <v>5</v>
+      </c>
+      <c r="V34"/>
+      <c r="W34"/>
+      <c r="X34"/>
+      <c r="Y34"/>
+      <c r="Z34"/>
+      <c r="AA34"/>
+      <c r="AB34"/>
+      <c r="AC34"/>
+      <c r="AD34"/>
+      <c r="AE34">
+        <v>1.55</v>
+      </c>
+      <c r="AF34">
+        <v>5</v>
+      </c>
+      <c r="AG34">
+        <v>6</v>
+      </c>
+      <c r="AH34">
+        <v>1.51</v>
+      </c>
+      <c r="AI34">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="AJ34">
+        <v>5.7</v>
+      </c>
+      <c r="AK34">
+        <v>1.54</v>
+      </c>
+      <c r="AL34">
+        <v>4.5</v>
+      </c>
+      <c r="AM34">
+        <v>7</v>
+      </c>
+      <c r="AN34">
+        <v>1.73</v>
+      </c>
+      <c r="AO34">
+        <v>2.08</v>
+      </c>
+      <c r="AP34"/>
+      <c r="AQ34"/>
+      <c r="AR34">
+        <v>1.75</v>
+      </c>
+      <c r="AS34">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AT34">
+        <v>1.7</v>
+      </c>
+      <c r="AU34">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AV34">
+        <v>1.76</v>
+      </c>
+      <c r="AW34">
+        <v>2.12</v>
+      </c>
+      <c r="AX34">
+        <v>-1</v>
+      </c>
+      <c r="AY34">
+        <v>1.93</v>
+      </c>
+      <c r="AZ34">
+        <v>1.93</v>
+      </c>
+      <c r="BA34"/>
+      <c r="BB34"/>
+      <c r="BC34">
+        <v>1.93</v>
+      </c>
+      <c r="BD34">
+        <v>1.93</v>
+      </c>
+      <c r="BE34">
+        <v>1.87</v>
+      </c>
+      <c r="BF34">
+        <v>1.85</v>
+      </c>
+      <c r="BG34">
+        <v>1.87</v>
+      </c>
+      <c r="BH34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D35" t="s">
+        <v>157</v>
+      </c>
+      <c r="E35" t="s">
+        <v>152</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G35">
+        <v>1.37</v>
+      </c>
+      <c r="H35">
+        <v>4.5</v>
+      </c>
+      <c r="I35">
+        <v>7.5</v>
+      </c>
+      <c r="J35">
+        <v>1.4</v>
+      </c>
+      <c r="K35">
+        <v>4.5</v>
+      </c>
+      <c r="L35">
+        <v>7.5</v>
+      </c>
+      <c r="M35">
+        <v>1.44</v>
+      </c>
+      <c r="N35">
+        <v>4.3</v>
+      </c>
+      <c r="O35">
+        <v>6.25</v>
+      </c>
+      <c r="P35">
+        <v>1.4</v>
+      </c>
+      <c r="Q35">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="R35">
+        <v>7.5</v>
+      </c>
+      <c r="S35">
+        <v>1.43</v>
+      </c>
+      <c r="T35">
+        <v>4.75</v>
+      </c>
+      <c r="U35">
+        <v>6.25</v>
+      </c>
+      <c r="V35"/>
+      <c r="W35"/>
+      <c r="X35"/>
+      <c r="Y35"/>
+      <c r="Z35"/>
+      <c r="AA35"/>
+      <c r="AB35"/>
+      <c r="AC35"/>
+      <c r="AD35"/>
+      <c r="AE35">
+        <v>1.44</v>
+      </c>
+      <c r="AF35">
+        <v>5</v>
+      </c>
+      <c r="AG35">
+        <v>8</v>
+      </c>
+      <c r="AH35">
+        <v>1.4</v>
+      </c>
+      <c r="AI35">
+        <v>4.54</v>
+      </c>
+      <c r="AJ35">
+        <v>7.07</v>
+      </c>
+      <c r="AK35">
+        <v>1.42</v>
+      </c>
+      <c r="AL35">
+        <v>4.8</v>
+      </c>
+      <c r="AM35">
+        <v>8.4</v>
+      </c>
+      <c r="AN35">
+        <v>1.7</v>
+      </c>
+      <c r="AO35">
+        <v>2.1</v>
+      </c>
+      <c r="AP35"/>
+      <c r="AQ35"/>
+      <c r="AR35">
+        <v>1.71</v>
+      </c>
+      <c r="AS35">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AT35">
+        <v>1.65</v>
+      </c>
+      <c r="AU35">
+        <v>2.12</v>
+      </c>
+      <c r="AV35">
+        <v>1.72</v>
+      </c>
+      <c r="AW35">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AX35">
+        <v>-1.25</v>
+      </c>
+      <c r="AY35">
+        <v>1.93</v>
+      </c>
+      <c r="AZ35">
+        <v>1.93</v>
+      </c>
+      <c r="BA35"/>
+      <c r="BB35"/>
+      <c r="BC35">
+        <v>1.93</v>
+      </c>
+      <c r="BD35">
+        <v>1.93</v>
+      </c>
+      <c r="BE35">
+        <v>1.87</v>
+      </c>
+      <c r="BF35">
+        <v>1.85</v>
+      </c>
+      <c r="BG35">
+        <v>1.96</v>
+      </c>
+      <c r="BH35">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D36" t="s">
+        <v>165</v>
+      </c>
+      <c r="E36" t="s">
+        <v>156</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G36">
+        <v>2.4</v>
+      </c>
+      <c r="H36">
+        <v>3.4</v>
+      </c>
+      <c r="I36">
+        <v>2.7</v>
+      </c>
+      <c r="J36">
+        <v>2.5</v>
+      </c>
+      <c r="K36">
+        <v>3.4</v>
+      </c>
+      <c r="L36">
+        <v>2.75</v>
+      </c>
+      <c r="M36">
+        <v>2.6</v>
+      </c>
+      <c r="N36">
+        <v>3.3</v>
+      </c>
+      <c r="O36">
+        <v>2.5</v>
+      </c>
+      <c r="P36">
+        <v>2.4</v>
+      </c>
+      <c r="Q36">
+        <v>3.4</v>
+      </c>
+      <c r="R36">
+        <v>2.8</v>
+      </c>
+      <c r="S36">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="T36">
+        <v>3.4</v>
+      </c>
+      <c r="U36">
+        <v>2.65</v>
+      </c>
+      <c r="V36"/>
+      <c r="W36"/>
+      <c r="X36"/>
+      <c r="Y36"/>
+      <c r="Z36"/>
+      <c r="AA36"/>
+      <c r="AB36"/>
+      <c r="AC36"/>
+      <c r="AD36"/>
+      <c r="AE36">
+        <v>2.6</v>
+      </c>
+      <c r="AF36">
+        <v>3.6</v>
+      </c>
+      <c r="AG36">
+        <v>2.8</v>
+      </c>
+      <c r="AH36">
+        <v>2.46</v>
+      </c>
+      <c r="AI36">
+        <v>3.36</v>
+      </c>
+      <c r="AJ36">
+        <v>2.69</v>
+      </c>
+      <c r="AK36">
+        <v>2.52</v>
+      </c>
+      <c r="AL36">
+        <v>3.5</v>
+      </c>
+      <c r="AM36">
+        <v>2.98</v>
+      </c>
+      <c r="AN36">
+        <v>1.9</v>
+      </c>
+      <c r="AO36">
+        <v>1.95</v>
+      </c>
+      <c r="AP36"/>
+      <c r="AQ36"/>
+      <c r="AR36">
+        <v>1.91</v>
+      </c>
+      <c r="AS36">
+        <v>1.95</v>
+      </c>
+      <c r="AT36">
+        <v>1.84</v>
+      </c>
+      <c r="AU36">
+        <v>1.88</v>
+      </c>
+      <c r="AV36">
+        <v>2</v>
+      </c>
+      <c r="AW36">
+        <v>1.92</v>
+      </c>
+      <c r="AX36">
+        <v>0</v>
+      </c>
+      <c r="AY36">
+        <v>1.8</v>
+      </c>
+      <c r="AZ36">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BA36"/>
+      <c r="BB36"/>
+      <c r="BC36">
+        <v>1.8</v>
+      </c>
+      <c r="BD36">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BE36">
+        <v>1.75</v>
+      </c>
+      <c r="BF36">
+        <v>1.99</v>
+      </c>
+      <c r="BG36">
+        <v>1.81</v>
+      </c>
+      <c r="BH36">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D37" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" t="s">
+        <v>166</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37">
+        <v>2.15</v>
+      </c>
+      <c r="H37">
+        <v>3.3</v>
+      </c>
+      <c r="I37">
+        <v>3.2</v>
+      </c>
+      <c r="J37">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K37">
+        <v>3.4</v>
+      </c>
+      <c r="L37">
+        <v>3.2</v>
+      </c>
+      <c r="M37">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="N37">
+        <v>3.4</v>
+      </c>
+      <c r="O37">
+        <v>2.95</v>
+      </c>
+      <c r="P37">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q37">
+        <v>3.4</v>
+      </c>
+      <c r="R37">
+        <v>3.13</v>
+      </c>
+      <c r="S37">
+        <v>2.25</v>
+      </c>
+      <c r="T37">
+        <v>3.4</v>
+      </c>
+      <c r="U37">
+        <v>3</v>
+      </c>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+      <c r="Y37"/>
+      <c r="Z37"/>
+      <c r="AA37"/>
+      <c r="AB37"/>
+      <c r="AC37"/>
+      <c r="AD37"/>
+      <c r="AE37">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AF37">
+        <v>3.4</v>
+      </c>
+      <c r="AG37">
+        <v>3.2</v>
+      </c>
+      <c r="AH37">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AI37">
+        <v>3.36</v>
+      </c>
+      <c r="AJ37">
+        <v>3.09</v>
+      </c>
+      <c r="AK37">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="AL37">
+        <v>3.35</v>
+      </c>
+      <c r="AM37">
+        <v>3.3</v>
+      </c>
+      <c r="AN37">
+        <v>2</v>
+      </c>
+      <c r="AO37">
+        <v>1.85</v>
+      </c>
+      <c r="AP37"/>
+      <c r="AQ37"/>
+      <c r="AR37">
+        <v>2</v>
+      </c>
+      <c r="AS37">
+        <v>1.92</v>
+      </c>
+      <c r="AT37">
+        <v>1.91</v>
+      </c>
+      <c r="AU37">
+        <v>1.82</v>
+      </c>
+      <c r="AV37">
+        <v>1.99</v>
+      </c>
+      <c r="AW37">
+        <v>1.98</v>
+      </c>
+      <c r="AX37">
+        <v>-0.25</v>
+      </c>
+      <c r="AY37">
+        <v>1.93</v>
+      </c>
+      <c r="AZ37">
+        <v>1.93</v>
+      </c>
+      <c r="BA37"/>
+      <c r="BB37"/>
+      <c r="BC37">
+        <v>1.93</v>
+      </c>
+      <c r="BD37">
+        <v>1.93</v>
+      </c>
+      <c r="BE37">
+        <v>1.87</v>
+      </c>
+      <c r="BF37">
+        <v>1.85</v>
+      </c>
+      <c r="BG37">
+        <v>2</v>
+      </c>
+      <c r="BH37">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E38" t="s">
+        <v>154</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G38">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H38">
+        <v>3.2</v>
+      </c>
+      <c r="I38">
+        <v>3.2</v>
+      </c>
+      <c r="J38">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K38">
+        <v>3.25</v>
+      </c>
+      <c r="L38">
+        <v>3.1</v>
+      </c>
+      <c r="M38">
+        <v>2.08</v>
+      </c>
+      <c r="N38">
+        <v>3.25</v>
+      </c>
+      <c r="O38">
+        <v>3.35</v>
+      </c>
+      <c r="P38">
+        <v>2.25</v>
+      </c>
+      <c r="Q38">
+        <v>3.2</v>
+      </c>
+      <c r="R38">
+        <v>3.2</v>
+      </c>
+      <c r="S38">
+        <v>2.25</v>
+      </c>
+      <c r="T38">
+        <v>3.3</v>
+      </c>
+      <c r="U38">
+        <v>3.1</v>
+      </c>
+      <c r="V38"/>
+      <c r="W38"/>
+      <c r="X38"/>
+      <c r="Y38"/>
+      <c r="Z38"/>
+      <c r="AA38"/>
+      <c r="AB38"/>
+      <c r="AC38"/>
+      <c r="AD38"/>
+      <c r="AE38">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AF38">
+        <v>3.4</v>
+      </c>
+      <c r="AG38">
+        <v>3.35</v>
+      </c>
+      <c r="AH38">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AI38">
+        <v>3.26</v>
+      </c>
+      <c r="AJ38">
+        <v>3.15</v>
+      </c>
+      <c r="AK38">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="AL38">
+        <v>3.35</v>
+      </c>
+      <c r="AM38">
+        <v>3.25</v>
+      </c>
+      <c r="AN38">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AO38">
+        <v>1.65</v>
+      </c>
+      <c r="AP38"/>
+      <c r="AQ38"/>
+      <c r="AR38">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AS38">
+        <v>1.68</v>
+      </c>
+      <c r="AT38">
+        <v>2.14</v>
+      </c>
+      <c r="AU38">
+        <v>1.64</v>
+      </c>
+      <c r="AV38">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="AW38">
+        <v>1.7</v>
+      </c>
+      <c r="AX38">
+        <v>-0.25</v>
+      </c>
+      <c r="AY38">
+        <v>1.98</v>
+      </c>
+      <c r="AZ38">
+        <v>1.88</v>
+      </c>
+      <c r="BA38"/>
+      <c r="BB38"/>
+      <c r="BC38">
+        <v>1.98</v>
+      </c>
+      <c r="BD38">
+        <v>1.88</v>
+      </c>
+      <c r="BE38">
+        <v>1.91</v>
+      </c>
+      <c r="BF38">
+        <v>1.81</v>
+      </c>
+      <c r="BG38">
+        <v>1.99</v>
+      </c>
+      <c r="BH38">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D39" t="s">
+        <v>163</v>
+      </c>
+      <c r="E39" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G39">
+        <v>1.66</v>
+      </c>
+      <c r="H39">
+        <v>3.6</v>
+      </c>
+      <c r="I39">
+        <v>4.75</v>
+      </c>
+      <c r="J39">
+        <v>1.73</v>
+      </c>
+      <c r="K39">
+        <v>3.6</v>
+      </c>
+      <c r="L39">
+        <v>5</v>
+      </c>
+      <c r="M39">
+        <v>1.72</v>
+      </c>
+      <c r="N39">
+        <v>3.5</v>
+      </c>
+      <c r="O39">
+        <v>4.5</v>
+      </c>
+      <c r="P39">
+        <v>1.7</v>
+      </c>
+      <c r="Q39">
+        <v>3.6</v>
+      </c>
+      <c r="R39">
+        <v>5</v>
+      </c>
+      <c r="S39">
+        <v>1.72</v>
+      </c>
+      <c r="T39">
+        <v>3.5</v>
+      </c>
+      <c r="U39">
+        <v>4.8</v>
+      </c>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+      <c r="Y39"/>
+      <c r="Z39"/>
+      <c r="AA39"/>
+      <c r="AB39"/>
+      <c r="AC39"/>
+      <c r="AD39"/>
+      <c r="AE39">
+        <v>1.75</v>
+      </c>
+      <c r="AF39">
+        <v>3.75</v>
+      </c>
+      <c r="AG39">
+        <v>5</v>
+      </c>
+      <c r="AH39">
+        <v>1.71</v>
+      </c>
+      <c r="AI39">
+        <v>3.53</v>
+      </c>
+      <c r="AJ39">
+        <v>4.83</v>
+      </c>
+      <c r="AK39">
+        <v>1.78</v>
+      </c>
+      <c r="AL39">
+        <v>3.8</v>
+      </c>
+      <c r="AM39">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AN39">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AO39">
+        <v>1.75</v>
+      </c>
+      <c r="AP39"/>
+      <c r="AQ39"/>
+      <c r="AR39">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AS39">
+        <v>1.8</v>
+      </c>
+      <c r="AT39">
+        <v>1.99</v>
+      </c>
+      <c r="AU39">
+        <v>1.74</v>
+      </c>
+      <c r="AV39">
+        <v>2.04</v>
+      </c>
+      <c r="AW39">
+        <v>1.8</v>
+      </c>
+      <c r="AX39">
+        <v>-0.75</v>
+      </c>
+      <c r="AY39">
+        <v>1.95</v>
+      </c>
+      <c r="AZ39">
+        <v>1.9</v>
+      </c>
+      <c r="BA39"/>
+      <c r="BB39"/>
+      <c r="BC39">
+        <v>1.95</v>
+      </c>
+      <c r="BD39">
+        <v>1.9</v>
+      </c>
+      <c r="BE39">
+        <v>1.9</v>
+      </c>
+      <c r="BF39">
+        <v>1.82</v>
+      </c>
+      <c r="BG39">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="BH39">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D40" t="s">
+        <v>203</v>
+      </c>
+      <c r="E40" t="s">
+        <v>223</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G40">
+        <v>2.1</v>
+      </c>
+      <c r="H40">
+        <v>3.6</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>2.1</v>
+      </c>
+      <c r="K40">
+        <v>3.75</v>
+      </c>
+      <c r="L40">
+        <v>2.88</v>
+      </c>
+      <c r="M40">
+        <v>2</v>
+      </c>
+      <c r="N40">
+        <v>3.7</v>
+      </c>
+      <c r="O40">
+        <v>3.05</v>
+      </c>
+      <c r="P40">
+        <v>2.1</v>
+      </c>
+      <c r="Q40">
+        <v>3.7</v>
+      </c>
+      <c r="R40">
+        <v>2.9</v>
+      </c>
+      <c r="S40">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="T40">
+        <v>3.6</v>
+      </c>
+      <c r="U40">
+        <v>2.8</v>
+      </c>
+      <c r="V40"/>
+      <c r="W40"/>
+      <c r="X40"/>
+      <c r="Y40"/>
+      <c r="Z40"/>
+      <c r="AA40"/>
+      <c r="AB40"/>
+      <c r="AC40"/>
+      <c r="AD40"/>
+      <c r="AE40">
+        <v>2.12</v>
+      </c>
+      <c r="AF40">
+        <v>3.75</v>
+      </c>
+      <c r="AG40">
+        <v>3.05</v>
+      </c>
+      <c r="AH40">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="AI40">
+        <v>3.64</v>
+      </c>
+      <c r="AJ40">
+        <v>2.94</v>
+      </c>
+      <c r="AK40">
+        <v>2.1</v>
+      </c>
+      <c r="AL40">
+        <v>2.72</v>
+      </c>
+      <c r="AM40">
+        <v>2.78</v>
+      </c>
+      <c r="AN40">
+        <v>1.53</v>
+      </c>
+      <c r="AO40">
+        <v>2.4</v>
+      </c>
+      <c r="AP40"/>
+      <c r="AQ40"/>
+      <c r="AR40">
+        <v>1.53</v>
+      </c>
+      <c r="AS40">
+        <v>2.63</v>
+      </c>
+      <c r="AT40">
+        <v>1.48</v>
+      </c>
+      <c r="AU40">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="AV40">
+        <v>1.47</v>
+      </c>
+      <c r="AW40">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AX40">
+        <v>-0.25</v>
+      </c>
+      <c r="AY40">
+        <v>1.85</v>
+      </c>
+      <c r="AZ40">
+        <v>1.95</v>
+      </c>
+      <c r="BA40"/>
+      <c r="BB40"/>
+      <c r="BC40">
+        <v>1.85</v>
+      </c>
+      <c r="BD40">
+        <v>1.95</v>
+      </c>
+      <c r="BE40">
+        <v>1.82</v>
+      </c>
+      <c r="BF40">
+        <v>1.87</v>
+      </c>
+      <c r="BG40">
+        <v>1.85</v>
+      </c>
+      <c r="BH40">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C41" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
+        <v>209</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G41">
+        <v>2.6</v>
+      </c>
+      <c r="H41">
+        <v>3.5</v>
+      </c>
+      <c r="I41">
+        <v>2.38</v>
+      </c>
+      <c r="J41">
+        <v>2.6</v>
+      </c>
+      <c r="K41">
+        <v>3.5</v>
+      </c>
+      <c r="L41">
+        <v>2.4</v>
+      </c>
+      <c r="M41">
+        <v>2.63</v>
+      </c>
+      <c r="N41">
+        <v>3.5</v>
+      </c>
+      <c r="O41">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="P41">
+        <v>2.63</v>
+      </c>
+      <c r="Q41">
+        <v>3.4</v>
+      </c>
+      <c r="R41">
+        <v>2.38</v>
+      </c>
+      <c r="S41">
+        <v>2.5</v>
+      </c>
+      <c r="T41">
+        <v>3.4</v>
+      </c>
+      <c r="U41">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+      <c r="Y41"/>
+      <c r="Z41"/>
+      <c r="AA41"/>
+      <c r="AB41"/>
+      <c r="AC41"/>
+      <c r="AD41"/>
+      <c r="AE41">
+        <v>2.75</v>
+      </c>
+      <c r="AF41">
+        <v>3.6</v>
+      </c>
+      <c r="AG41">
+        <v>2.5</v>
+      </c>
+      <c r="AH41">
+        <v>2.6</v>
+      </c>
+      <c r="AI41">
+        <v>3.45</v>
+      </c>
+      <c r="AJ41">
+        <v>2.36</v>
+      </c>
+      <c r="AK41">
+        <v>2.78</v>
+      </c>
+      <c r="AL41">
+        <v>3.55</v>
+      </c>
+      <c r="AM41">
+        <v>2.38</v>
+      </c>
+      <c r="AN41">
+        <v>1.7</v>
+      </c>
+      <c r="AO41">
+        <v>2.1</v>
+      </c>
+      <c r="AP41"/>
+      <c r="AQ41"/>
+      <c r="AR41">
+        <v>1.7</v>
+      </c>
+      <c r="AS41">
+        <v>2.4</v>
+      </c>
+      <c r="AT41">
+        <v>1.65</v>
+      </c>
+      <c r="AU41">
+        <v>2.13</v>
+      </c>
+      <c r="AV41">
+        <v>1.68</v>
+      </c>
+      <c r="AW41">
+        <v>1.98</v>
+      </c>
+      <c r="AX41">
+        <v>0</v>
+      </c>
+      <c r="AY41">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ41">
+        <v>1.78</v>
+      </c>
+      <c r="BA41"/>
+      <c r="BB41"/>
+      <c r="BC41">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD41">
+        <v>1.78</v>
+      </c>
+      <c r="BE41">
+        <v>1.97</v>
+      </c>
+      <c r="BF41">
+        <v>1.73</v>
+      </c>
+      <c r="BG41">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BH41">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C42" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D42" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" t="s">
+        <v>216</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="G42">
+        <v>1.55</v>
+      </c>
+      <c r="H42">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I42">
+        <v>4.75</v>
+      </c>
+      <c r="J42">
+        <v>1.53</v>
+      </c>
+      <c r="K42">
+        <v>4.33</v>
+      </c>
+      <c r="L42">
+        <v>5</v>
+      </c>
+      <c r="M42">
+        <v>1.52</v>
+      </c>
+      <c r="N42">
+        <v>4.2</v>
+      </c>
+      <c r="O42">
+        <v>5</v>
+      </c>
+      <c r="P42">
+        <v>1.55</v>
+      </c>
+      <c r="Q42">
+        <v>4.2</v>
+      </c>
+      <c r="R42">
+        <v>4.75</v>
+      </c>
+      <c r="S42">
+        <v>1.55</v>
+      </c>
+      <c r="T42">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="U42">
+        <v>4.33</v>
+      </c>
+      <c r="V42"/>
+      <c r="W42"/>
+      <c r="X42"/>
+      <c r="Y42"/>
+      <c r="Z42"/>
+      <c r="AA42"/>
+      <c r="AB42"/>
+      <c r="AC42"/>
+      <c r="AD42"/>
+      <c r="AE42">
+        <v>1.6</v>
+      </c>
+      <c r="AF42">
+        <v>4.5</v>
+      </c>
+      <c r="AG42">
+        <v>5</v>
+      </c>
+      <c r="AH42">
+        <v>1.54</v>
+      </c>
+      <c r="AI42">
+        <v>4.24</v>
+      </c>
+      <c r="AJ42">
+        <v>4.7</v>
+      </c>
+      <c r="AK42">
+        <v>1.6</v>
+      </c>
+      <c r="AL42">
+        <v>4.5</v>
+      </c>
+      <c r="AM42">
+        <v>5.3</v>
+      </c>
+      <c r="AN42">
+        <v>1.48</v>
+      </c>
+      <c r="AO42">
+        <v>2.6</v>
+      </c>
+      <c r="AP42"/>
+      <c r="AQ42"/>
+      <c r="AR42">
+        <v>1.48</v>
+      </c>
+      <c r="AS42">
+        <v>2.8</v>
+      </c>
+      <c r="AT42">
+        <v>1.44</v>
+      </c>
+      <c r="AU42">
+        <v>2.61</v>
+      </c>
+      <c r="AV42">
+        <v>1.4</v>
+      </c>
+      <c r="AW42">
+        <v>2.76</v>
+      </c>
+      <c r="AX42">
+        <v>-1</v>
+      </c>
+      <c r="AY42">
+        <v>1.95</v>
+      </c>
+      <c r="AZ42">
+        <v>1.85</v>
+      </c>
+      <c r="BA42"/>
+      <c r="BB42"/>
+      <c r="BC42">
+        <v>1.95</v>
+      </c>
+      <c r="BD42">
+        <v>1.85</v>
+      </c>
+      <c r="BE42">
+        <v>1.88</v>
+      </c>
+      <c r="BF42">
+        <v>1.81</v>
+      </c>
+      <c r="BG42">
+        <v>1.94</v>
+      </c>
+      <c r="BH42">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C43" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D43" t="s">
+        <v>242</v>
+      </c>
+      <c r="E43" t="s">
+        <v>222</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G43">
+        <v>5.5</v>
+      </c>
+      <c r="H43">
+        <v>4.2</v>
+      </c>
+      <c r="I43">
+        <v>1.48</v>
+      </c>
+      <c r="J43">
+        <v>5.5</v>
+      </c>
+      <c r="K43">
+        <v>4.5</v>
+      </c>
+      <c r="L43">
+        <v>1.44</v>
+      </c>
+      <c r="M43">
+        <v>5.2</v>
+      </c>
+      <c r="N43">
+        <v>4.2</v>
+      </c>
+      <c r="O43">
+        <v>1.5</v>
+      </c>
+      <c r="P43">
+        <v>5.25</v>
+      </c>
+      <c r="Q43">
+        <v>4.33</v>
+      </c>
+      <c r="R43">
+        <v>1.5</v>
+      </c>
+      <c r="S43">
+        <v>5</v>
+      </c>
+      <c r="T43">
+        <v>4.2</v>
+      </c>
+      <c r="U43">
+        <v>1.47</v>
+      </c>
+      <c r="V43"/>
+      <c r="W43"/>
+      <c r="X43"/>
+      <c r="Y43"/>
+      <c r="Z43"/>
+      <c r="AA43"/>
+      <c r="AB43"/>
+      <c r="AC43"/>
+      <c r="AD43"/>
+      <c r="AE43">
+        <v>6.25</v>
+      </c>
+      <c r="AF43">
+        <v>4.5</v>
+      </c>
+      <c r="AG43">
+        <v>1.5</v>
+      </c>
+      <c r="AH43">
+        <v>5.4</v>
+      </c>
+      <c r="AI43">
+        <v>4.3</v>
+      </c>
+      <c r="AJ43">
+        <v>1.47</v>
+      </c>
+      <c r="AK43">
+        <v>6</v>
+      </c>
+      <c r="AL43">
+        <v>4.8</v>
+      </c>
+      <c r="AM43">
+        <v>1.5</v>
+      </c>
+      <c r="AN43">
+        <v>1.48</v>
+      </c>
+      <c r="AO43">
+        <v>2.6</v>
+      </c>
+      <c r="AP43"/>
+      <c r="AQ43"/>
+      <c r="AR43">
+        <v>1.5</v>
+      </c>
+      <c r="AS43">
+        <v>2.7</v>
+      </c>
+      <c r="AT43">
+        <v>1.46</v>
+      </c>
+      <c r="AU43">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AV43">
+        <v>1.5</v>
+      </c>
+      <c r="AW43">
+        <v>2.72</v>
+      </c>
+      <c r="AX43">
+        <v>1</v>
+      </c>
+      <c r="AY43">
+        <v>2</v>
+      </c>
+      <c r="AZ43">
+        <v>1.8</v>
+      </c>
+      <c r="BA43"/>
+      <c r="BB43"/>
+      <c r="BC43">
+        <v>2</v>
+      </c>
+      <c r="BD43">
+        <v>1.8</v>
+      </c>
+      <c r="BE43">
+        <v>1.95</v>
+      </c>
+      <c r="BF43">
+        <v>1.75</v>
+      </c>
+      <c r="BG43">
+        <v>2.09</v>
+      </c>
+      <c r="BH43">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C44" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D44" t="s">
+        <v>219</v>
+      </c>
+      <c r="E44" t="s">
+        <v>210</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G44">
+        <v>1.5</v>
+      </c>
+      <c r="H44">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I44">
+        <v>5.25</v>
+      </c>
+      <c r="J44">
+        <v>1.5</v>
+      </c>
+      <c r="K44">
+        <v>4.33</v>
+      </c>
+      <c r="L44">
+        <v>5</v>
+      </c>
+      <c r="M44">
+        <v>1.37</v>
+      </c>
+      <c r="N44">
+        <v>4.8</v>
+      </c>
+      <c r="O44">
+        <v>6.25</v>
+      </c>
+      <c r="P44">
+        <v>1.5</v>
+      </c>
+      <c r="Q44">
+        <v>4.33</v>
+      </c>
+      <c r="R44">
+        <v>5</v>
+      </c>
+      <c r="S44">
+        <v>1.5</v>
+      </c>
+      <c r="T44">
+        <v>4.2</v>
+      </c>
+      <c r="U44">
+        <v>4.75</v>
+      </c>
+      <c r="V44"/>
+      <c r="W44"/>
+      <c r="X44"/>
+      <c r="Y44"/>
+      <c r="Z44"/>
+      <c r="AA44"/>
+      <c r="AB44"/>
+      <c r="AC44"/>
+      <c r="AD44"/>
+      <c r="AE44">
+        <v>1.55</v>
+      </c>
+      <c r="AF44">
+        <v>4.8</v>
+      </c>
+      <c r="AG44">
+        <v>6.25</v>
+      </c>
+      <c r="AH44">
+        <v>1.48</v>
+      </c>
+      <c r="AI44">
+        <v>4.38</v>
+      </c>
+      <c r="AJ44">
+        <v>5.19</v>
+      </c>
+      <c r="AK44">
+        <v>1.53</v>
+      </c>
+      <c r="AL44">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AM44">
+        <v>5.4</v>
+      </c>
+      <c r="AN44">
+        <v>1.48</v>
+      </c>
+      <c r="AO44">
+        <v>2.6</v>
+      </c>
+      <c r="AP44"/>
+      <c r="AQ44"/>
+      <c r="AR44">
+        <v>1.5</v>
+      </c>
+      <c r="AS44">
+        <v>3</v>
+      </c>
+      <c r="AT44">
+        <v>1.44</v>
+      </c>
+      <c r="AU44">
+        <v>2.62</v>
+      </c>
+      <c r="AV44">
+        <v>1.21</v>
+      </c>
+      <c r="AW44">
+        <v>2.54</v>
+      </c>
+      <c r="AX44">
+        <v>-1</v>
+      </c>
+      <c r="AY44">
+        <v>1.85</v>
+      </c>
+      <c r="AZ44">
+        <v>1.95</v>
+      </c>
+      <c r="BA44"/>
+      <c r="BB44"/>
+      <c r="BC44">
+        <v>1.85</v>
+      </c>
+      <c r="BD44">
+        <v>1.95</v>
+      </c>
+      <c r="BE44">
+        <v>1.81</v>
+      </c>
+      <c r="BF44">
+        <v>1.88</v>
+      </c>
+      <c r="BG44">
+        <v>1.84</v>
+      </c>
+      <c r="BH44">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C45" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D45" t="s">
+        <v>213</v>
+      </c>
+      <c r="E45" t="s">
+        <v>206</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G45">
+        <v>1.36</v>
+      </c>
+      <c r="H45">
+        <v>4.75</v>
+      </c>
+      <c r="I45">
+        <v>7</v>
+      </c>
+      <c r="J45">
+        <v>1.33</v>
+      </c>
+      <c r="K45">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L45">
+        <v>8</v>
+      </c>
+      <c r="M45">
+        <v>1.4</v>
+      </c>
+      <c r="N45">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="O45">
+        <v>6.5</v>
+      </c>
+      <c r="P45">
+        <v>1.33</v>
+      </c>
+      <c r="Q45">
+        <v>4.75</v>
+      </c>
+      <c r="R45">
+        <v>7.5</v>
+      </c>
+      <c r="S45">
+        <v>1.35</v>
+      </c>
+      <c r="T45">
+        <v>4.5</v>
+      </c>
+      <c r="U45">
+        <v>6.5</v>
+      </c>
+      <c r="V45"/>
+      <c r="W45"/>
+      <c r="X45"/>
+      <c r="Y45"/>
+      <c r="Z45"/>
+      <c r="AA45"/>
+      <c r="AB45"/>
+      <c r="AC45"/>
+      <c r="AD45"/>
+      <c r="AE45">
+        <v>1.4</v>
+      </c>
+      <c r="AF45">
+        <v>4.75</v>
+      </c>
+      <c r="AG45">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AH45">
+        <v>1.35</v>
+      </c>
+      <c r="AI45">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AJ45">
+        <v>7.1</v>
+      </c>
+      <c r="AK45">
+        <v>1.35</v>
+      </c>
+      <c r="AL45">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AM45">
+        <v>8.6</v>
+      </c>
+      <c r="AN45">
+        <v>1.57</v>
+      </c>
+      <c r="AO45">
+        <v>2.35</v>
+      </c>
+      <c r="AP45"/>
+      <c r="AQ45"/>
+      <c r="AR45">
+        <v>1.57</v>
+      </c>
+      <c r="AS45">
+        <v>2.4</v>
+      </c>
+      <c r="AT45">
+        <v>1.55</v>
+      </c>
+      <c r="AU45">
+        <v>2.29</v>
+      </c>
+      <c r="AV45">
+        <v>1.5</v>
+      </c>
+      <c r="AW45">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="AX45">
+        <v>-1.5</v>
+      </c>
+      <c r="AY45">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ45">
+        <v>1.78</v>
+      </c>
+      <c r="BA45"/>
+      <c r="BB45"/>
+      <c r="BC45">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD45">
+        <v>1.78</v>
+      </c>
+      <c r="BE45">
+        <v>1.98</v>
+      </c>
+      <c r="BF45">
+        <v>1.72</v>
+      </c>
+      <c r="BG45"/>
+      <c r="BH45"/>
+    </row>
+    <row r="46" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D46" t="s">
+        <v>205</v>
+      </c>
+      <c r="E46" t="s">
+        <v>263</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G46">
+        <v>1.29</v>
+      </c>
+      <c r="H46">
+        <v>5.25</v>
+      </c>
+      <c r="I46">
+        <v>8</v>
+      </c>
+      <c r="J46">
+        <v>1.29</v>
+      </c>
+      <c r="K46">
+        <v>5</v>
+      </c>
+      <c r="L46">
+        <v>9</v>
+      </c>
+      <c r="M46">
+        <v>1.27</v>
+      </c>
+      <c r="N46">
+        <v>5.2</v>
+      </c>
+      <c r="O46">
+        <v>8.5</v>
+      </c>
+      <c r="P46">
+        <v>1.25</v>
+      </c>
+      <c r="Q46">
+        <v>5.5</v>
+      </c>
+      <c r="R46">
+        <v>9</v>
+      </c>
+      <c r="S46">
+        <v>1.28</v>
+      </c>
+      <c r="T46">
+        <v>5.25</v>
+      </c>
+      <c r="U46">
+        <v>7.5</v>
+      </c>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+      <c r="Y46"/>
+      <c r="Z46"/>
+      <c r="AA46"/>
+      <c r="AB46"/>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46">
+        <v>1.29</v>
+      </c>
+      <c r="AF46">
+        <v>5.75</v>
+      </c>
+      <c r="AG46">
+        <v>9</v>
+      </c>
+      <c r="AH46">
+        <v>1.27</v>
+      </c>
+      <c r="AI46">
+        <v>5.27</v>
+      </c>
+      <c r="AJ46">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="AK46">
+        <v>1.28</v>
+      </c>
+      <c r="AL46">
+        <v>6</v>
+      </c>
+      <c r="AM46">
+        <v>10</v>
+      </c>
+      <c r="AN46">
+        <v>1.44</v>
+      </c>
+      <c r="AO46">
+        <v>2.7</v>
+      </c>
+      <c r="AP46"/>
+      <c r="AQ46"/>
+      <c r="AR46">
+        <v>1.5</v>
+      </c>
+      <c r="AS46">
+        <v>2.8</v>
+      </c>
+      <c r="AT46">
+        <v>1.43</v>
+      </c>
+      <c r="AU46">
+        <v>2.62</v>
+      </c>
+      <c r="AV46">
+        <v>1.44</v>
+      </c>
+      <c r="AW46">
+        <v>2.78</v>
+      </c>
+      <c r="AX46">
+        <v>-1.5</v>
+      </c>
+      <c r="AY46">
+        <v>1.8</v>
+      </c>
+      <c r="AZ46">
+        <v>2</v>
+      </c>
+      <c r="BA46"/>
+      <c r="BB46"/>
+      <c r="BC46">
+        <v>1.8</v>
+      </c>
+      <c r="BD46">
+        <v>2</v>
+      </c>
+      <c r="BE46">
+        <v>1.75</v>
+      </c>
+      <c r="BF46">
+        <v>1.93</v>
+      </c>
+      <c r="BG46">
+        <v>1.79</v>
+      </c>
+      <c r="BH46">
+        <v>2.0299999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C47" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D47" t="s">
+        <v>215</v>
+      </c>
+      <c r="E47" t="s">
+        <v>221</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="G47">
+        <v>1.9</v>
+      </c>
+      <c r="H47">
+        <v>3.6</v>
+      </c>
+      <c r="I47">
+        <v>3.5</v>
+      </c>
+      <c r="J47">
+        <v>1.95</v>
+      </c>
+      <c r="K47">
+        <v>3.6</v>
+      </c>
+      <c r="L47">
+        <v>3.3</v>
+      </c>
+      <c r="M47">
+        <v>1.9</v>
+      </c>
+      <c r="N47">
+        <v>3.6</v>
+      </c>
+      <c r="O47">
+        <v>3.4</v>
+      </c>
+      <c r="P47">
+        <v>1.9</v>
+      </c>
+      <c r="Q47">
+        <v>3.6</v>
+      </c>
+      <c r="R47">
+        <v>3.4</v>
+      </c>
+      <c r="S47">
+        <v>1.9</v>
+      </c>
+      <c r="T47">
+        <v>3.6</v>
+      </c>
+      <c r="U47">
+        <v>3.1</v>
+      </c>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+      <c r="Y47"/>
+      <c r="Z47"/>
+      <c r="AA47"/>
+      <c r="AB47"/>
+      <c r="AC47"/>
+      <c r="AD47"/>
+      <c r="AE47">
+        <v>1.95</v>
+      </c>
+      <c r="AF47">
+        <v>4</v>
+      </c>
+      <c r="AG47">
+        <v>3.5</v>
+      </c>
+      <c r="AH47">
+        <v>1.9</v>
+      </c>
+      <c r="AI47">
+        <v>3.66</v>
+      </c>
+      <c r="AJ47">
+        <v>3.34</v>
+      </c>
+      <c r="AK47">
+        <v>1.94</v>
+      </c>
+      <c r="AL47">
+        <v>3.6</v>
+      </c>
+      <c r="AM47">
+        <v>3.15</v>
+      </c>
+      <c r="AN47">
+        <v>1.62</v>
+      </c>
+      <c r="AO47">
+        <v>2.25</v>
+      </c>
+      <c r="AP47"/>
+      <c r="AQ47"/>
+      <c r="AR47">
+        <v>1.65</v>
+      </c>
+      <c r="AS47">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AT47">
+        <v>1.6</v>
+      </c>
+      <c r="AU47">
+        <v>2.21</v>
+      </c>
+      <c r="AV47">
+        <v>1.51</v>
+      </c>
+      <c r="AW47">
+        <v>2.1</v>
+      </c>
+      <c r="AX47">
+        <v>-0.5</v>
+      </c>
+      <c r="AY47">
+        <v>1.93</v>
+      </c>
+      <c r="AZ47">
+        <v>1.88</v>
+      </c>
+      <c r="BA47"/>
+      <c r="BB47"/>
+      <c r="BC47">
+        <v>1.93</v>
+      </c>
+      <c r="BD47">
+        <v>1.88</v>
+      </c>
+      <c r="BE47">
+        <v>1.85</v>
+      </c>
+      <c r="BF47">
+        <v>1.82</v>
+      </c>
+      <c r="BG47">
+        <v>1.94</v>
+      </c>
+      <c r="BH47">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C48" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D48" t="s">
+        <v>211</v>
+      </c>
+      <c r="E48" t="s">
+        <v>208</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="G48">
+        <v>1.25</v>
+      </c>
+      <c r="H48">
+        <v>5.25</v>
+      </c>
+      <c r="I48">
+        <v>10</v>
+      </c>
+      <c r="J48">
+        <v>1.25</v>
+      </c>
+      <c r="K48">
+        <v>5.5</v>
+      </c>
+      <c r="L48">
+        <v>10</v>
+      </c>
+      <c r="M48">
+        <v>1.22</v>
+      </c>
+      <c r="N48">
+        <v>5.75</v>
+      </c>
+      <c r="O48">
+        <v>9.5</v>
+      </c>
+      <c r="P48">
+        <v>1.22</v>
+      </c>
+      <c r="Q48">
+        <v>5.75</v>
+      </c>
+      <c r="R48">
+        <v>9.5</v>
+      </c>
+      <c r="S48">
+        <v>1.26</v>
+      </c>
+      <c r="T48">
+        <v>5.5</v>
+      </c>
+      <c r="U48">
+        <v>7.75</v>
+      </c>
+      <c r="V48"/>
+      <c r="W48"/>
+      <c r="X48"/>
+      <c r="Y48"/>
+      <c r="Z48"/>
+      <c r="AA48"/>
+      <c r="AB48"/>
+      <c r="AC48"/>
+      <c r="AD48"/>
+      <c r="AE48">
+        <v>1.26</v>
+      </c>
+      <c r="AF48">
+        <v>6.33</v>
+      </c>
+      <c r="AG48">
+        <v>10.25</v>
+      </c>
+      <c r="AH48">
+        <v>1.23</v>
+      </c>
+      <c r="AI48">
+        <v>5.54</v>
+      </c>
+      <c r="AJ48">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="AK48">
+        <v>1.26</v>
+      </c>
+      <c r="AL48">
+        <v>6</v>
+      </c>
+      <c r="AM48">
+        <v>13.5</v>
+      </c>
+      <c r="AN48">
+        <v>1.44</v>
+      </c>
+      <c r="AO48">
+        <v>2.7</v>
+      </c>
+      <c r="AP48"/>
+      <c r="AQ48"/>
+      <c r="AR48">
+        <v>1.44</v>
+      </c>
+      <c r="AS48">
+        <v>2.88</v>
+      </c>
+      <c r="AT48">
+        <v>1.41</v>
+      </c>
+      <c r="AU48">
+        <v>2.71</v>
+      </c>
+      <c r="AV48">
+        <v>1.41</v>
+      </c>
+      <c r="AW48">
+        <v>2.5</v>
+      </c>
+      <c r="AX48">
+        <v>-1.75</v>
+      </c>
+      <c r="AY48">
+        <v>1.93</v>
+      </c>
+      <c r="AZ48">
+        <v>1.88</v>
+      </c>
+      <c r="BA48"/>
+      <c r="BB48"/>
+      <c r="BC48">
+        <v>1.93</v>
+      </c>
+      <c r="BD48">
+        <v>1.88</v>
+      </c>
+      <c r="BE48">
+        <v>1.86</v>
+      </c>
+      <c r="BF48">
+        <v>1.83</v>
+      </c>
+      <c r="BG48">
+        <v>1.8</v>
+      </c>
+      <c r="BH48">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C49" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D49" t="s">
+        <v>214</v>
+      </c>
+      <c r="E49" t="s">
+        <v>212</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G49">
+        <v>2.15</v>
+      </c>
+      <c r="H49">
+        <v>3.5</v>
+      </c>
+      <c r="I49">
+        <v>2.9</v>
+      </c>
+      <c r="J49">
+        <v>2.15</v>
+      </c>
+      <c r="K49">
+        <v>3.6</v>
+      </c>
+      <c r="L49">
+        <v>2.88</v>
+      </c>
+      <c r="M49">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="N49">
+        <v>3.5</v>
+      </c>
+      <c r="O49">
+        <v>2.8</v>
+      </c>
+      <c r="P49">
+        <v>2.15</v>
+      </c>
+      <c r="Q49">
+        <v>3.5</v>
+      </c>
+      <c r="R49">
+        <v>2.88</v>
+      </c>
+      <c r="S49">
+        <v>2.1</v>
+      </c>
+      <c r="T49">
+        <v>3.5</v>
+      </c>
+      <c r="U49">
+        <v>2.75</v>
+      </c>
+      <c r="V49"/>
+      <c r="W49"/>
+      <c r="X49"/>
+      <c r="Y49"/>
+      <c r="Z49"/>
+      <c r="AA49"/>
+      <c r="AB49"/>
+      <c r="AC49"/>
+      <c r="AD49"/>
+      <c r="AE49">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AF49">
+        <v>3.6</v>
+      </c>
+      <c r="AG49">
+        <v>3.1</v>
+      </c>
+      <c r="AH49">
+        <v>2.16</v>
+      </c>
+      <c r="AI49">
+        <v>3.48</v>
+      </c>
+      <c r="AJ49">
+        <v>2.87</v>
+      </c>
+      <c r="AK49">
+        <v>2.06</v>
+      </c>
+      <c r="AL49">
+        <v>3.15</v>
+      </c>
+      <c r="AM49">
+        <v>2.84</v>
+      </c>
+      <c r="AN49">
+        <v>1.62</v>
+      </c>
+      <c r="AO49">
+        <v>2.25</v>
+      </c>
+      <c r="AP49"/>
+      <c r="AQ49"/>
+      <c r="AR49">
+        <v>1.62</v>
+      </c>
+      <c r="AS49">
+        <v>2.4</v>
+      </c>
+      <c r="AT49">
+        <v>1.58</v>
+      </c>
+      <c r="AU49">
+        <v>2.25</v>
+      </c>
+      <c r="AV49">
+        <v>1.54</v>
+      </c>
+      <c r="AW49">
+        <v>2.06</v>
+      </c>
+      <c r="AX49">
+        <v>-0.25</v>
+      </c>
+      <c r="AY49">
+        <v>1.93</v>
+      </c>
+      <c r="AZ49">
+        <v>1.88</v>
+      </c>
+      <c r="BA49"/>
+      <c r="BB49"/>
+      <c r="BC49">
+        <v>1.93</v>
+      </c>
+      <c r="BD49">
+        <v>1.88</v>
+      </c>
+      <c r="BE49">
+        <v>1.87</v>
+      </c>
+      <c r="BF49">
+        <v>1.82</v>
+      </c>
+      <c r="BG49">
+        <v>1.83</v>
+      </c>
+      <c r="BH49">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C50" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D50" t="s">
+        <v>218</v>
+      </c>
+      <c r="E50" t="s">
+        <v>207</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G50">
+        <v>1.7</v>
+      </c>
+      <c r="H50">
+        <v>3.6</v>
+      </c>
+      <c r="I50">
+        <v>4.33</v>
+      </c>
+      <c r="J50">
+        <v>1.7</v>
+      </c>
+      <c r="K50">
+        <v>3.75</v>
+      </c>
+      <c r="L50">
+        <v>4.33</v>
+      </c>
+      <c r="M50">
+        <v>1.82</v>
+      </c>
+      <c r="N50">
+        <v>3.5</v>
+      </c>
+      <c r="O50">
+        <v>3.75</v>
+      </c>
+      <c r="P50">
+        <v>1.7</v>
+      </c>
+      <c r="Q50">
+        <v>3.7</v>
+      </c>
+      <c r="R50">
+        <v>4.2</v>
+      </c>
+      <c r="S50">
+        <v>1.68</v>
+      </c>
+      <c r="T50">
+        <v>3.6</v>
+      </c>
+      <c r="U50">
+        <v>4</v>
+      </c>
+      <c r="V50"/>
+      <c r="W50"/>
+      <c r="X50"/>
+      <c r="Y50"/>
+      <c r="Z50"/>
+      <c r="AA50"/>
+      <c r="AB50"/>
+      <c r="AC50"/>
+      <c r="AD50"/>
+      <c r="AE50">
+        <v>1.82</v>
+      </c>
+      <c r="AF50">
+        <v>3.75</v>
+      </c>
+      <c r="AG50">
+        <v>4.75</v>
+      </c>
+      <c r="AH50">
+        <v>1.72</v>
+      </c>
+      <c r="AI50">
+        <v>3.64</v>
+      </c>
+      <c r="AJ50">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="AK50">
+        <v>1.67</v>
+      </c>
+      <c r="AL50">
+        <v>3.4</v>
+      </c>
+      <c r="AM50">
+        <v>3.85</v>
+      </c>
+      <c r="AN50">
+        <v>1.73</v>
+      </c>
+      <c r="AO50">
+        <v>2.08</v>
+      </c>
+      <c r="AP50"/>
+      <c r="AQ50"/>
+      <c r="AR50">
+        <v>1.73</v>
+      </c>
+      <c r="AS50">
+        <v>2.25</v>
+      </c>
+      <c r="AT50">
+        <v>1.69</v>
+      </c>
+      <c r="AU50">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AV50">
+        <v>1.63</v>
+      </c>
+      <c r="AW50">
+        <v>1.94</v>
+      </c>
+      <c r="AX50">
+        <v>-0.75</v>
+      </c>
+      <c r="AY50">
+        <v>1.95</v>
+      </c>
+      <c r="AZ50">
+        <v>1.85</v>
+      </c>
+      <c r="BA50"/>
+      <c r="BB50"/>
+      <c r="BC50">
+        <v>1.95</v>
+      </c>
+      <c r="BD50">
+        <v>1.85</v>
+      </c>
+      <c r="BE50">
+        <v>1.9</v>
+      </c>
+      <c r="BF50">
+        <v>1.79</v>
+      </c>
+      <c r="BG50">
+        <v>1.85</v>
+      </c>
+      <c r="BH50">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C51" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D51" t="s">
+        <v>220</v>
+      </c>
+      <c r="E51" t="s">
+        <v>217</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G51">
+        <v>2.25</v>
+      </c>
+      <c r="H51">
+        <v>3.1</v>
+      </c>
+      <c r="I51">
+        <v>3</v>
+      </c>
+      <c r="J51">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K51">
+        <v>3.3</v>
+      </c>
+      <c r="L51">
+        <v>3</v>
+      </c>
+      <c r="M51">
+        <v>2.08</v>
+      </c>
+      <c r="N51">
+        <v>3.35</v>
+      </c>
+      <c r="O51">
+        <v>3.15</v>
+      </c>
+      <c r="P51">
+        <v>2.25</v>
+      </c>
+      <c r="Q51">
+        <v>3.2</v>
+      </c>
+      <c r="R51">
+        <v>3</v>
+      </c>
+      <c r="S51">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T51">
+        <v>3.2</v>
+      </c>
+      <c r="U51">
+        <v>2.85</v>
+      </c>
+      <c r="V51"/>
+      <c r="W51"/>
+      <c r="X51"/>
+      <c r="Y51"/>
+      <c r="Z51"/>
+      <c r="AA51"/>
+      <c r="AB51"/>
+      <c r="AC51"/>
+      <c r="AD51"/>
+      <c r="AE51">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AF51">
+        <v>3.5</v>
+      </c>
+      <c r="AG51">
+        <v>3.15</v>
+      </c>
+      <c r="AH51">
+        <v>2.21</v>
+      </c>
+      <c r="AI51">
+        <v>3.25</v>
+      </c>
+      <c r="AJ51">
+        <v>2.97</v>
+      </c>
+      <c r="AK51">
+        <v>2.16</v>
+      </c>
+      <c r="AL51">
+        <v>3.3</v>
+      </c>
+      <c r="AM51">
+        <v>2.94</v>
+      </c>
+      <c r="AN51">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AO51">
+        <v>1.75</v>
+      </c>
+      <c r="AP51"/>
+      <c r="AQ51"/>
+      <c r="AR51">
+        <v>2.1</v>
+      </c>
+      <c r="AS51">
+        <v>1.83</v>
+      </c>
+      <c r="AT51">
+        <v>1.98</v>
+      </c>
+      <c r="AU51">
+        <v>1.74</v>
+      </c>
+      <c r="AV51">
+        <v>1.89</v>
+      </c>
+      <c r="AW51">
+        <v>1.75</v>
+      </c>
+      <c r="AX51">
+        <v>-0.25</v>
+      </c>
+      <c r="AY51">
+        <v>1.98</v>
+      </c>
+      <c r="AZ51">
+        <v>1.83</v>
+      </c>
+      <c r="BA51"/>
+      <c r="BB51"/>
+      <c r="BC51">
+        <v>1.98</v>
+      </c>
+      <c r="BD51">
+        <v>1.83</v>
+      </c>
+      <c r="BE51">
+        <v>1.93</v>
+      </c>
+      <c r="BF51">
+        <v>1.77</v>
+      </c>
+      <c r="BG51">
+        <v>1.88</v>
+      </c>
+      <c r="BH51">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C52" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D52" t="s">
+        <v>224</v>
+      </c>
+      <c r="E52" t="s">
+        <v>225</v>
+      </c>
+      <c r="F52"/>
+      <c r="G52">
+        <v>1.3</v>
+      </c>
+      <c r="H52">
+        <v>4.5</v>
+      </c>
+      <c r="I52">
+        <v>10</v>
+      </c>
+      <c r="J52">
+        <v>1.33</v>
+      </c>
+      <c r="K52">
+        <v>4.5</v>
+      </c>
+      <c r="L52">
+        <v>8.5</v>
+      </c>
+      <c r="M52">
+        <v>1.38</v>
+      </c>
+      <c r="N52">
+        <v>4.5</v>
+      </c>
+      <c r="O52">
+        <v>7.5</v>
+      </c>
+      <c r="P52">
+        <v>1.3</v>
+      </c>
+      <c r="Q52">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="R52">
+        <v>9</v>
+      </c>
+      <c r="S52">
+        <v>1.36</v>
+      </c>
+      <c r="T52">
+        <v>5</v>
+      </c>
+      <c r="U52">
+        <v>8</v>
+      </c>
+      <c r="V52"/>
+      <c r="W52"/>
+      <c r="X52"/>
+      <c r="Y52"/>
+      <c r="Z52"/>
+      <c r="AA52"/>
+      <c r="AB52"/>
+      <c r="AC52"/>
+      <c r="AD52"/>
+      <c r="AE52">
+        <v>1.38</v>
+      </c>
+      <c r="AF52">
+        <v>5</v>
+      </c>
+      <c r="AG52">
+        <v>10</v>
+      </c>
+      <c r="AH52">
+        <v>1.33</v>
+      </c>
+      <c r="AI52">
+        <v>4.62</v>
+      </c>
+      <c r="AJ52">
+        <v>8.66</v>
+      </c>
+      <c r="AK52">
+        <v>1.35</v>
+      </c>
+      <c r="AL52">
+        <v>5.2</v>
+      </c>
+      <c r="AM52">
+        <v>11.5</v>
+      </c>
+      <c r="AN52">
+        <v>1.85</v>
+      </c>
+      <c r="AO52">
+        <v>1.95</v>
+      </c>
+      <c r="AP52"/>
+      <c r="AQ52"/>
+      <c r="AR52">
+        <v>1.85</v>
+      </c>
+      <c r="AS52">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AT52">
+        <v>1.78</v>
+      </c>
+      <c r="AU52">
+        <v>1.96</v>
+      </c>
+      <c r="AV52">
+        <v>1.84</v>
+      </c>
+      <c r="AW52">
+        <v>2.06</v>
+      </c>
+      <c r="AX52">
+        <v>-1.25</v>
+      </c>
+      <c r="AY52">
+        <v>1.8</v>
+      </c>
+      <c r="AZ52">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BA52"/>
+      <c r="BB52"/>
+      <c r="BC52">
+        <v>1.83</v>
+      </c>
+      <c r="BD52">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BE52">
+        <v>1.77</v>
+      </c>
+      <c r="BF52">
+        <v>1.97</v>
+      </c>
+      <c r="BG52"/>
+      <c r="BH52"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BH17">
-    <sortCondition ref="A2:A17"/>
-    <sortCondition ref="B2:B17"/>
-    <sortCondition ref="C2:C17"/>
-    <sortCondition ref="D2:D17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:BH52">
+    <sortCondition ref="A8:A52"/>
+    <sortCondition ref="B8:B52"/>
+    <sortCondition ref="C8:C52"/>
+    <sortCondition ref="D8:D52"/>
   </sortState>
   <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/fixtures.xlsx
+++ b/fixtures.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joebu\OneDrive\Documents\Football Fortunes\All data\Data\Riku\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee16c21b72f3fde9/Documents/Football Fortunes/All data/Data/Riku/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97C040A-0251-441C-A287-02922C373B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{05C4D078-E3C2-4AED-A23F-36D1249ADD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F67416A-5F39-48DA-9B92-9EEF5D462C84}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="223">
   <si>
     <t>Div</t>
   </si>
@@ -243,13 +243,19 @@
     <t>E0</t>
   </si>
   <si>
+    <t>SP2</t>
+  </si>
+  <si>
     <t>Referee</t>
   </si>
   <si>
     <t>B1</t>
   </si>
   <si>
-    <t>G1</t>
+    <t>I1</t>
+  </si>
+  <si>
+    <t>SP1</t>
   </si>
   <si>
     <t>Standard</t>
@@ -288,18 +294,69 @@
     <t>St Truiden</t>
   </si>
   <si>
+    <t>S Barrott</t>
+  </si>
+  <si>
+    <t>A Kitchen</t>
+  </si>
+  <si>
     <t>Man City</t>
   </si>
   <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Nott'm Forest</t>
+  </si>
+  <si>
+    <t>M Oliver</t>
+  </si>
+  <si>
     <t>Bournemouth</t>
   </si>
   <si>
+    <t>West Ham</t>
+  </si>
+  <si>
+    <t>Brighton</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Newcastle</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
     <t>Tottenham</t>
   </si>
   <si>
     <t>Chelsea</t>
   </si>
   <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Man United</t>
+  </si>
+  <si>
+    <t>Wolves</t>
+  </si>
+  <si>
+    <t>C Kavanagh</t>
+  </si>
+  <si>
     <t>BFEH</t>
   </si>
   <si>
@@ -432,28 +489,217 @@
     <t>LBCA</t>
   </si>
   <si>
+    <t>F Hallam</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Leeds</t>
+  </si>
+  <si>
     <t>A Taylor</t>
   </si>
   <si>
-    <t>S Attwell</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Panetolikos</t>
-  </si>
-  <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
-    <t>Larisa</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
+    <t>C Pawson</t>
+  </si>
+  <si>
+    <t>R Jones</t>
+  </si>
+  <si>
+    <t>D England</t>
+  </si>
+  <si>
+    <t>Girona</t>
+  </si>
+  <si>
+    <t>Vallecano</t>
+  </si>
+  <si>
+    <t>Villarreal</t>
+  </si>
+  <si>
+    <t>Oviedo</t>
+  </si>
+  <si>
+    <t>Mallorca</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Alaves</t>
+  </si>
+  <si>
+    <t>Levante</t>
+  </si>
+  <si>
+    <t>Valencia</t>
+  </si>
+  <si>
+    <t>Sociedad</t>
+  </si>
+  <si>
+    <t>Celta</t>
+  </si>
+  <si>
+    <t>Getafe</t>
+  </si>
+  <si>
+    <t>Ath Bilbao</t>
+  </si>
+  <si>
+    <t>Sevilla</t>
+  </si>
+  <si>
+    <t>Espanol</t>
+  </si>
+  <si>
+    <t>Ath Madrid</t>
+  </si>
+  <si>
+    <t>Elche</t>
+  </si>
+  <si>
+    <t>Betis</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Osasuna</t>
+  </si>
+  <si>
+    <t>Burgos</t>
+  </si>
+  <si>
+    <t>Cultural Leonesa</t>
+  </si>
+  <si>
+    <t>Valladolid</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Santander</t>
+  </si>
+  <si>
+    <t>Castellon</t>
+  </si>
+  <si>
+    <t>Malaga</t>
+  </si>
+  <si>
+    <t>Eibar</t>
+  </si>
+  <si>
+    <t>Granada</t>
+  </si>
+  <si>
+    <t>La Coruna</t>
+  </si>
+  <si>
+    <t>Sociedad B</t>
+  </si>
+  <si>
+    <t>Zaragoza</t>
+  </si>
+  <si>
+    <t>Cadiz</t>
+  </si>
+  <si>
+    <t>Mirandes</t>
+  </si>
+  <si>
+    <t>Huesca</t>
+  </si>
+  <si>
+    <t>Leganes</t>
+  </si>
+  <si>
+    <t>Las Palmas</t>
+  </si>
+  <si>
+    <t>Andorra</t>
+  </si>
+  <si>
+    <t>Sp Gijon</t>
+  </si>
+  <si>
+    <t>Cordoba</t>
+  </si>
+  <si>
+    <t>Almeria</t>
+  </si>
+  <si>
+    <t>Albacete</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
+    <t>Lecce</t>
+  </si>
+  <si>
+    <t>Sassuolo</t>
+  </si>
+  <si>
+    <t>Napoli</t>
+  </si>
+  <si>
+    <t>Milan</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Bologna</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Fiorentina</t>
+  </si>
+  <si>
+    <t>Como</t>
+  </si>
+  <si>
+    <t>Lazio</t>
+  </si>
+  <si>
+    <t>Atalanta</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>Juventus</t>
+  </si>
+  <si>
+    <t>Parma</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Verona</t>
+  </si>
+  <si>
+    <t>Inter</t>
+  </si>
+  <si>
+    <t>Torino</t>
+  </si>
+  <si>
+    <t>A Madley</t>
   </si>
 </sst>
 </file>
@@ -1981,14 +2227,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64032AAF-94ED-49C7-B015-7ECD08F95F34}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:DJ12"/>
+  <dimension ref="A1:DJ48"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.26953125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.54296875" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.90625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.36328125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="18.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.26953125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="6.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.7265625" style="1" bestFit="1" customWidth="1"/>
@@ -2003,9 +2249,9 @@
     <col min="28" max="29" width="4.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="4.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="32" width="5.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="5.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="38" width="5.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="5.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="40" max="41" width="8.7265625" style="1" bestFit="1" customWidth="1"/>
@@ -2082,7 +2328,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>4</v>
@@ -2094,31 +2340,31 @@
         <v>6</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>7</v>
@@ -2130,22 +2376,22 @@
         <v>9</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="AB1" s="5" t="s">
         <v>10</v>
@@ -2175,13 +2421,13 @@
         <v>19</v>
       </c>
       <c r="AK1" s="5" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="AL1" s="5" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="AM1" s="5" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="AN1" s="5" t="s">
         <v>20</v>
@@ -2208,10 +2454,10 @@
         <v>27</v>
       </c>
       <c r="AV1" s="5" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="AW1" s="5" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="AX1" s="5" t="s">
         <v>28</v>
@@ -2241,10 +2487,10 @@
         <v>36</v>
       </c>
       <c r="BG1" s="5" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="BH1" s="5" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="BI1" s="5" t="s">
         <v>37</v>
@@ -2256,31 +2502,31 @@
         <v>39</v>
       </c>
       <c r="BL1" s="5" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="BM1" s="5" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="BN1" s="5" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="BO1" s="5" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="BP1" s="5" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="BQ1" s="5" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="BR1" s="5" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="BS1" s="5" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="BT1" s="5" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="BU1" s="5" t="s">
         <v>40</v>
@@ -2292,22 +2538,22 @@
         <v>42</v>
       </c>
       <c r="BX1" s="5" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="BY1" s="5" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="BZ1" s="5" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="CA1" s="7" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="CB1" s="7" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="CC1" s="7" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="CD1" s="5" t="s">
         <v>43</v>
@@ -2337,13 +2583,13 @@
         <v>51</v>
       </c>
       <c r="CM1" s="7" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="CN1" s="5" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="CO1" s="5" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="CP1" s="5" t="s">
         <v>52</v>
@@ -2370,10 +2616,10 @@
         <v>59</v>
       </c>
       <c r="CX1" s="7" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="CY1" s="5" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="CZ1" s="5" t="s">
         <v>60</v>
@@ -2403,287 +2649,287 @@
         <v>68</v>
       </c>
       <c r="DI1" s="5" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="DJ1" s="5" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2">
-        <v>46161</v>
+        <v>46165</v>
       </c>
       <c r="C2" s="3">
-        <v>0.8125</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F2"/>
       <c r="G2">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I2">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J2">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="K2">
         <v>3.75</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="M2">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
-        <v>4.0999999999999996</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
         <v>3.8</v>
       </c>
       <c r="R2">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="S2">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="T2">
         <v>3.9</v>
       </c>
       <c r="U2">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="V2">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="W2">
         <v>3.9</v>
       </c>
       <c r="X2">
+        <v>3.5</v>
+      </c>
+      <c r="Y2">
+        <v>1.91</v>
+      </c>
+      <c r="Z2">
         <v>3.9</v>
       </c>
-      <c r="Y2">
-        <v>1.83</v>
-      </c>
-      <c r="Z2">
-        <v>3.8</v>
-      </c>
       <c r="AA2">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AB2"/>
       <c r="AC2"/>
       <c r="AD2"/>
       <c r="AE2">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AF2">
         <v>4</v>
       </c>
       <c r="AG2">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="AH2">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AI2">
-        <v>3.84</v>
+        <v>3.77</v>
       </c>
       <c r="AJ2">
-        <v>3.91</v>
+        <v>3.42</v>
       </c>
       <c r="AK2">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AL2">
         <v>4</v>
       </c>
       <c r="AM2">
-        <v>4.0999999999999996</v>
+        <v>3.75</v>
       </c>
       <c r="AN2">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AO2">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AP2"/>
       <c r="AQ2"/>
       <c r="AR2">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AS2">
         <v>2.5</v>
       </c>
       <c r="AT2">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU2">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="AV2">
-        <v>1.65</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AW2">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AX2">
-        <v>-0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="AY2">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AZ2">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="BA2"/>
       <c r="BB2"/>
       <c r="BC2">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="BD2">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="BE2">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="BF2">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BG2">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="BH2">
-        <v>2.0299999999999998</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="3" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2">
-        <v>46161</v>
+        <v>46165</v>
       </c>
       <c r="C3" s="3">
-        <v>0.8125</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F3"/>
       <c r="G3">
-        <v>1.55</v>
+        <v>3.7</v>
       </c>
       <c r="H3">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>1.85</v>
       </c>
       <c r="J3">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="M3">
-        <v>1.48</v>
+        <v>3.45</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O3">
-        <v>5.25</v>
+        <v>1.85</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R3">
-        <v>5.5</v>
+        <v>1.83</v>
       </c>
       <c r="S3">
-        <v>1.58</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="U3">
-        <v>5.25</v>
+        <v>1.88</v>
       </c>
       <c r="V3">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="W3">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="X3">
-        <v>5.25</v>
+        <v>1.91</v>
       </c>
       <c r="Y3">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="Z3">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA3">
-        <v>5.25</v>
+        <v>1.91</v>
       </c>
       <c r="AB3"/>
       <c r="AC3"/>
       <c r="AD3"/>
       <c r="AE3">
-        <v>1.58</v>
+        <v>3.7</v>
       </c>
       <c r="AF3">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AG3">
-        <v>5.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH3">
-        <v>1.53</v>
+        <v>3.54</v>
       </c>
       <c r="AI3">
-        <v>4.1500000000000004</v>
+        <v>3.73</v>
       </c>
       <c r="AJ3">
-        <v>5.36</v>
+        <v>1.87</v>
       </c>
       <c r="AK3">
-        <v>1.59</v>
+        <v>3.9</v>
       </c>
       <c r="AL3">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="AM3">
-        <v>6</v>
+        <v>1.86</v>
       </c>
       <c r="AN3">
         <v>1.67</v>
@@ -2697,129 +2943,129 @@
         <v>1.67</v>
       </c>
       <c r="AS3">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AT3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AU3">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AV3">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AW3">
-        <v>2.2799999999999998</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="AX3">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="AY3">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AZ3">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BA3"/>
       <c r="BB3"/>
       <c r="BC3">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BD3">
+        <v>1.85</v>
+      </c>
+      <c r="BE3">
         <v>1.88</v>
       </c>
-      <c r="BE3">
-        <v>1.87</v>
-      </c>
       <c r="BF3">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BG3">
-        <v>1.98</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="BH3">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="2">
-        <v>46161</v>
+        <v>46165</v>
       </c>
       <c r="C4" s="3">
-        <v>0.8125</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F4"/>
       <c r="G4">
         <v>2.1</v>
       </c>
       <c r="H4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I4">
+        <v>3.2</v>
+      </c>
+      <c r="J4">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K4">
         <v>3.3</v>
       </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3.6</v>
-      </c>
       <c r="L4">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="M4">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="N4">
+        <v>3.35</v>
+      </c>
+      <c r="O4">
         <v>3.45</v>
       </c>
-      <c r="O4">
-        <v>3.3</v>
-      </c>
       <c r="P4">
-        <v>2</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="Q4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R4">
         <v>3.25</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="T4">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U4">
         <v>3.5</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="W4">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="X4">
         <v>3.5</v>
       </c>
       <c r="Y4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB4"/>
       <c r="AC4"/>
@@ -2828,54 +3074,54 @@
         <v>2.1</v>
       </c>
       <c r="AF4">
+        <v>3.45</v>
+      </c>
+      <c r="AG4">
         <v>3.6</v>
       </c>
-      <c r="AG4">
-        <v>3.5</v>
-      </c>
       <c r="AH4">
-        <v>2.0099999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AI4">
-        <v>3.51</v>
+        <v>3.35</v>
       </c>
       <c r="AJ4">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AK4">
-        <v>2.14</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="AL4">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AM4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AN4">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AO4">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AP4"/>
       <c r="AQ4"/>
       <c r="AR4">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AS4">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AT4">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AU4">
-        <v>2.1800000000000002</v>
+        <v>1.86</v>
       </c>
       <c r="AV4">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AW4">
-        <v>2.34</v>
+        <v>1.97</v>
       </c>
       <c r="AX4">
         <v>-0.25</v>
@@ -2892,663 +3138,595 @@
         <v>1.85</v>
       </c>
       <c r="BD4">
-        <v>1.95</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="BE4">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BF4">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="BG4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BH4">
-        <v>2.0699999999999998</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="2">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="C5" s="3">
-        <v>0.8125</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F5"/>
-      <c r="G5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="H5">
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5">
+        <v>1.73</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
         <v>3.75</v>
       </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="K5">
-        <v>3.6</v>
-      </c>
-      <c r="L5">
-        <v>2.8</v>
-      </c>
       <c r="M5">
-        <v>2.0699999999999998</v>
+        <v>1.67</v>
       </c>
       <c r="N5">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="P5"/>
       <c r="Q5"/>
       <c r="R5"/>
       <c r="S5">
-        <v>2.2000000000000002</v>
+        <v>1.78</v>
       </c>
       <c r="T5">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="U5">
-        <v>3</v>
-      </c>
-      <c r="V5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="W5">
-        <v>3.7</v>
-      </c>
-      <c r="X5">
-        <v>3</v>
-      </c>
+        <v>3.8</v>
+      </c>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
       <c r="Y5">
-        <v>2.2000000000000002</v>
+        <v>1.75</v>
       </c>
       <c r="Z5">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA5">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AB5"/>
       <c r="AC5"/>
       <c r="AD5"/>
       <c r="AE5">
-        <v>2.2000000000000002</v>
+        <v>1.78</v>
       </c>
       <c r="AF5">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AG5">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AH5">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="AI5">
-        <v>3.61</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="AJ5">
-        <v>2.92</v>
+        <v>3.67</v>
       </c>
       <c r="AK5">
-        <v>2.2400000000000002</v>
+        <v>1.82</v>
       </c>
       <c r="AL5">
-        <v>3.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AM5">
-        <v>3.1</v>
-      </c>
-      <c r="AN5">
-        <v>1.6</v>
-      </c>
-      <c r="AO5">
-        <v>2.2999999999999998</v>
-      </c>
+        <v>3.55</v>
+      </c>
+      <c r="AN5"/>
+      <c r="AO5"/>
       <c r="AP5"/>
       <c r="AQ5"/>
       <c r="AR5">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AS5">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AT5">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="AU5">
-        <v>2.31</v>
+        <v>2.86</v>
       </c>
       <c r="AV5">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AW5">
-        <v>2.36</v>
+        <v>2.84</v>
       </c>
       <c r="AX5">
-        <v>-0.25</v>
-      </c>
-      <c r="AY5">
-        <v>1.9</v>
-      </c>
-      <c r="AZ5">
-        <v>1.9</v>
-      </c>
+        <v>-0.5</v>
+      </c>
+      <c r="AY5"/>
+      <c r="AZ5"/>
       <c r="BA5"/>
       <c r="BB5"/>
       <c r="BC5">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="BD5">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BE5">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="BF5">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BG5"/>
       <c r="BH5"/>
     </row>
     <row r="6" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="2">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="C6" s="3">
-        <v>0.8125</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F6"/>
-      <c r="G6">
-        <v>4.5</v>
-      </c>
-      <c r="H6">
-        <v>3.7</v>
-      </c>
-      <c r="I6">
-        <v>1.75</v>
-      </c>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
       <c r="J6">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
         <v>3.6</v>
       </c>
-      <c r="L6">
-        <v>1.73</v>
-      </c>
       <c r="M6">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="N6">
         <v>3.55</v>
       </c>
       <c r="O6">
-        <v>1.67</v>
+        <v>3.55</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
       <c r="R6"/>
       <c r="S6">
-        <v>4.4000000000000004</v>
+        <v>1.85</v>
       </c>
       <c r="T6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="U6">
         <v>3.6</v>
       </c>
-      <c r="U6">
-        <v>1.8</v>
-      </c>
-      <c r="V6">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="W6">
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6">
+        <v>1.85</v>
+      </c>
+      <c r="Z6">
+        <v>4</v>
+      </c>
+      <c r="AA6">
         <v>3.6</v>
-      </c>
-      <c r="X6">
-        <v>1.8</v>
-      </c>
-      <c r="Y6">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="Z6">
-        <v>3.6</v>
-      </c>
-      <c r="AA6">
-        <v>1.8</v>
       </c>
       <c r="AB6"/>
       <c r="AC6"/>
       <c r="AD6"/>
       <c r="AE6">
-        <v>4.5999999999999996</v>
+        <v>1.88</v>
       </c>
       <c r="AF6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AG6">
+        <v>3.65</v>
+      </c>
+      <c r="AH6">
+        <v>1.82</v>
+      </c>
+      <c r="AI6">
+        <v>3.85</v>
+      </c>
+      <c r="AJ6">
+        <v>3.53</v>
+      </c>
+      <c r="AK6">
+        <v>1.83</v>
+      </c>
+      <c r="AL6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AM6">
         <v>3.8</v>
       </c>
-      <c r="AG6">
-        <v>1.8</v>
-      </c>
-      <c r="AH6">
-        <v>4.32</v>
-      </c>
-      <c r="AI6">
-        <v>3.61</v>
-      </c>
-      <c r="AJ6">
-        <v>1.73</v>
-      </c>
-      <c r="AK6">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AL6">
-        <v>3.7</v>
-      </c>
-      <c r="AM6">
-        <v>1.77</v>
-      </c>
-      <c r="AN6">
-        <v>1.9</v>
-      </c>
-      <c r="AO6">
-        <v>1.9</v>
-      </c>
+      <c r="AN6"/>
+      <c r="AO6"/>
       <c r="AP6"/>
       <c r="AQ6"/>
       <c r="AR6">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AS6">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AT6">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AU6">
-        <v>1.86</v>
+        <v>2.34</v>
       </c>
       <c r="AV6">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AW6">
-        <v>1.9</v>
+        <v>2.44</v>
       </c>
       <c r="AX6">
-        <v>0.5</v>
-      </c>
-      <c r="AY6">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="AZ6">
-        <v>1.75</v>
-      </c>
+        <v>-0.5</v>
+      </c>
+      <c r="AY6"/>
+      <c r="AZ6"/>
       <c r="BA6"/>
       <c r="BB6"/>
       <c r="BC6">
-        <v>2.0499999999999998</v>
+        <v>1.83</v>
       </c>
       <c r="BD6">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BE6">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="BF6">
-        <v>1.73</v>
-      </c>
-      <c r="BG6">
-        <v>2.09</v>
-      </c>
-      <c r="BH6">
-        <v>1.77</v>
-      </c>
+        <v>1.91</v>
+      </c>
+      <c r="BG6"/>
+      <c r="BH6"/>
     </row>
     <row r="7" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="C7" s="3">
-        <v>0.8125</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" t="s">
         <v>80</v>
       </c>
-      <c r="E7" t="s">
-        <v>83</v>
-      </c>
       <c r="F7"/>
-      <c r="G7">
-        <v>7</v>
-      </c>
-      <c r="H7">
-        <v>4.75</v>
-      </c>
-      <c r="I7">
-        <v>1.38</v>
-      </c>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
       <c r="J7">
+        <v>1.44</v>
+      </c>
+      <c r="K7">
+        <v>4.2</v>
+      </c>
+      <c r="L7">
         <v>6.5</v>
       </c>
-      <c r="K7">
-        <v>5</v>
-      </c>
-      <c r="L7">
-        <v>1.36</v>
-      </c>
       <c r="M7">
-        <v>6.75</v>
+        <v>1.42</v>
       </c>
       <c r="N7">
-        <v>4.9000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="O7">
-        <v>1.32</v>
+        <v>6.1</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
       <c r="R7"/>
       <c r="S7">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="T7">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="U7">
-        <v>1.41</v>
-      </c>
-      <c r="V7">
-        <v>6.5</v>
-      </c>
-      <c r="W7">
-        <v>5.25</v>
-      </c>
-      <c r="X7">
-        <v>1.4</v>
-      </c>
+        <v>6.25</v>
+      </c>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
       <c r="Y7">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="Z7">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA7">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="AB7"/>
       <c r="AC7"/>
       <c r="AD7"/>
       <c r="AE7">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="AF7">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AG7">
-        <v>1.41</v>
+        <v>6.66</v>
       </c>
       <c r="AH7">
-        <v>6.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AJ7">
-        <v>1.37</v>
+        <v>6.26</v>
       </c>
       <c r="AK7">
-        <v>7.2</v>
+        <v>1.47</v>
       </c>
       <c r="AL7">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AM7">
-        <v>1.39</v>
-      </c>
-      <c r="AN7">
-        <v>1.4</v>
-      </c>
-      <c r="AO7">
-        <v>2.88</v>
-      </c>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AN7"/>
+      <c r="AO7"/>
       <c r="AP7"/>
       <c r="AQ7"/>
       <c r="AR7">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AS7">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AT7">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AU7">
-        <v>2.91</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="AV7">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="AX7">
-        <v>1.5</v>
-      </c>
-      <c r="AY7">
-        <v>1.8</v>
-      </c>
-      <c r="AZ7">
-        <v>2</v>
-      </c>
+        <v>-1.5</v>
+      </c>
+      <c r="AY7"/>
+      <c r="AZ7"/>
       <c r="BA7"/>
       <c r="BB7"/>
       <c r="BC7">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="BD7">
-        <v>2.0499999999999998</v>
+        <v>1.62</v>
       </c>
       <c r="BE7">
-        <v>1.75</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="BF7">
-        <v>1.98</v>
-      </c>
-      <c r="BG7">
-        <v>1.86</v>
-      </c>
-      <c r="BH7">
-        <v>2.04</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="BG7"/>
+      <c r="BH7"/>
     </row>
     <row r="8" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B8" s="2">
-        <v>46161</v>
+        <v>46166</v>
       </c>
       <c r="C8" s="3">
-        <v>0.8125</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="G8">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="H8">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="I8">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="J8">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="K8">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="M8">
-        <v>4.4000000000000004</v>
+        <v>1.86</v>
       </c>
       <c r="N8">
-        <v>4.0999999999999996</v>
+        <v>3.9</v>
       </c>
       <c r="O8">
-        <v>1.63</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>4.5999999999999996</v>
+        <v>1.83</v>
       </c>
       <c r="Q8">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R8">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="S8">
-        <v>4.33</v>
+        <v>1.85</v>
       </c>
       <c r="T8">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>1.68</v>
+        <v>3.7</v>
       </c>
       <c r="V8">
-        <v>4.33</v>
+        <v>1.85</v>
       </c>
       <c r="W8">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="X8">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="Y8">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="Z8">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA8">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8"/>
       <c r="AE8">
-        <v>4.5999999999999996</v>
+        <v>1.92</v>
       </c>
       <c r="AF8">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>3.75</v>
       </c>
       <c r="AH8">
-        <v>4.42</v>
+        <v>1.86</v>
       </c>
       <c r="AI8">
-        <v>4.2699999999999996</v>
+        <v>3.98</v>
       </c>
       <c r="AJ8">
-        <v>1.66</v>
+        <v>3.58</v>
       </c>
       <c r="AK8">
-        <v>4.8</v>
+        <v>1.95</v>
       </c>
       <c r="AL8">
-        <v>4.5999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="AM8">
-        <v>1.72</v>
+        <v>3.8</v>
       </c>
       <c r="AN8">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AO8">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AP8"/>
       <c r="AQ8"/>
       <c r="AR8">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AS8">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AT8">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AU8">
+        <v>2.6</v>
+      </c>
+      <c r="AV8">
+        <v>1.52</v>
+      </c>
+      <c r="AW8">
         <v>2.8</v>
       </c>
-      <c r="AV8">
-        <v>1.48</v>
-      </c>
-      <c r="AW8">
-        <v>3</v>
-      </c>
       <c r="AX8">
-        <v>0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="AY8">
-        <v>2.0299999999999998</v>
+        <v>1.85</v>
       </c>
       <c r="AZ8">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BA8"/>
       <c r="BB8"/>
       <c r="BC8">
-        <v>2.0299999999999998</v>
+        <v>1.9</v>
       </c>
       <c r="BD8">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="BE8">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="BF8">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="BG8">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="BH8">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="9" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3556,112 +3734,112 @@
         <v>69</v>
       </c>
       <c r="B9" s="2">
-        <v>46161</v>
+        <v>46166</v>
       </c>
       <c r="C9" s="3">
-        <v>0.84375</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="G9">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="H9">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I9">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J9">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="K9">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L9">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="M9">
-        <v>1.89</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="N9">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="P9">
-        <v>1.91</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="Q9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="S9">
-        <v>1.9</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="T9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>1.91</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="W9">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="X9">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y9">
-        <v>1.91</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="Z9">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA9">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9"/>
       <c r="AE9">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="AF9">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AG9">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AH9">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AI9">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AJ9">
-        <v>3.76</v>
+        <v>2.77</v>
       </c>
       <c r="AK9">
-        <v>1.99</v>
+        <v>2.48</v>
       </c>
       <c r="AL9">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AM9">
-        <v>4.0999999999999996</v>
+        <v>3</v>
       </c>
       <c r="AN9">
         <v>1.73</v>
@@ -3675,476 +3853,6418 @@
         <v>1.73</v>
       </c>
       <c r="AS9">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AT9">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AU9">
-        <v>2.12</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AV9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AW9">
-        <v>2.2400000000000002</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AX9">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="AY9">
-        <v>1.93</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="AZ9">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BA9"/>
       <c r="BB9"/>
       <c r="BC9">
-        <v>1.93</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="BD9">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BE9">
-        <v>1.87</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="BF9">
+        <v>1.74</v>
+      </c>
+      <c r="BG9">
+        <v>2.14</v>
+      </c>
+      <c r="BH9">
         <v>1.85</v>
-      </c>
-      <c r="BG9">
-        <v>1.99</v>
-      </c>
-      <c r="BH9">
-        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="C10" s="3">
         <v>0.66666666666666663</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>138</v>
-      </c>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
+        <v>90</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10">
+        <v>4.2</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>1.75</v>
+      </c>
       <c r="J10">
-        <v>1.53</v>
+        <v>4.2</v>
       </c>
       <c r="K10">
         <v>3.75</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M10">
-        <v>1.67</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O10">
-        <v>5.2</v>
-      </c>
-      <c r="P10"/>
-      <c r="Q10"/>
-      <c r="R10"/>
+        <v>1.72</v>
+      </c>
+      <c r="P10">
+        <v>4.2</v>
+      </c>
+      <c r="Q10">
+        <v>3.8</v>
+      </c>
+      <c r="R10">
+        <v>1.75</v>
+      </c>
       <c r="S10">
-        <v>1.57</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="T10">
+        <v>3.8</v>
+      </c>
+      <c r="U10">
+        <v>1.82</v>
+      </c>
+      <c r="V10">
         <v>4</v>
       </c>
-      <c r="U10">
-        <v>5.5</v>
-      </c>
-      <c r="V10">
-        <v>1.53</v>
-      </c>
       <c r="W10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="Y10">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="Z10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10"/>
       <c r="AE10">
+        <v>4.33</v>
+      </c>
+      <c r="AF10">
+        <v>4.2</v>
+      </c>
+      <c r="AG10">
+        <v>1.82</v>
+      </c>
+      <c r="AH10">
+        <v>4.13</v>
+      </c>
+      <c r="AI10">
+        <v>3.86</v>
+      </c>
+      <c r="AJ10">
+        <v>1.76</v>
+      </c>
+      <c r="AK10">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AL10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AM10">
+        <v>1.83</v>
+      </c>
+      <c r="AN10">
         <v>1.67</v>
       </c>
-      <c r="AF10">
-        <v>4</v>
-      </c>
-      <c r="AG10">
-        <v>6</v>
-      </c>
-      <c r="AH10">
-        <v>1.57</v>
-      </c>
-      <c r="AI10">
-        <v>3.71</v>
-      </c>
-      <c r="AJ10">
-        <v>5.28</v>
-      </c>
-      <c r="AK10">
-        <v>1.55</v>
-      </c>
-      <c r="AL10">
-        <v>3.55</v>
-      </c>
-      <c r="AM10">
-        <v>4.8</v>
-      </c>
-      <c r="AN10"/>
-      <c r="AO10"/>
+      <c r="AO10">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="AP10"/>
       <c r="AQ10"/>
       <c r="AR10">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AS10">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AT10">
-        <v>1.99</v>
+        <v>1.63</v>
       </c>
       <c r="AU10">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="AV10">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AW10">
-        <v>1.86</v>
+        <v>2.34</v>
       </c>
       <c r="AX10">
-        <v>-0.75</v>
-      </c>
-      <c r="AY10"/>
-      <c r="AZ10"/>
+        <v>0.75</v>
+      </c>
+      <c r="AY10">
+        <v>1.85</v>
+      </c>
+      <c r="AZ10">
+        <v>2</v>
+      </c>
       <c r="BA10"/>
       <c r="BB10"/>
       <c r="BC10">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="BD10">
-        <v>2.0499999999999998</v>
+        <v>2</v>
       </c>
       <c r="BE10">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="BF10">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="BG10"/>
-      <c r="BH10"/>
+        <v>1.94</v>
+      </c>
+      <c r="BG10">
+        <v>1.93</v>
+      </c>
+      <c r="BH10">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="11" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="C11" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
+        <v>99</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11">
+        <v>2.88</v>
+      </c>
+      <c r="H11">
+        <v>3.8</v>
+      </c>
+      <c r="I11">
+        <v>2.25</v>
+      </c>
       <c r="J11">
+        <v>2.8</v>
+      </c>
+      <c r="K11">
+        <v>3.75</v>
+      </c>
+      <c r="L11">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M11">
+        <v>2.88</v>
+      </c>
+      <c r="N11">
+        <v>3.5</v>
+      </c>
+      <c r="O11">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P11">
+        <v>2.8</v>
+      </c>
+      <c r="Q11">
+        <v>3.6</v>
+      </c>
+      <c r="R11">
         <v>2.25</v>
       </c>
-      <c r="K11">
-        <v>3.2</v>
-      </c>
-      <c r="L11">
-        <v>3</v>
-      </c>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11"/>
       <c r="S11">
+        <v>2.8</v>
+      </c>
+      <c r="T11">
+        <v>3.7</v>
+      </c>
+      <c r="U11">
+        <v>2.35</v>
+      </c>
+      <c r="V11">
+        <v>2.8</v>
+      </c>
+      <c r="W11">
+        <v>3.7</v>
+      </c>
+      <c r="X11">
+        <v>2.37</v>
+      </c>
+      <c r="Y11">
+        <v>2.8</v>
+      </c>
+      <c r="Z11">
+        <v>3.6</v>
+      </c>
+      <c r="AA11">
         <v>2.2999999999999998</v>
-      </c>
-      <c r="T11">
-        <v>3.25</v>
-      </c>
-      <c r="U11">
-        <v>3</v>
-      </c>
-      <c r="V11">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="W11">
-        <v>3.1</v>
-      </c>
-      <c r="X11">
-        <v>2.9</v>
-      </c>
-      <c r="Y11">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Z11">
-        <v>3.1</v>
-      </c>
-      <c r="AA11">
-        <v>2.9</v>
       </c>
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11"/>
       <c r="AE11">
+        <v>2.9</v>
+      </c>
+      <c r="AF11">
+        <v>3.8</v>
+      </c>
+      <c r="AG11">
+        <v>2.37</v>
+      </c>
+      <c r="AH11">
+        <v>2.82</v>
+      </c>
+      <c r="AI11">
+        <v>3.66</v>
+      </c>
+      <c r="AJ11">
+        <v>2.27</v>
+      </c>
+      <c r="AK11">
+        <v>2.98</v>
+      </c>
+      <c r="AL11">
+        <v>3.9</v>
+      </c>
+      <c r="AM11">
+        <v>2.42</v>
+      </c>
+      <c r="AN11">
+        <v>1.62</v>
+      </c>
+      <c r="AO11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AF11">
-        <v>3.25</v>
-      </c>
-      <c r="AG11">
-        <v>3.2</v>
-      </c>
-      <c r="AH11">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="AI11">
-        <v>3.13</v>
-      </c>
-      <c r="AJ11">
-        <v>2.98</v>
-      </c>
-      <c r="AK11">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="AL11">
-        <v>3.15</v>
-      </c>
-      <c r="AM11">
-        <v>3.25</v>
-      </c>
-      <c r="AN11"/>
-      <c r="AO11"/>
       <c r="AP11"/>
       <c r="AQ11"/>
       <c r="AR11">
-        <v>2.14</v>
+        <v>1.62</v>
       </c>
       <c r="AS11">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="AT11">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="AU11">
+        <v>2.25</v>
+      </c>
+      <c r="AV11">
         <v>1.67</v>
       </c>
-      <c r="AV11">
-        <v>2.08</v>
-      </c>
       <c r="AW11">
-        <v>1.74</v>
+        <v>2.42</v>
       </c>
       <c r="AX11">
-        <v>-0.25</v>
-      </c>
-      <c r="AY11"/>
-      <c r="AZ11"/>
+        <v>0.25</v>
+      </c>
+      <c r="AY11">
+        <v>1.85</v>
+      </c>
+      <c r="AZ11">
+        <v>2</v>
+      </c>
       <c r="BA11"/>
       <c r="BB11"/>
       <c r="BC11">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BD11">
+        <v>2</v>
+      </c>
+      <c r="BE11">
         <v>1.8</v>
       </c>
-      <c r="BE11">
-        <v>1.91</v>
-      </c>
       <c r="BF11">
-        <v>1.78</v>
-      </c>
-      <c r="BG11"/>
-      <c r="BH11"/>
+        <v>1.94</v>
+      </c>
+      <c r="BG11">
+        <v>1.87</v>
+      </c>
+      <c r="BH11">
+        <v>2.11</v>
+      </c>
     </row>
     <row r="12" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2">
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="C12" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
+        <v>101</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G12">
+        <v>1.8</v>
+      </c>
+      <c r="H12">
+        <v>4.2</v>
+      </c>
+      <c r="I12">
+        <v>3.8</v>
+      </c>
       <c r="J12">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="K12">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="O12">
-        <v>2.95</v>
-      </c>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12"/>
+        <v>3.75</v>
+      </c>
+      <c r="P12">
+        <v>1.8</v>
+      </c>
+      <c r="Q12">
+        <v>3.9</v>
+      </c>
+      <c r="R12">
+        <v>3.8</v>
+      </c>
       <c r="S12">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="U12">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="V12">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="W12">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="X12">
-        <v>2.87</v>
+        <v>3.75</v>
       </c>
       <c r="Y12">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Z12">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA12">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12"/>
       <c r="AE12">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="AF12">
-        <v>3.3</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="AG12">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AH12">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AI12">
-        <v>3.13</v>
+        <v>4.09</v>
       </c>
       <c r="AJ12">
-        <v>2.9</v>
+        <v>3.73</v>
       </c>
       <c r="AK12">
-        <v>2.44</v>
+        <v>1.88</v>
       </c>
       <c r="AL12">
-        <v>3.15</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="AM12">
-        <v>2.98</v>
-      </c>
-      <c r="AN12"/>
-      <c r="AO12"/>
+        <v>4</v>
+      </c>
+      <c r="AN12">
+        <v>1.5</v>
+      </c>
+      <c r="AO12">
+        <v>2.63</v>
+      </c>
       <c r="AP12"/>
       <c r="AQ12"/>
       <c r="AR12">
-        <v>2.2000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="AS12">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AT12">
-        <v>2.09</v>
+        <v>1.48</v>
       </c>
       <c r="AU12">
-        <v>1.66</v>
+        <v>2.56</v>
       </c>
       <c r="AV12">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AW12">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AX12">
-        <v>-0.25</v>
-      </c>
-      <c r="AY12"/>
-      <c r="AZ12"/>
+        <v>-0.75</v>
+      </c>
+      <c r="AY12">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ12">
+        <v>1.83</v>
+      </c>
       <c r="BA12"/>
       <c r="BB12"/>
       <c r="BC12">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD12">
+        <v>1.83</v>
+      </c>
+      <c r="BE12">
+        <v>1.97</v>
+      </c>
+      <c r="BF12">
+        <v>1.77</v>
+      </c>
+      <c r="BG12">
+        <v>2.11</v>
+      </c>
+      <c r="BH12">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G13">
+        <v>1.29</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>9</v>
+      </c>
+      <c r="J13">
+        <v>1.29</v>
+      </c>
+      <c r="K13">
+        <v>6</v>
+      </c>
+      <c r="L13">
+        <v>9</v>
+      </c>
+      <c r="M13">
+        <v>1.27</v>
+      </c>
+      <c r="N13">
+        <v>5.8</v>
+      </c>
+      <c r="O13">
+        <v>8</v>
+      </c>
+      <c r="P13">
+        <v>1.25</v>
+      </c>
+      <c r="Q13">
+        <v>6</v>
+      </c>
+      <c r="R13">
+        <v>9.5</v>
+      </c>
+      <c r="S13">
+        <v>1.31</v>
+      </c>
+      <c r="T13">
+        <v>6.25</v>
+      </c>
+      <c r="U13">
+        <v>7.75</v>
+      </c>
+      <c r="V13">
+        <v>1.3</v>
+      </c>
+      <c r="W13">
+        <v>6</v>
+      </c>
+      <c r="X13">
+        <v>7.5</v>
+      </c>
+      <c r="Y13">
+        <v>1.3</v>
+      </c>
+      <c r="Z13">
+        <v>6</v>
+      </c>
+      <c r="AA13">
+        <v>7.5</v>
+      </c>
+      <c r="AB13"/>
+      <c r="AC13"/>
+      <c r="AD13"/>
+      <c r="AE13">
+        <v>1.31</v>
+      </c>
+      <c r="AF13">
+        <v>6.25</v>
+      </c>
+      <c r="AG13">
+        <v>9.5</v>
+      </c>
+      <c r="AH13">
+        <v>1.28</v>
+      </c>
+      <c r="AI13">
+        <v>5.93</v>
+      </c>
+      <c r="AJ13">
+        <v>8.39</v>
+      </c>
+      <c r="AK13">
+        <v>1.34</v>
+      </c>
+      <c r="AL13">
+        <v>6.6</v>
+      </c>
+      <c r="AM13">
+        <v>9.6</v>
+      </c>
+      <c r="AN13">
+        <v>1.3</v>
+      </c>
+      <c r="AO13">
+        <v>3.5</v>
+      </c>
+      <c r="AP13"/>
+      <c r="AQ13"/>
+      <c r="AR13">
+        <v>1.31</v>
+      </c>
+      <c r="AS13">
+        <v>3.55</v>
+      </c>
+      <c r="AT13">
+        <v>1.29</v>
+      </c>
+      <c r="AU13">
+        <v>3.38</v>
+      </c>
+      <c r="AV13">
+        <v>1.35</v>
+      </c>
+      <c r="AW13">
+        <v>3.7</v>
+      </c>
+      <c r="AX13">
+        <v>-1.75</v>
+      </c>
+      <c r="AY13">
+        <v>1.95</v>
+      </c>
+      <c r="AZ13">
+        <v>1.9</v>
+      </c>
+      <c r="BA13"/>
+      <c r="BB13"/>
+      <c r="BC13">
+        <v>1.95</v>
+      </c>
+      <c r="BD13">
+        <v>1.9</v>
+      </c>
+      <c r="BE13">
+        <v>1.9</v>
+      </c>
+      <c r="BF13">
+        <v>1.85</v>
+      </c>
+      <c r="BG13">
+        <v>1.97</v>
+      </c>
+      <c r="BH13">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14">
+        <v>3.3</v>
+      </c>
+      <c r="H14">
+        <v>3.75</v>
+      </c>
+      <c r="I14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="J14">
+        <v>3.1</v>
+      </c>
+      <c r="K14">
+        <v>3.75</v>
+      </c>
+      <c r="L14">
+        <v>2.1</v>
+      </c>
+      <c r="M14">
+        <v>3.25</v>
+      </c>
+      <c r="N14">
+        <v>3.6</v>
+      </c>
+      <c r="O14">
+        <v>1.98</v>
+      </c>
+      <c r="P14">
+        <v>3.13</v>
+      </c>
+      <c r="Q14">
+        <v>3.75</v>
+      </c>
+      <c r="R14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="S14">
+        <v>3.2</v>
+      </c>
+      <c r="T14">
+        <v>3.7</v>
+      </c>
+      <c r="U14">
+        <v>2.1</v>
+      </c>
+      <c r="V14">
+        <v>3.2</v>
+      </c>
+      <c r="W14">
+        <v>3.7</v>
+      </c>
+      <c r="X14">
+        <v>2.1</v>
+      </c>
+      <c r="Y14">
+        <v>3.2</v>
+      </c>
+      <c r="Z14">
+        <v>3.7</v>
+      </c>
+      <c r="AA14">
+        <v>2.1</v>
+      </c>
+      <c r="AB14"/>
+      <c r="AC14"/>
+      <c r="AD14"/>
+      <c r="AE14">
+        <v>3.3</v>
+      </c>
+      <c r="AF14">
+        <v>3.9</v>
+      </c>
+      <c r="AG14">
+        <v>2.1</v>
+      </c>
+      <c r="AH14">
+        <v>3.19</v>
+      </c>
+      <c r="AI14">
+        <v>3.72</v>
+      </c>
+      <c r="AJ14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AK14">
+        <v>3.5</v>
+      </c>
+      <c r="AL14">
+        <v>3.9</v>
+      </c>
+      <c r="AM14">
+        <v>2.16</v>
+      </c>
+      <c r="AN14">
+        <v>1.57</v>
+      </c>
+      <c r="AO14">
+        <v>2.38</v>
+      </c>
+      <c r="AP14"/>
+      <c r="AQ14"/>
+      <c r="AR14">
+        <v>1.61</v>
+      </c>
+      <c r="AS14">
+        <v>2.38</v>
+      </c>
+      <c r="AT14">
+        <v>1.56</v>
+      </c>
+      <c r="AU14">
+        <v>2.34</v>
+      </c>
+      <c r="AV14">
+        <v>1.63</v>
+      </c>
+      <c r="AW14">
+        <v>2.52</v>
+      </c>
+      <c r="AX14">
+        <v>0.25</v>
+      </c>
+      <c r="AY14">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ14">
+        <v>1.83</v>
+      </c>
+      <c r="BA14"/>
+      <c r="BB14"/>
+      <c r="BC14">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD14">
+        <v>1.83</v>
+      </c>
+      <c r="BE14">
+        <v>1.95</v>
+      </c>
+      <c r="BF14">
+        <v>1.79</v>
+      </c>
+      <c r="BG14">
+        <v>2.1</v>
+      </c>
+      <c r="BH14">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15">
+        <v>3.6</v>
+      </c>
+      <c r="H15">
+        <v>3.6</v>
+      </c>
+      <c r="I15">
         <v>2</v>
       </c>
-      <c r="BD12">
+      <c r="J15">
+        <v>3.5</v>
+      </c>
+      <c r="K15">
+        <v>3.6</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>3.5</v>
+      </c>
+      <c r="N15">
+        <v>3.4</v>
+      </c>
+      <c r="O15">
+        <v>1.97</v>
+      </c>
+      <c r="P15">
+        <v>3.5</v>
+      </c>
+      <c r="Q15">
+        <v>3.6</v>
+      </c>
+      <c r="R15">
+        <v>1.95</v>
+      </c>
+      <c r="S15">
+        <v>3.4</v>
+      </c>
+      <c r="T15">
+        <v>3.7</v>
+      </c>
+      <c r="U15">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="V15">
+        <v>3.4</v>
+      </c>
+      <c r="W15">
+        <v>3.7</v>
+      </c>
+      <c r="X15">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="Y15">
+        <v>3.4</v>
+      </c>
+      <c r="Z15">
+        <v>3.6</v>
+      </c>
+      <c r="AA15">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
+      <c r="AE15">
+        <v>3.65</v>
+      </c>
+      <c r="AF15">
+        <v>3.75</v>
+      </c>
+      <c r="AG15">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AH15">
+        <v>3.47</v>
+      </c>
+      <c r="AI15">
+        <v>3.59</v>
+      </c>
+      <c r="AJ15">
+        <v>1.99</v>
+      </c>
+      <c r="AK15">
+        <v>3.7</v>
+      </c>
+      <c r="AL15">
+        <v>3.9</v>
+      </c>
+      <c r="AM15">
+        <v>2.1</v>
+      </c>
+      <c r="AN15">
+        <v>1.73</v>
+      </c>
+      <c r="AO15">
+        <v>2.1</v>
+      </c>
+      <c r="AP15"/>
+      <c r="AQ15"/>
+      <c r="AR15">
+        <v>1.79</v>
+      </c>
+      <c r="AS15">
+        <v>2.1</v>
+      </c>
+      <c r="AT15">
+        <v>1.73</v>
+      </c>
+      <c r="AU15">
+        <v>2.04</v>
+      </c>
+      <c r="AV15">
+        <v>1.81</v>
+      </c>
+      <c r="AW15">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="AX15">
+        <v>0.5</v>
+      </c>
+      <c r="AY15">
+        <v>1.85</v>
+      </c>
+      <c r="AZ15">
+        <v>2</v>
+      </c>
+      <c r="BA15"/>
+      <c r="BB15"/>
+      <c r="BC15">
+        <v>1.85</v>
+      </c>
+      <c r="BD15">
+        <v>2</v>
+      </c>
+      <c r="BE15">
+        <v>1.79</v>
+      </c>
+      <c r="BF15">
+        <v>1.94</v>
+      </c>
+      <c r="BG15">
+        <v>1.9</v>
+      </c>
+      <c r="BH15">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:114" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16">
+        <v>1.91</v>
+      </c>
+      <c r="H16">
+        <v>3.75</v>
+      </c>
+      <c r="I16">
+        <v>3.8</v>
+      </c>
+      <c r="J16">
+        <v>1.91</v>
+      </c>
+      <c r="K16">
+        <v>3.75</v>
+      </c>
+      <c r="L16">
+        <v>3.75</v>
+      </c>
+      <c r="M16">
+        <v>1.87</v>
+      </c>
+      <c r="N16">
+        <v>3.45</v>
+      </c>
+      <c r="O16">
+        <v>3.8</v>
+      </c>
+      <c r="P16">
+        <v>1.87</v>
+      </c>
+      <c r="Q16">
+        <v>3.6</v>
+      </c>
+      <c r="R16">
+        <v>3.8</v>
+      </c>
+      <c r="S16">
+        <v>1.93</v>
+      </c>
+      <c r="T16">
+        <v>3.7</v>
+      </c>
+      <c r="U16">
+        <v>3.7</v>
+      </c>
+      <c r="V16">
+        <v>1.95</v>
+      </c>
+      <c r="W16">
+        <v>3.7</v>
+      </c>
+      <c r="X16">
+        <v>3.7</v>
+      </c>
+      <c r="Y16">
+        <v>1.91</v>
+      </c>
+      <c r="Z16">
+        <v>3.7</v>
+      </c>
+      <c r="AA16">
+        <v>3.7</v>
+      </c>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16">
+        <v>1.95</v>
+      </c>
+      <c r="AF16">
+        <v>3.75</v>
+      </c>
+      <c r="AG16">
+        <v>4.3</v>
+      </c>
+      <c r="AH16">
+        <v>1.89</v>
+      </c>
+      <c r="AI16">
+        <v>3.63</v>
+      </c>
+      <c r="AJ16">
+        <v>3.78</v>
+      </c>
+      <c r="AK16">
+        <v>1.97</v>
+      </c>
+      <c r="AL16">
+        <v>3.85</v>
+      </c>
+      <c r="AM16">
+        <v>4.2</v>
+      </c>
+      <c r="AN16">
+        <v>1.73</v>
+      </c>
+      <c r="AO16">
+        <v>2.1</v>
+      </c>
+      <c r="AP16"/>
+      <c r="AQ16"/>
+      <c r="AR16">
+        <v>1.76</v>
+      </c>
+      <c r="AS16">
+        <v>2.12</v>
+      </c>
+      <c r="AT16">
+        <v>1.73</v>
+      </c>
+      <c r="AU16">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AV16">
+        <v>1.83</v>
+      </c>
+      <c r="AW16">
+        <v>2.14</v>
+      </c>
+      <c r="AX16">
+        <v>-0.5</v>
+      </c>
+      <c r="AY16">
+        <v>1.88</v>
+      </c>
+      <c r="AZ16">
+        <v>1.98</v>
+      </c>
+      <c r="BA16"/>
+      <c r="BB16"/>
+      <c r="BC16">
+        <v>1.9</v>
+      </c>
+      <c r="BD16">
+        <v>1.98</v>
+      </c>
+      <c r="BE16">
+        <v>1.85</v>
+      </c>
+      <c r="BF16">
+        <v>1.87</v>
+      </c>
+      <c r="BG16">
+        <v>1.94</v>
+      </c>
+      <c r="BH16">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="17" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17">
+        <v>1.85</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>3.75</v>
+      </c>
+      <c r="J17">
+        <v>1.83</v>
+      </c>
+      <c r="K17">
+        <v>3.75</v>
+      </c>
+      <c r="L17">
+        <v>4</v>
+      </c>
+      <c r="M17">
+        <v>1.77</v>
+      </c>
+      <c r="N17">
+        <v>3.9</v>
+      </c>
+      <c r="O17">
+        <v>3.7</v>
+      </c>
+      <c r="P17">
+        <v>1.83</v>
+      </c>
+      <c r="Q17">
+        <v>3.75</v>
+      </c>
+      <c r="R17">
+        <v>3.8</v>
+      </c>
+      <c r="S17">
+        <v>1.85</v>
+      </c>
+      <c r="T17">
+        <v>3.9</v>
+      </c>
+      <c r="U17">
+        <v>3.8</v>
+      </c>
+      <c r="V17">
+        <v>1.85</v>
+      </c>
+      <c r="W17">
+        <v>3.9</v>
+      </c>
+      <c r="X17">
+        <v>3.8</v>
+      </c>
+      <c r="Y17">
+        <v>1.85</v>
+      </c>
+      <c r="Z17">
+        <v>3.8</v>
+      </c>
+      <c r="AA17">
+        <v>3.8</v>
+      </c>
+      <c r="AB17"/>
+      <c r="AC17"/>
+      <c r="AD17"/>
+      <c r="AE17">
+        <v>1.88</v>
+      </c>
+      <c r="AF17">
+        <v>4.2</v>
+      </c>
+      <c r="AG17">
+        <v>4</v>
+      </c>
+      <c r="AH17">
+        <v>1.82</v>
+      </c>
+      <c r="AI17">
+        <v>3.9</v>
+      </c>
+      <c r="AJ17">
+        <v>3.75</v>
+      </c>
+      <c r="AK17">
+        <v>1.91</v>
+      </c>
+      <c r="AL17">
+        <v>4.2</v>
+      </c>
+      <c r="AM17">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AN17">
+        <v>1.67</v>
+      </c>
+      <c r="AO17">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AP17"/>
+      <c r="AQ17"/>
+      <c r="AR17">
+        <v>1.67</v>
+      </c>
+      <c r="AS17">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AT17">
+        <v>1.64</v>
+      </c>
+      <c r="AU17">
+        <v>2.19</v>
+      </c>
+      <c r="AV17">
+        <v>1.72</v>
+      </c>
+      <c r="AW17">
+        <v>2.34</v>
+      </c>
+      <c r="AX17">
+        <v>-0.5</v>
+      </c>
+      <c r="AY17">
+        <v>1.85</v>
+      </c>
+      <c r="AZ17">
+        <v>2</v>
+      </c>
+      <c r="BA17"/>
+      <c r="BB17"/>
+      <c r="BC17">
+        <v>1.85</v>
+      </c>
+      <c r="BD17">
+        <v>2</v>
+      </c>
+      <c r="BE17">
+        <v>1.79</v>
+      </c>
+      <c r="BF17">
+        <v>1.92</v>
+      </c>
+      <c r="BG17">
+        <v>1.91</v>
+      </c>
+      <c r="BH17">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="18" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D18" t="s">
+        <v>211</v>
+      </c>
+      <c r="E18" t="s">
+        <v>214</v>
+      </c>
+      <c r="F18"/>
+      <c r="G18">
+        <v>2.7</v>
+      </c>
+      <c r="H18">
+        <v>3.5</v>
+      </c>
+      <c r="I18">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="J18">
+        <v>2.63</v>
+      </c>
+      <c r="K18">
+        <v>3.5</v>
+      </c>
+      <c r="L18">
+        <v>2.5</v>
+      </c>
+      <c r="M18">
+        <v>2.63</v>
+      </c>
+      <c r="N18">
+        <v>3.25</v>
+      </c>
+      <c r="O18">
+        <v>2.4</v>
+      </c>
+      <c r="P18">
+        <v>2.7</v>
+      </c>
+      <c r="Q18">
+        <v>3.5</v>
+      </c>
+      <c r="R18">
+        <v>2.5</v>
+      </c>
+      <c r="S18">
+        <v>2.65</v>
+      </c>
+      <c r="T18">
+        <v>3.4</v>
+      </c>
+      <c r="U18">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="V18">
+        <v>2.7</v>
+      </c>
+      <c r="W18">
+        <v>3.4</v>
+      </c>
+      <c r="X18">
+        <v>2.6</v>
+      </c>
+      <c r="Y18">
+        <v>2.62</v>
+      </c>
+      <c r="Z18">
+        <v>3.4</v>
+      </c>
+      <c r="AA18">
+        <v>2.5</v>
+      </c>
+      <c r="AB18"/>
+      <c r="AC18"/>
+      <c r="AD18"/>
+      <c r="AE18">
+        <v>2.72</v>
+      </c>
+      <c r="AF18">
+        <v>3.6</v>
+      </c>
+      <c r="AG18">
+        <v>2.6</v>
+      </c>
+      <c r="AH18">
+        <v>2.65</v>
+      </c>
+      <c r="AI18">
+        <v>3.43</v>
+      </c>
+      <c r="AJ18">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="AK18">
+        <v>2.82</v>
+      </c>
+      <c r="AL18">
+        <v>3.65</v>
+      </c>
+      <c r="AM18">
+        <v>2.62</v>
+      </c>
+      <c r="AN18">
+        <v>1.67</v>
+      </c>
+      <c r="AO18">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AP18"/>
+      <c r="AQ18"/>
+      <c r="AR18">
+        <v>1.68</v>
+      </c>
+      <c r="AS18">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AT18">
+        <v>1.65</v>
+      </c>
+      <c r="AU18">
+        <v>2.19</v>
+      </c>
+      <c r="AV18">
+        <v>1.72</v>
+      </c>
+      <c r="AW18">
+        <v>2.36</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>2</v>
+      </c>
+      <c r="AZ18">
+        <v>1.85</v>
+      </c>
+      <c r="BA18"/>
+      <c r="BB18"/>
+      <c r="BC18">
+        <v>2</v>
+      </c>
+      <c r="BD18">
+        <v>1.85</v>
+      </c>
+      <c r="BE18">
+        <v>1.94</v>
+      </c>
+      <c r="BF18">
+        <v>1.81</v>
+      </c>
+      <c r="BG18">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="BH18">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D19" t="s">
+        <v>209</v>
+      </c>
+      <c r="E19" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19">
+        <v>3.1</v>
+      </c>
+      <c r="H19">
+        <v>3.6</v>
+      </c>
+      <c r="I19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J19">
+        <v>2.88</v>
+      </c>
+      <c r="K19">
+        <v>3.75</v>
+      </c>
+      <c r="L19">
+        <v>2.25</v>
+      </c>
+      <c r="M19">
+        <v>2.85</v>
+      </c>
+      <c r="N19">
+        <v>3.45</v>
+      </c>
+      <c r="O19">
+        <v>2.15</v>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <v>3.75</v>
+      </c>
+      <c r="R19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S19">
+        <v>3</v>
+      </c>
+      <c r="T19">
+        <v>3.75</v>
+      </c>
+      <c r="U19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="V19">
+        <v>3</v>
+      </c>
+      <c r="W19">
+        <v>3.75</v>
+      </c>
+      <c r="X19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Y19">
+        <v>3</v>
+      </c>
+      <c r="Z19">
+        <v>3.75</v>
+      </c>
+      <c r="AA19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
+      <c r="AE19">
+        <v>3.1</v>
+      </c>
+      <c r="AF19">
+        <v>3.75</v>
+      </c>
+      <c r="AG19">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AH19">
+        <v>2.95</v>
+      </c>
+      <c r="AI19">
+        <v>3.64</v>
+      </c>
+      <c r="AJ19">
+        <v>2.19</v>
+      </c>
+      <c r="AK19">
+        <v>3.2</v>
+      </c>
+      <c r="AL19">
+        <v>3.8</v>
+      </c>
+      <c r="AM19">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="AN19">
+        <v>1.57</v>
+      </c>
+      <c r="AO19">
+        <v>2.38</v>
+      </c>
+      <c r="AP19"/>
+      <c r="AQ19"/>
+      <c r="AR19">
+        <v>1.57</v>
+      </c>
+      <c r="AS19">
+        <v>2.5</v>
+      </c>
+      <c r="AT19">
+        <v>1.55</v>
+      </c>
+      <c r="AU19">
+        <v>2.36</v>
+      </c>
+      <c r="AV19">
+        <v>1.63</v>
+      </c>
+      <c r="AW19">
+        <v>2.52</v>
+      </c>
+      <c r="AX19">
+        <v>0.25</v>
+      </c>
+      <c r="AY19">
+        <v>1.9</v>
+      </c>
+      <c r="AZ19">
+        <v>1.95</v>
+      </c>
+      <c r="BA19"/>
+      <c r="BB19"/>
+      <c r="BC19">
+        <v>1.9</v>
+      </c>
+      <c r="BD19">
+        <v>1.95</v>
+      </c>
+      <c r="BE19">
+        <v>1.85</v>
+      </c>
+      <c r="BF19">
+        <v>1.9</v>
+      </c>
+      <c r="BG19">
+        <v>1.96</v>
+      </c>
+      <c r="BH19">
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D20" t="s">
+        <v>213</v>
+      </c>
+      <c r="E20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20">
+        <v>1.55</v>
+      </c>
+      <c r="H20">
+        <v>4.2</v>
+      </c>
+      <c r="I20">
+        <v>6</v>
+      </c>
+      <c r="J20">
+        <v>1.53</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <v>6</v>
+      </c>
+      <c r="M20">
+        <v>1.5</v>
+      </c>
+      <c r="N20">
+        <v>3.9</v>
+      </c>
+      <c r="O20">
+        <v>5.6</v>
+      </c>
+      <c r="P20">
+        <v>1.53</v>
+      </c>
+      <c r="Q20">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="R20">
+        <v>6</v>
+      </c>
+      <c r="S20">
+        <v>1.55</v>
+      </c>
+      <c r="T20">
+        <v>4.33</v>
+      </c>
+      <c r="U20">
+        <v>5.5</v>
+      </c>
+      <c r="V20">
+        <v>1.55</v>
+      </c>
+      <c r="W20">
+        <v>4.33</v>
+      </c>
+      <c r="X20">
+        <v>5.5</v>
+      </c>
+      <c r="Y20">
+        <v>1.53</v>
+      </c>
+      <c r="Z20">
+        <v>4.33</v>
+      </c>
+      <c r="AA20">
+        <v>5.5</v>
+      </c>
+      <c r="AB20"/>
+      <c r="AC20"/>
+      <c r="AD20"/>
+      <c r="AE20">
+        <v>1.55</v>
+      </c>
+      <c r="AF20">
+        <v>4.5</v>
+      </c>
+      <c r="AG20">
+        <v>6.6</v>
+      </c>
+      <c r="AH20">
+        <v>1.52</v>
+      </c>
+      <c r="AI20">
+        <v>4.16</v>
+      </c>
+      <c r="AJ20">
+        <v>5.76</v>
+      </c>
+      <c r="AK20">
+        <v>1.59</v>
+      </c>
+      <c r="AL20">
+        <v>4.5</v>
+      </c>
+      <c r="AM20">
+        <v>6.6</v>
+      </c>
+      <c r="AN20">
         <v>1.8</v>
       </c>
-      <c r="BE12">
+      <c r="AO20">
+        <v>2</v>
+      </c>
+      <c r="AP20"/>
+      <c r="AQ20"/>
+      <c r="AR20">
+        <v>1.8</v>
+      </c>
+      <c r="AS20">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AT20">
+        <v>1.76</v>
+      </c>
+      <c r="AU20">
+        <v>2</v>
+      </c>
+      <c r="AV20">
+        <v>1.83</v>
+      </c>
+      <c r="AW20">
+        <v>2.16</v>
+      </c>
+      <c r="AX20">
+        <v>-1</v>
+      </c>
+      <c r="AY20">
+        <v>1.93</v>
+      </c>
+      <c r="AZ20">
+        <v>1.93</v>
+      </c>
+      <c r="BA20"/>
+      <c r="BB20"/>
+      <c r="BC20">
+        <v>1.93</v>
+      </c>
+      <c r="BD20">
+        <v>1.95</v>
+      </c>
+      <c r="BE20">
+        <v>1.86</v>
+      </c>
+      <c r="BF20">
+        <v>1.89</v>
+      </c>
+      <c r="BG20">
+        <v>1.99</v>
+      </c>
+      <c r="BH20">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" t="s">
+        <v>204</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21">
+        <v>2.7</v>
+      </c>
+      <c r="H21">
+        <v>3.4</v>
+      </c>
+      <c r="I21">
+        <v>2.63</v>
+      </c>
+      <c r="J21">
+        <v>2.63</v>
+      </c>
+      <c r="K21">
+        <v>3.4</v>
+      </c>
+      <c r="L21">
+        <v>2.6</v>
+      </c>
+      <c r="M21">
+        <v>2.63</v>
+      </c>
+      <c r="N21">
+        <v>3.15</v>
+      </c>
+      <c r="O21">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="P21">
+        <v>2.6</v>
+      </c>
+      <c r="Q21">
+        <v>3.4</v>
+      </c>
+      <c r="R21">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="S21">
+        <v>2.65</v>
+      </c>
+      <c r="T21">
+        <v>3.4</v>
+      </c>
+      <c r="U21">
+        <v>2.6</v>
+      </c>
+      <c r="V21">
+        <v>2.5</v>
+      </c>
+      <c r="W21">
+        <v>3.2</v>
+      </c>
+      <c r="X21">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Y21">
+        <v>2.5</v>
+      </c>
+      <c r="Z21">
+        <v>3.2</v>
+      </c>
+      <c r="AA21">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="AB21"/>
+      <c r="AC21"/>
+      <c r="AD21"/>
+      <c r="AE21">
+        <v>2.7</v>
+      </c>
+      <c r="AF21">
+        <v>3.45</v>
+      </c>
+      <c r="AG21">
+        <v>2.68</v>
+      </c>
+      <c r="AH21">
+        <v>2.61</v>
+      </c>
+      <c r="AI21">
+        <v>3.3</v>
+      </c>
+      <c r="AJ21">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AK21">
+        <v>2.8</v>
+      </c>
+      <c r="AL21">
+        <v>3.4</v>
+      </c>
+      <c r="AM21">
+        <v>2.78</v>
+      </c>
+      <c r="AN21">
+        <v>1.9</v>
+      </c>
+      <c r="AO21">
+        <v>1.95</v>
+      </c>
+      <c r="AP21"/>
+      <c r="AQ21"/>
+      <c r="AR21">
+        <v>1.91</v>
+      </c>
+      <c r="AS21">
+        <v>1.95</v>
+      </c>
+      <c r="AT21">
+        <v>1.87</v>
+      </c>
+      <c r="AU21">
+        <v>1.87</v>
+      </c>
+      <c r="AV21">
+        <v>1.97</v>
+      </c>
+      <c r="AW21">
+        <v>2</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>1.95</v>
+      </c>
+      <c r="AZ21">
+        <v>1.9</v>
+      </c>
+      <c r="BA21"/>
+      <c r="BB21"/>
+      <c r="BC21">
+        <v>1.95</v>
+      </c>
+      <c r="BD21">
+        <v>1.9</v>
+      </c>
+      <c r="BE21">
+        <v>1.88</v>
+      </c>
+      <c r="BF21">
+        <v>1.85</v>
+      </c>
+      <c r="BG21">
+        <v>1.99</v>
+      </c>
+      <c r="BH21">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D22" t="s">
+        <v>205</v>
+      </c>
+      <c r="E22" t="s">
+        <v>218</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22">
+        <v>1.48</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>8</v>
+      </c>
+      <c r="J22">
+        <v>1.5</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>7</v>
+      </c>
+      <c r="M22">
+        <v>1.45</v>
+      </c>
+      <c r="N22">
+        <v>3.9</v>
+      </c>
+      <c r="O22">
+        <v>6.4</v>
+      </c>
+      <c r="P22">
+        <v>1.45</v>
+      </c>
+      <c r="Q22">
+        <v>4.2</v>
+      </c>
+      <c r="R22">
+        <v>7</v>
+      </c>
+      <c r="S22">
+        <v>1.5</v>
+      </c>
+      <c r="T22">
+        <v>4.2</v>
+      </c>
+      <c r="U22">
+        <v>6.75</v>
+      </c>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22">
+        <v>1.5</v>
+      </c>
+      <c r="Z22">
+        <v>4.2</v>
+      </c>
+      <c r="AA22">
+        <v>6.5</v>
+      </c>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22">
+        <v>1.5</v>
+      </c>
+      <c r="AF22">
+        <v>4.33</v>
+      </c>
+      <c r="AG22">
+        <v>8</v>
+      </c>
+      <c r="AH22">
+        <v>1.47</v>
+      </c>
+      <c r="AI22">
+        <v>4.07</v>
+      </c>
+      <c r="AJ22">
+        <v>6.72</v>
+      </c>
+      <c r="AK22">
+        <v>1.53</v>
+      </c>
+      <c r="AL22">
+        <v>4.3</v>
+      </c>
+      <c r="AM22">
+        <v>7.8</v>
+      </c>
+      <c r="AN22">
+        <v>1.9</v>
+      </c>
+      <c r="AO22">
+        <v>1.95</v>
+      </c>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+      <c r="AR22">
+        <v>1.91</v>
+      </c>
+      <c r="AS22">
+        <v>1.95</v>
+      </c>
+      <c r="AT22">
+        <v>1.87</v>
+      </c>
+      <c r="AU22">
+        <v>1.86</v>
+      </c>
+      <c r="AV22">
         <v>1.96</v>
       </c>
-      <c r="BF12">
+      <c r="AW22">
+        <v>1.99</v>
+      </c>
+      <c r="AX22">
+        <v>-1</v>
+      </c>
+      <c r="AY22">
+        <v>1.8</v>
+      </c>
+      <c r="AZ22">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BA22"/>
+      <c r="BB22"/>
+      <c r="BC22">
+        <v>1.8</v>
+      </c>
+      <c r="BD22">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BE22">
         <v>1.76</v>
       </c>
-      <c r="BG12"/>
-      <c r="BH12"/>
+      <c r="BF22">
+        <v>1.99</v>
+      </c>
+      <c r="BG22">
+        <v>1.86</v>
+      </c>
+      <c r="BH22">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="23" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D23" t="s">
+        <v>207</v>
+      </c>
+      <c r="E23" t="s">
+        <v>212</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23">
+        <v>5.25</v>
+      </c>
+      <c r="H23">
+        <v>4.33</v>
+      </c>
+      <c r="I23">
+        <v>1.57</v>
+      </c>
+      <c r="J23">
+        <v>5.5</v>
+      </c>
+      <c r="K23">
+        <v>4.2</v>
+      </c>
+      <c r="L23">
+        <v>1.57</v>
+      </c>
+      <c r="M23">
+        <v>5.3</v>
+      </c>
+      <c r="N23">
+        <v>3.8</v>
+      </c>
+      <c r="O23">
+        <v>1.53</v>
+      </c>
+      <c r="P23">
+        <v>5.5</v>
+      </c>
+      <c r="Q23">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="R23">
+        <v>1.55</v>
+      </c>
+      <c r="S23">
+        <v>5.25</v>
+      </c>
+      <c r="T23">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="U23">
+        <v>1.6</v>
+      </c>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23">
+        <v>5.25</v>
+      </c>
+      <c r="Z23">
+        <v>4</v>
+      </c>
+      <c r="AA23">
+        <v>1.6</v>
+      </c>
+      <c r="AB23"/>
+      <c r="AC23"/>
+      <c r="AD23"/>
+      <c r="AE23">
+        <v>5.66</v>
+      </c>
+      <c r="AF23">
+        <v>4.33</v>
+      </c>
+      <c r="AG23">
+        <v>1.6</v>
+      </c>
+      <c r="AH23">
+        <v>5.33</v>
+      </c>
+      <c r="AI23">
+        <v>4.05</v>
+      </c>
+      <c r="AJ23">
+        <v>1.55</v>
+      </c>
+      <c r="AK23">
+        <v>5.9</v>
+      </c>
+      <c r="AL23">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AM23">
+        <v>1.63</v>
+      </c>
+      <c r="AN23">
+        <v>1.67</v>
+      </c>
+      <c r="AO23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+      <c r="AR23">
+        <v>1.73</v>
+      </c>
+      <c r="AS23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AT23">
+        <v>1.67</v>
+      </c>
+      <c r="AU23">
+        <v>2.13</v>
+      </c>
+      <c r="AV23">
+        <v>1.72</v>
+      </c>
+      <c r="AW23">
+        <v>2.34</v>
+      </c>
+      <c r="AX23">
+        <v>1</v>
+      </c>
+      <c r="AY23">
+        <v>1.88</v>
+      </c>
+      <c r="AZ23">
+        <v>1.98</v>
+      </c>
+      <c r="BA23"/>
+      <c r="BB23"/>
+      <c r="BC23">
+        <v>1.9</v>
+      </c>
+      <c r="BD23">
+        <v>1.98</v>
+      </c>
+      <c r="BE23">
+        <v>1.84</v>
+      </c>
+      <c r="BF23">
+        <v>1.92</v>
+      </c>
+      <c r="BG23">
+        <v>1.9</v>
+      </c>
+      <c r="BH23">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="24" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D24" t="s">
+        <v>203</v>
+      </c>
+      <c r="E24" t="s">
+        <v>202</v>
+      </c>
+      <c r="F24"/>
+      <c r="G24">
+        <v>1.75</v>
+      </c>
+      <c r="H24">
+        <v>3.5</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24">
+        <v>1.8</v>
+      </c>
+      <c r="K24">
+        <v>3.4</v>
+      </c>
+      <c r="L24">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="M24">
+        <v>1.66</v>
+      </c>
+      <c r="N24">
+        <v>3.4</v>
+      </c>
+      <c r="O24">
+        <v>4.8</v>
+      </c>
+      <c r="P24">
+        <v>1.73</v>
+      </c>
+      <c r="Q24">
+        <v>3.4</v>
+      </c>
+      <c r="R24">
+        <v>5</v>
+      </c>
+      <c r="S24">
+        <v>1.77</v>
+      </c>
+      <c r="T24">
+        <v>3.4</v>
+      </c>
+      <c r="U24">
+        <v>5</v>
+      </c>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24"/>
+      <c r="Y24">
+        <v>1.75</v>
+      </c>
+      <c r="Z24">
+        <v>3.4</v>
+      </c>
+      <c r="AA24">
+        <v>5</v>
+      </c>
+      <c r="AB24"/>
+      <c r="AC24"/>
+      <c r="AD24"/>
+      <c r="AE24">
+        <v>1.8</v>
+      </c>
+      <c r="AF24">
+        <v>3.5</v>
+      </c>
+      <c r="AG24">
+        <v>5</v>
+      </c>
+      <c r="AH24">
+        <v>1.73</v>
+      </c>
+      <c r="AI24">
+        <v>3.42</v>
+      </c>
+      <c r="AJ24">
+        <v>4.84</v>
+      </c>
+      <c r="AK24">
+        <v>1.85</v>
+      </c>
+      <c r="AL24">
+        <v>3.65</v>
+      </c>
+      <c r="AM24">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AN24">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AO24">
+        <v>1.62</v>
+      </c>
+      <c r="AP24"/>
+      <c r="AQ24"/>
+      <c r="AR24">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AS24">
+        <v>1.62</v>
+      </c>
+      <c r="AT24">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AU24">
+        <v>1.59</v>
+      </c>
+      <c r="AV24">
+        <v>2.44</v>
+      </c>
+      <c r="AW24">
+        <v>1.66</v>
+      </c>
+      <c r="AX24">
+        <v>-0.75</v>
+      </c>
+      <c r="AY24">
+        <v>2</v>
+      </c>
+      <c r="AZ24">
+        <v>1.85</v>
+      </c>
+      <c r="BA24"/>
+      <c r="BB24"/>
+      <c r="BC24">
+        <v>2</v>
+      </c>
+      <c r="BD24">
+        <v>1.85</v>
+      </c>
+      <c r="BE24">
+        <v>1.94</v>
+      </c>
+      <c r="BF24">
+        <v>1.8</v>
+      </c>
+      <c r="BG24">
+        <v>2.11</v>
+      </c>
+      <c r="BH24">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D25" t="s">
+        <v>206</v>
+      </c>
+      <c r="E25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F25"/>
+      <c r="G25">
+        <v>1.29</v>
+      </c>
+      <c r="H25">
+        <v>5.5</v>
+      </c>
+      <c r="I25">
+        <v>11</v>
+      </c>
+      <c r="J25">
+        <v>1.29</v>
+      </c>
+      <c r="K25">
+        <v>5</v>
+      </c>
+      <c r="L25">
+        <v>11</v>
+      </c>
+      <c r="M25">
+        <v>1.25</v>
+      </c>
+      <c r="N25">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O25">
+        <v>9.5</v>
+      </c>
+      <c r="P25">
+        <v>1.25</v>
+      </c>
+      <c r="Q25">
+        <v>5.5</v>
+      </c>
+      <c r="R25">
+        <v>11</v>
+      </c>
+      <c r="S25">
+        <v>1.29</v>
+      </c>
+      <c r="T25">
+        <v>5.75</v>
+      </c>
+      <c r="U25">
+        <v>10</v>
+      </c>
+      <c r="V25"/>
+      <c r="W25"/>
+      <c r="X25"/>
+      <c r="Y25">
+        <v>1.28</v>
+      </c>
+      <c r="Z25">
+        <v>5.75</v>
+      </c>
+      <c r="AA25">
+        <v>10</v>
+      </c>
+      <c r="AB25"/>
+      <c r="AC25"/>
+      <c r="AD25"/>
+      <c r="AE25">
+        <v>1.29</v>
+      </c>
+      <c r="AF25">
+        <v>5.75</v>
+      </c>
+      <c r="AG25">
+        <v>11</v>
+      </c>
+      <c r="AH25">
+        <v>1.26</v>
+      </c>
+      <c r="AI25">
+        <v>5.3</v>
+      </c>
+      <c r="AJ25">
+        <v>10.35</v>
+      </c>
+      <c r="AK25">
+        <v>1.32</v>
+      </c>
+      <c r="AL25">
+        <v>5.9</v>
+      </c>
+      <c r="AM25">
+        <v>12</v>
+      </c>
+      <c r="AN25">
+        <v>1.67</v>
+      </c>
+      <c r="AO25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AP25"/>
+      <c r="AQ25"/>
+      <c r="AR25">
+        <v>1.73</v>
+      </c>
+      <c r="AS25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AT25">
+        <v>1.66</v>
+      </c>
+      <c r="AU25">
+        <v>2.14</v>
+      </c>
+      <c r="AV25">
+        <v>1.76</v>
+      </c>
+      <c r="AW25">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AX25">
+        <v>-1.5</v>
+      </c>
+      <c r="AY25">
+        <v>1.85</v>
+      </c>
+      <c r="AZ25">
+        <v>2</v>
+      </c>
+      <c r="BA25"/>
+      <c r="BB25"/>
+      <c r="BC25">
+        <v>1.85</v>
+      </c>
+      <c r="BD25">
+        <v>2</v>
+      </c>
+      <c r="BE25">
+        <v>1.8</v>
+      </c>
+      <c r="BF25">
+        <v>1.91</v>
+      </c>
+      <c r="BG25">
+        <v>1.91</v>
+      </c>
+      <c r="BH25">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="26" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D26" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" t="s">
+        <v>216</v>
+      </c>
+      <c r="F26"/>
+      <c r="G26">
+        <v>7.5</v>
+      </c>
+      <c r="H26">
+        <v>4.5</v>
+      </c>
+      <c r="I26">
+        <v>1.42</v>
+      </c>
+      <c r="J26">
+        <v>7.5</v>
+      </c>
+      <c r="K26">
+        <v>4.5</v>
+      </c>
+      <c r="L26">
+        <v>1.4</v>
+      </c>
+      <c r="M26">
+        <v>7</v>
+      </c>
+      <c r="N26">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="O26">
+        <v>1.36</v>
+      </c>
+      <c r="P26">
+        <v>7.5</v>
+      </c>
+      <c r="Q26">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R26">
+        <v>1.4</v>
+      </c>
+      <c r="S26">
+        <v>7</v>
+      </c>
+      <c r="T26">
+        <v>4.75</v>
+      </c>
+      <c r="U26">
+        <v>1.43</v>
+      </c>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+      <c r="Y26">
+        <v>7</v>
+      </c>
+      <c r="Z26">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AA26">
+        <v>1.44</v>
+      </c>
+      <c r="AB26"/>
+      <c r="AC26"/>
+      <c r="AD26"/>
+      <c r="AE26">
+        <v>7.5</v>
+      </c>
+      <c r="AF26">
+        <v>4.75</v>
+      </c>
+      <c r="AG26">
+        <v>1.44</v>
+      </c>
+      <c r="AH26">
+        <v>7.23</v>
+      </c>
+      <c r="AI26">
+        <v>4.45</v>
+      </c>
+      <c r="AJ26">
+        <v>1.4</v>
+      </c>
+      <c r="AK26">
+        <v>8.6</v>
+      </c>
+      <c r="AL26">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AM26">
+        <v>1.47</v>
+      </c>
+      <c r="AN26">
+        <v>1.73</v>
+      </c>
+      <c r="AO26">
+        <v>2.1</v>
+      </c>
+      <c r="AP26"/>
+      <c r="AQ26"/>
+      <c r="AR26">
+        <v>1.75</v>
+      </c>
+      <c r="AS26">
+        <v>2.1</v>
+      </c>
+      <c r="AT26">
+        <v>1.72</v>
+      </c>
+      <c r="AU26">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AV26">
+        <v>1.81</v>
+      </c>
+      <c r="AW26">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="AX26">
+        <v>1.25</v>
+      </c>
+      <c r="AY26">
+        <v>1.88</v>
+      </c>
+      <c r="AZ26">
+        <v>1.98</v>
+      </c>
+      <c r="BA26"/>
+      <c r="BB26"/>
+      <c r="BC26">
+        <v>1.88</v>
+      </c>
+      <c r="BD26">
+        <v>1.98</v>
+      </c>
+      <c r="BE26">
+        <v>1.83</v>
+      </c>
+      <c r="BF26">
+        <v>1.93</v>
+      </c>
+      <c r="BG26">
+        <v>1.93</v>
+      </c>
+      <c r="BH26">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D27" t="s">
+        <v>219</v>
+      </c>
+      <c r="E27" t="s">
+        <v>208</v>
+      </c>
+      <c r="F27"/>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27">
+        <v>5.5</v>
+      </c>
+      <c r="I27">
+        <v>1.3</v>
+      </c>
+      <c r="J27">
+        <v>11</v>
+      </c>
+      <c r="K27">
+        <v>5</v>
+      </c>
+      <c r="L27">
+        <v>1.3</v>
+      </c>
+      <c r="M27">
+        <v>9</v>
+      </c>
+      <c r="N27">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O27">
+        <v>1.29</v>
+      </c>
+      <c r="P27">
+        <v>10.5</v>
+      </c>
+      <c r="Q27">
+        <v>5</v>
+      </c>
+      <c r="R27">
+        <v>1.29</v>
+      </c>
+      <c r="S27">
+        <v>9</v>
+      </c>
+      <c r="T27">
+        <v>5</v>
+      </c>
+      <c r="U27">
+        <v>1.34</v>
+      </c>
+      <c r="V27">
+        <v>9</v>
+      </c>
+      <c r="W27">
+        <v>5</v>
+      </c>
+      <c r="X27">
+        <v>1.35</v>
+      </c>
+      <c r="Y27">
+        <v>9</v>
+      </c>
+      <c r="Z27">
+        <v>5</v>
+      </c>
+      <c r="AA27">
+        <v>1.33</v>
+      </c>
+      <c r="AB27"/>
+      <c r="AC27"/>
+      <c r="AD27"/>
+      <c r="AE27">
+        <v>13</v>
+      </c>
+      <c r="AF27">
+        <v>5.5</v>
+      </c>
+      <c r="AG27">
+        <v>1.35</v>
+      </c>
+      <c r="AH27">
+        <v>9.84</v>
+      </c>
+      <c r="AI27">
+        <v>5.01</v>
+      </c>
+      <c r="AJ27">
+        <v>1.3</v>
+      </c>
+      <c r="AK27">
+        <v>12</v>
+      </c>
+      <c r="AL27">
+        <v>5.8</v>
+      </c>
+      <c r="AM27">
+        <v>1.34</v>
+      </c>
+      <c r="AN27">
+        <v>1.8</v>
+      </c>
+      <c r="AO27">
+        <v>2</v>
+      </c>
+      <c r="AP27"/>
+      <c r="AQ27"/>
+      <c r="AR27">
+        <v>1.8</v>
+      </c>
+      <c r="AS27">
+        <v>2</v>
+      </c>
+      <c r="AT27">
+        <v>1.78</v>
+      </c>
+      <c r="AU27">
+        <v>1.97</v>
+      </c>
+      <c r="AV27">
+        <v>1.9</v>
+      </c>
+      <c r="AW27">
+        <v>2.06</v>
+      </c>
+      <c r="AX27">
+        <v>1.5</v>
+      </c>
+      <c r="AY27">
+        <v>1.88</v>
+      </c>
+      <c r="AZ27">
+        <v>1.98</v>
+      </c>
+      <c r="BA27"/>
+      <c r="BB27"/>
+      <c r="BC27">
+        <v>1.9</v>
+      </c>
+      <c r="BD27">
+        <v>1.98</v>
+      </c>
+      <c r="BE27">
+        <v>1.82</v>
+      </c>
+      <c r="BF27">
+        <v>1.91</v>
+      </c>
+      <c r="BG27">
+        <v>1.92</v>
+      </c>
+      <c r="BH27">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D28" t="s">
+        <v>166</v>
+      </c>
+      <c r="E28" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28"/>
+      <c r="G28">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="H28">
+        <v>3.4</v>
+      </c>
+      <c r="I28">
+        <v>2.8</v>
+      </c>
+      <c r="J28">
+        <v>2.4</v>
+      </c>
+      <c r="K28">
+        <v>3.4</v>
+      </c>
+      <c r="L28">
+        <v>2.8</v>
+      </c>
+      <c r="M28">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="N28">
+        <v>3.1</v>
+      </c>
+      <c r="O28">
+        <v>2.88</v>
+      </c>
+      <c r="P28">
+        <v>2.4</v>
+      </c>
+      <c r="Q28">
+        <v>3.4</v>
+      </c>
+      <c r="R28">
+        <v>2.88</v>
+      </c>
+      <c r="S28">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="T28">
+        <v>3.4</v>
+      </c>
+      <c r="U28">
+        <v>2.8</v>
+      </c>
+      <c r="V28">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="W28">
+        <v>3.4</v>
+      </c>
+      <c r="X28">
+        <v>2.8</v>
+      </c>
+      <c r="Y28">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Z28">
+        <v>3.3</v>
+      </c>
+      <c r="AA28">
+        <v>2.8</v>
+      </c>
+      <c r="AB28"/>
+      <c r="AC28"/>
+      <c r="AD28"/>
+      <c r="AE28">
+        <v>2.5</v>
+      </c>
+      <c r="AF28">
+        <v>3.5</v>
+      </c>
+      <c r="AG28">
+        <v>2.9</v>
+      </c>
+      <c r="AH28">
+        <v>2.41</v>
+      </c>
+      <c r="AI28">
+        <v>3.31</v>
+      </c>
+      <c r="AJ28">
+        <v>2.82</v>
+      </c>
+      <c r="AK28">
+        <v>2.58</v>
+      </c>
+      <c r="AL28">
+        <v>3.5</v>
+      </c>
+      <c r="AM28">
+        <v>3</v>
+      </c>
+      <c r="AN28">
+        <v>1.98</v>
+      </c>
+      <c r="AO28">
+        <v>1.88</v>
+      </c>
+      <c r="AP28"/>
+      <c r="AQ28"/>
+      <c r="AR28">
+        <v>2</v>
+      </c>
+      <c r="AS28">
+        <v>1.88</v>
+      </c>
+      <c r="AT28">
+        <v>1.94</v>
+      </c>
+      <c r="AU28">
+        <v>1.79</v>
+      </c>
+      <c r="AV28">
+        <v>2.04</v>
+      </c>
+      <c r="AW28">
+        <v>1.91</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>1.8</v>
+      </c>
+      <c r="AZ28">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BA28"/>
+      <c r="BB28"/>
+      <c r="BC28">
+        <v>1.8</v>
+      </c>
+      <c r="BD28">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BE28">
+        <v>1.75</v>
+      </c>
+      <c r="BF28">
+        <v>2</v>
+      </c>
+      <c r="BG28">
+        <v>1.84</v>
+      </c>
+      <c r="BH28">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D29" t="s">
+        <v>177</v>
+      </c>
+      <c r="E29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29"/>
+      <c r="G29">
+        <v>2.25</v>
+      </c>
+      <c r="H29">
+        <v>3.2</v>
+      </c>
+      <c r="I29">
+        <v>3.4</v>
+      </c>
+      <c r="J29">
+        <v>2.25</v>
+      </c>
+      <c r="K29">
+        <v>3.4</v>
+      </c>
+      <c r="L29">
+        <v>3.1</v>
+      </c>
+      <c r="M29">
+        <v>2.17</v>
+      </c>
+      <c r="N29">
+        <v>3.1</v>
+      </c>
+      <c r="O29">
+        <v>3.1</v>
+      </c>
+      <c r="P29">
+        <v>2.15</v>
+      </c>
+      <c r="Q29">
+        <v>3.5</v>
+      </c>
+      <c r="R29">
+        <v>3.25</v>
+      </c>
+      <c r="S29">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T29">
+        <v>3.25</v>
+      </c>
+      <c r="U29">
+        <v>3.4</v>
+      </c>
+      <c r="V29">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="W29">
+        <v>3.25</v>
+      </c>
+      <c r="X29">
+        <v>3.4</v>
+      </c>
+      <c r="Y29">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Z29">
+        <v>3.25</v>
+      </c>
+      <c r="AA29">
+        <v>3.4</v>
+      </c>
+      <c r="AB29"/>
+      <c r="AC29"/>
+      <c r="AD29"/>
+      <c r="AE29">
+        <v>2.25</v>
+      </c>
+      <c r="AF29">
+        <v>3.5</v>
+      </c>
+      <c r="AG29">
+        <v>3.5</v>
+      </c>
+      <c r="AH29">
+        <v>2.19</v>
+      </c>
+      <c r="AI29">
+        <v>3.26</v>
+      </c>
+      <c r="AJ29">
+        <v>3.26</v>
+      </c>
+      <c r="AK29">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AL29">
+        <v>3.45</v>
+      </c>
+      <c r="AM29">
+        <v>3.65</v>
+      </c>
+      <c r="AN29">
+        <v>1.73</v>
+      </c>
+      <c r="AO29">
+        <v>2.1</v>
+      </c>
+      <c r="AP29"/>
+      <c r="AQ29"/>
+      <c r="AR29">
+        <v>1.73</v>
+      </c>
+      <c r="AS29">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AT29">
+        <v>1.65</v>
+      </c>
+      <c r="AU29">
+        <v>2.15</v>
+      </c>
+      <c r="AV29">
+        <v>1.75</v>
+      </c>
+      <c r="AW29">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AX29">
+        <v>-0.25</v>
+      </c>
+      <c r="AY29">
+        <v>1.9</v>
+      </c>
+      <c r="AZ29">
+        <v>1.95</v>
+      </c>
+      <c r="BA29"/>
+      <c r="BB29"/>
+      <c r="BC29">
+        <v>1.9</v>
+      </c>
+      <c r="BD29">
+        <v>1.95</v>
+      </c>
+      <c r="BE29">
+        <v>1.84</v>
+      </c>
+      <c r="BF29">
+        <v>1.91</v>
+      </c>
+      <c r="BG29">
+        <v>1.93</v>
+      </c>
+      <c r="BH29">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D30" t="s">
+        <v>170</v>
+      </c>
+      <c r="E30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30"/>
+      <c r="G30">
+        <v>1.73</v>
+      </c>
+      <c r="H30">
+        <v>3.8</v>
+      </c>
+      <c r="I30">
+        <v>4.75</v>
+      </c>
+      <c r="J30">
+        <v>1.73</v>
+      </c>
+      <c r="K30">
+        <v>3.75</v>
+      </c>
+      <c r="L30">
+        <v>4.5</v>
+      </c>
+      <c r="M30">
+        <v>1.71</v>
+      </c>
+      <c r="N30">
+        <v>3.55</v>
+      </c>
+      <c r="O30">
+        <v>4.2</v>
+      </c>
+      <c r="P30">
+        <v>1.75</v>
+      </c>
+      <c r="Q30">
+        <v>3.75</v>
+      </c>
+      <c r="R30">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S30">
+        <v>1.78</v>
+      </c>
+      <c r="T30">
+        <v>3.6</v>
+      </c>
+      <c r="U30">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="V30">
+        <v>1.8</v>
+      </c>
+      <c r="W30">
+        <v>3.6</v>
+      </c>
+      <c r="X30">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Y30">
+        <v>1.75</v>
+      </c>
+      <c r="Z30">
+        <v>3.6</v>
+      </c>
+      <c r="AA30">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB30"/>
+      <c r="AC30"/>
+      <c r="AD30"/>
+      <c r="AE30">
+        <v>1.8</v>
+      </c>
+      <c r="AF30">
+        <v>3.8</v>
+      </c>
+      <c r="AG30">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="AH30">
+        <v>1.74</v>
+      </c>
+      <c r="AI30">
+        <v>3.68</v>
+      </c>
+      <c r="AJ30">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="AK30">
+        <v>1.81</v>
+      </c>
+      <c r="AL30">
+        <v>3.85</v>
+      </c>
+      <c r="AM30">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AN30">
+        <v>1.91</v>
+      </c>
+      <c r="AO30">
+        <v>1.91</v>
+      </c>
+      <c r="AP30"/>
+      <c r="AQ30"/>
+      <c r="AR30">
+        <v>1.91</v>
+      </c>
+      <c r="AS30">
+        <v>1.91</v>
+      </c>
+      <c r="AT30">
+        <v>1.86</v>
+      </c>
+      <c r="AU30">
+        <v>1.87</v>
+      </c>
+      <c r="AV30">
+        <v>1.97</v>
+      </c>
+      <c r="AW30">
+        <v>1.98</v>
+      </c>
+      <c r="AX30">
+        <v>-0.75</v>
+      </c>
+      <c r="AY30">
+        <v>1.98</v>
+      </c>
+      <c r="AZ30">
+        <v>1.88</v>
+      </c>
+      <c r="BA30"/>
+      <c r="BB30"/>
+      <c r="BC30">
+        <v>1.98</v>
+      </c>
+      <c r="BD30">
+        <v>1.9</v>
+      </c>
+      <c r="BE30">
+        <v>1.93</v>
+      </c>
+      <c r="BF30">
+        <v>1.83</v>
+      </c>
+      <c r="BG30">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BH30">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D31" t="s">
+        <v>174</v>
+      </c>
+      <c r="E31" t="s">
+        <v>169</v>
+      </c>
+      <c r="F31"/>
+      <c r="G31">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="H31">
+        <v>3.5</v>
+      </c>
+      <c r="I31">
+        <v>2.75</v>
+      </c>
+      <c r="J31">
+        <v>2.4</v>
+      </c>
+      <c r="K31">
+        <v>3.5</v>
+      </c>
+      <c r="L31">
+        <v>2.75</v>
+      </c>
+      <c r="M31">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="N31">
+        <v>3.25</v>
+      </c>
+      <c r="O31">
+        <v>2.8</v>
+      </c>
+      <c r="P31">
+        <v>2.4</v>
+      </c>
+      <c r="Q31">
+        <v>3.5</v>
+      </c>
+      <c r="R31">
+        <v>2.8</v>
+      </c>
+      <c r="S31">
+        <v>2.5</v>
+      </c>
+      <c r="T31">
+        <v>3.4</v>
+      </c>
+      <c r="U31">
+        <v>2.75</v>
+      </c>
+      <c r="V31">
+        <v>2.5</v>
+      </c>
+      <c r="W31">
+        <v>3.4</v>
+      </c>
+      <c r="X31">
+        <v>2.75</v>
+      </c>
+      <c r="Y31">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Z31">
+        <v>3.4</v>
+      </c>
+      <c r="AA31">
+        <v>2.75</v>
+      </c>
+      <c r="AB31"/>
+      <c r="AC31"/>
+      <c r="AD31"/>
+      <c r="AE31">
+        <v>2.5</v>
+      </c>
+      <c r="AF31">
+        <v>3.55</v>
+      </c>
+      <c r="AG31">
+        <v>2.85</v>
+      </c>
+      <c r="AH31">
+        <v>2.4</v>
+      </c>
+      <c r="AI31">
+        <v>3.41</v>
+      </c>
+      <c r="AJ31">
+        <v>2.76</v>
+      </c>
+      <c r="AK31">
+        <v>2.54</v>
+      </c>
+      <c r="AL31">
+        <v>3.6</v>
+      </c>
+      <c r="AM31">
+        <v>3</v>
+      </c>
+      <c r="AN31">
+        <v>1.85</v>
+      </c>
+      <c r="AO31">
+        <v>2</v>
+      </c>
+      <c r="AP31"/>
+      <c r="AQ31"/>
+      <c r="AR31">
+        <v>1.85</v>
+      </c>
+      <c r="AS31">
+        <v>2</v>
+      </c>
+      <c r="AT31">
+        <v>1.8</v>
+      </c>
+      <c r="AU31">
+        <v>1.93</v>
+      </c>
+      <c r="AV31">
+        <v>1.89</v>
+      </c>
+      <c r="AW31">
+        <v>2.06</v>
+      </c>
+      <c r="AX31">
+        <v>0</v>
+      </c>
+      <c r="AY31">
+        <v>1.8</v>
+      </c>
+      <c r="AZ31">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BA31"/>
+      <c r="BB31"/>
+      <c r="BC31">
+        <v>1.8</v>
+      </c>
+      <c r="BD31">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BE31">
+        <v>1.74</v>
+      </c>
+      <c r="BF31">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="BG31">
+        <v>1.83</v>
+      </c>
+      <c r="BH31">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D32" t="s">
+        <v>171</v>
+      </c>
+      <c r="E32" t="s">
+        <v>179</v>
+      </c>
+      <c r="F32"/>
+      <c r="G32">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="H32">
+        <v>2.88</v>
+      </c>
+      <c r="I32">
+        <v>3.4</v>
+      </c>
+      <c r="J32">
+        <v>2.4</v>
+      </c>
+      <c r="K32">
+        <v>2.88</v>
+      </c>
+      <c r="L32">
+        <v>3.3</v>
+      </c>
+      <c r="M32">
+        <v>2.33</v>
+      </c>
+      <c r="N32">
+        <v>2.7</v>
+      </c>
+      <c r="O32">
+        <v>3.25</v>
+      </c>
+      <c r="P32">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Q32">
+        <v>2.8</v>
+      </c>
+      <c r="R32">
+        <v>3.4</v>
+      </c>
+      <c r="S32">
+        <v>2.4</v>
+      </c>
+      <c r="T32">
+        <v>2.85</v>
+      </c>
+      <c r="U32">
+        <v>3.4</v>
+      </c>
+      <c r="V32">
+        <v>2.4</v>
+      </c>
+      <c r="W32">
+        <v>2.87</v>
+      </c>
+      <c r="X32">
+        <v>3.4</v>
+      </c>
+      <c r="Y32">
+        <v>2.4</v>
+      </c>
+      <c r="Z32">
+        <v>2.8</v>
+      </c>
+      <c r="AA32">
+        <v>3.4</v>
+      </c>
+      <c r="AB32"/>
+      <c r="AC32"/>
+      <c r="AD32"/>
+      <c r="AE32">
+        <v>2.5</v>
+      </c>
+      <c r="AF32">
+        <v>2.88</v>
+      </c>
+      <c r="AG32">
+        <v>3.66</v>
+      </c>
+      <c r="AH32">
+        <v>2.41</v>
+      </c>
+      <c r="AI32">
+        <v>2.77</v>
+      </c>
+      <c r="AJ32">
+        <v>3.38</v>
+      </c>
+      <c r="AK32">
+        <v>2.62</v>
+      </c>
+      <c r="AL32">
+        <v>2.86</v>
+      </c>
+      <c r="AM32">
+        <v>3.6</v>
+      </c>
+      <c r="AN32">
+        <v>2.75</v>
+      </c>
+      <c r="AO32">
+        <v>1.44</v>
+      </c>
+      <c r="AP32"/>
+      <c r="AQ32"/>
+      <c r="AR32">
+        <v>2.75</v>
+      </c>
+      <c r="AS32">
+        <v>1.5</v>
+      </c>
+      <c r="AT32">
+        <v>2.68</v>
+      </c>
+      <c r="AU32">
+        <v>1.43</v>
+      </c>
+      <c r="AV32">
+        <v>2.98</v>
+      </c>
+      <c r="AW32">
+        <v>1.49</v>
+      </c>
+      <c r="AX32">
+        <v>-0.25</v>
+      </c>
+      <c r="AY32">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AZ32">
+        <v>1.8</v>
+      </c>
+      <c r="BA32"/>
+      <c r="BB32"/>
+      <c r="BC32">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BD32">
+        <v>1.8</v>
+      </c>
+      <c r="BE32">
+        <v>1.99</v>
+      </c>
+      <c r="BF32">
+        <v>1.75</v>
+      </c>
+      <c r="BG32">
+        <v>2.16</v>
+      </c>
+      <c r="BH32">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D33" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" t="s">
+        <v>176</v>
+      </c>
+      <c r="F33"/>
+      <c r="G33">
+        <v>1.8</v>
+      </c>
+      <c r="H33">
+        <v>3.9</v>
+      </c>
+      <c r="I33">
+        <v>4.2</v>
+      </c>
+      <c r="J33">
+        <v>1.8</v>
+      </c>
+      <c r="K33">
+        <v>3.75</v>
+      </c>
+      <c r="L33">
+        <v>4.2</v>
+      </c>
+      <c r="M33">
+        <v>1.7</v>
+      </c>
+      <c r="N33">
+        <v>3.65</v>
+      </c>
+      <c r="O33">
+        <v>4.2</v>
+      </c>
+      <c r="P33">
+        <v>1.75</v>
+      </c>
+      <c r="Q33">
+        <v>3.9</v>
+      </c>
+      <c r="R33">
+        <v>4.33</v>
+      </c>
+      <c r="S33">
+        <v>1.78</v>
+      </c>
+      <c r="T33">
+        <v>4</v>
+      </c>
+      <c r="U33">
+        <v>4</v>
+      </c>
+      <c r="V33">
+        <v>1.8</v>
+      </c>
+      <c r="W33">
+        <v>4</v>
+      </c>
+      <c r="X33">
+        <v>4</v>
+      </c>
+      <c r="Y33">
+        <v>1.8</v>
+      </c>
+      <c r="Z33">
+        <v>4</v>
+      </c>
+      <c r="AA33">
+        <v>4</v>
+      </c>
+      <c r="AB33"/>
+      <c r="AC33"/>
+      <c r="AD33"/>
+      <c r="AE33">
+        <v>1.8</v>
+      </c>
+      <c r="AF33">
+        <v>4</v>
+      </c>
+      <c r="AG33">
+        <v>4.45</v>
+      </c>
+      <c r="AH33">
+        <v>1.76</v>
+      </c>
+      <c r="AI33">
+        <v>3.86</v>
+      </c>
+      <c r="AJ33">
+        <v>4.16</v>
+      </c>
+      <c r="AK33">
+        <v>1.84</v>
+      </c>
+      <c r="AL33">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AM33">
+        <v>4.5</v>
+      </c>
+      <c r="AN33">
+        <v>1.73</v>
+      </c>
+      <c r="AO33">
+        <v>2.1</v>
+      </c>
+      <c r="AP33"/>
+      <c r="AQ33"/>
+      <c r="AR33">
+        <v>1.73</v>
+      </c>
+      <c r="AS33">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AT33">
+        <v>1.65</v>
+      </c>
+      <c r="AU33">
+        <v>2.14</v>
+      </c>
+      <c r="AV33">
+        <v>1.75</v>
+      </c>
+      <c r="AW33">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AX33">
+        <v>-0.75</v>
+      </c>
+      <c r="AY33">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ33">
+        <v>1.83</v>
+      </c>
+      <c r="BA33"/>
+      <c r="BB33"/>
+      <c r="BC33">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD33">
+        <v>1.86</v>
+      </c>
+      <c r="BE33">
+        <v>1.95</v>
+      </c>
+      <c r="BF33">
+        <v>1.8</v>
+      </c>
+      <c r="BG33">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="BH33">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D34" t="s">
+        <v>164</v>
+      </c>
+      <c r="E34" t="s">
+        <v>163</v>
+      </c>
+      <c r="F34"/>
+      <c r="G34">
+        <v>1.44</v>
+      </c>
+      <c r="H34">
+        <v>4.5</v>
+      </c>
+      <c r="I34">
+        <v>7</v>
+      </c>
+      <c r="J34">
+        <v>1.44</v>
+      </c>
+      <c r="K34">
+        <v>4.33</v>
+      </c>
+      <c r="L34">
+        <v>7.5</v>
+      </c>
+      <c r="M34">
+        <v>1.43</v>
+      </c>
+      <c r="N34">
+        <v>4</v>
+      </c>
+      <c r="O34">
+        <v>6.5</v>
+      </c>
+      <c r="P34">
+        <v>1.44</v>
+      </c>
+      <c r="Q34">
+        <v>4.33</v>
+      </c>
+      <c r="R34">
+        <v>7.5</v>
+      </c>
+      <c r="S34">
+        <v>1.47</v>
+      </c>
+      <c r="T34">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="U34">
+        <v>6.75</v>
+      </c>
+      <c r="V34">
+        <v>1.48</v>
+      </c>
+      <c r="W34">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="X34">
+        <v>7</v>
+      </c>
+      <c r="Y34">
+        <v>1.48</v>
+      </c>
+      <c r="Z34">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AA34">
+        <v>6.5</v>
+      </c>
+      <c r="AB34"/>
+      <c r="AC34"/>
+      <c r="AD34"/>
+      <c r="AE34">
+        <v>1.48</v>
+      </c>
+      <c r="AF34">
+        <v>4.7</v>
+      </c>
+      <c r="AG34">
+        <v>7.5</v>
+      </c>
+      <c r="AH34">
+        <v>1.45</v>
+      </c>
+      <c r="AI34">
+        <v>4.33</v>
+      </c>
+      <c r="AJ34">
+        <v>6.9</v>
+      </c>
+      <c r="AK34">
+        <v>1.49</v>
+      </c>
+      <c r="AL34">
+        <v>4.8</v>
+      </c>
+      <c r="AM34">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AN34">
+        <v>1.88</v>
+      </c>
+      <c r="AO34">
+        <v>1.98</v>
+      </c>
+      <c r="AP34"/>
+      <c r="AQ34"/>
+      <c r="AR34">
+        <v>1.91</v>
+      </c>
+      <c r="AS34">
+        <v>1.98</v>
+      </c>
+      <c r="AT34">
+        <v>1.83</v>
+      </c>
+      <c r="AU34">
+        <v>1.9</v>
+      </c>
+      <c r="AV34">
+        <v>1.94</v>
+      </c>
+      <c r="AW34">
+        <v>2.02</v>
+      </c>
+      <c r="AX34">
+        <v>-1.25</v>
+      </c>
+      <c r="AY34">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ34">
+        <v>1.83</v>
+      </c>
+      <c r="BA34"/>
+      <c r="BB34"/>
+      <c r="BC34">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD34">
+        <v>1.83</v>
+      </c>
+      <c r="BE34">
+        <v>1.98</v>
+      </c>
+      <c r="BF34">
+        <v>1.76</v>
+      </c>
+      <c r="BG34">
+        <v>2.08</v>
+      </c>
+      <c r="BH34">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D35" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35"/>
+      <c r="G35">
+        <v>1.5</v>
+      </c>
+      <c r="H35">
+        <v>4.75</v>
+      </c>
+      <c r="I35">
+        <v>5.75</v>
+      </c>
+      <c r="J35">
+        <v>1.44</v>
+      </c>
+      <c r="K35">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L35">
+        <v>6.5</v>
+      </c>
+      <c r="M35">
+        <v>1.43</v>
+      </c>
+      <c r="N35">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O35">
+        <v>5.8</v>
+      </c>
+      <c r="P35">
+        <v>1.44</v>
+      </c>
+      <c r="Q35">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R35">
+        <v>5.75</v>
+      </c>
+      <c r="S35">
+        <v>1.5</v>
+      </c>
+      <c r="T35">
+        <v>4.75</v>
+      </c>
+      <c r="U35">
+        <v>5.75</v>
+      </c>
+      <c r="V35">
+        <v>1.5</v>
+      </c>
+      <c r="W35">
+        <v>4.8</v>
+      </c>
+      <c r="X35">
+        <v>5.75</v>
+      </c>
+      <c r="Y35">
+        <v>1.5</v>
+      </c>
+      <c r="Z35">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AA35">
+        <v>5.5</v>
+      </c>
+      <c r="AB35"/>
+      <c r="AC35"/>
+      <c r="AD35"/>
+      <c r="AE35">
+        <v>1.5</v>
+      </c>
+      <c r="AF35">
+        <v>5</v>
+      </c>
+      <c r="AG35">
+        <v>6.5</v>
+      </c>
+      <c r="AH35">
+        <v>1.46</v>
+      </c>
+      <c r="AI35">
+        <v>4.63</v>
+      </c>
+      <c r="AJ35">
+        <v>5.84</v>
+      </c>
+      <c r="AK35">
+        <v>1.52</v>
+      </c>
+      <c r="AL35">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AM35">
+        <v>6.8</v>
+      </c>
+      <c r="AN35">
+        <v>1.5</v>
+      </c>
+      <c r="AO35">
+        <v>2.63</v>
+      </c>
+      <c r="AP35"/>
+      <c r="AQ35"/>
+      <c r="AR35">
+        <v>1.5</v>
+      </c>
+      <c r="AS35">
+        <v>2.63</v>
+      </c>
+      <c r="AT35">
+        <v>1.47</v>
+      </c>
+      <c r="AU35">
+        <v>2.57</v>
+      </c>
+      <c r="AV35">
+        <v>1.53</v>
+      </c>
+      <c r="AW35">
+        <v>2.78</v>
+      </c>
+      <c r="AX35">
+        <v>-1.25</v>
+      </c>
+      <c r="AY35">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ35">
+        <v>1.83</v>
+      </c>
+      <c r="BA35"/>
+      <c r="BB35"/>
+      <c r="BC35">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD35">
+        <v>1.83</v>
+      </c>
+      <c r="BE35">
+        <v>1.95</v>
+      </c>
+      <c r="BF35">
+        <v>1.79</v>
+      </c>
+      <c r="BG35">
+        <v>2.04</v>
+      </c>
+      <c r="BH35">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D36" t="s">
+        <v>168</v>
+      </c>
+      <c r="E36" t="s">
+        <v>165</v>
+      </c>
+      <c r="F36"/>
+      <c r="G36">
+        <v>3.6</v>
+      </c>
+      <c r="H36">
+        <v>4.2</v>
+      </c>
+      <c r="I36">
+        <v>1.85</v>
+      </c>
+      <c r="J36">
+        <v>3.6</v>
+      </c>
+      <c r="K36">
+        <v>4</v>
+      </c>
+      <c r="L36">
+        <v>1.9</v>
+      </c>
+      <c r="M36">
+        <v>3.55</v>
+      </c>
+      <c r="N36">
+        <v>3.85</v>
+      </c>
+      <c r="O36">
+        <v>1.78</v>
+      </c>
+      <c r="P36">
+        <v>3.4</v>
+      </c>
+      <c r="Q36">
+        <v>3.9</v>
+      </c>
+      <c r="R36">
+        <v>1.83</v>
+      </c>
+      <c r="S36">
+        <v>3.6</v>
+      </c>
+      <c r="T36">
+        <v>3.9</v>
+      </c>
+      <c r="U36">
+        <v>1.9</v>
+      </c>
+      <c r="V36">
+        <v>3.6</v>
+      </c>
+      <c r="W36">
+        <v>3.9</v>
+      </c>
+      <c r="X36">
+        <v>1.91</v>
+      </c>
+      <c r="Y36">
+        <v>3.6</v>
+      </c>
+      <c r="Z36">
+        <v>3.9</v>
+      </c>
+      <c r="AA36">
+        <v>1.91</v>
+      </c>
+      <c r="AB36"/>
+      <c r="AC36"/>
+      <c r="AD36"/>
+      <c r="AE36">
+        <v>3.75</v>
+      </c>
+      <c r="AF36">
+        <v>4.2</v>
+      </c>
+      <c r="AG36">
+        <v>1.91</v>
+      </c>
+      <c r="AH36">
+        <v>3.54</v>
+      </c>
+      <c r="AI36">
+        <v>3.98</v>
+      </c>
+      <c r="AJ36">
+        <v>1.84</v>
+      </c>
+      <c r="AK36">
+        <v>3.8</v>
+      </c>
+      <c r="AL36">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AM36">
+        <v>1.95</v>
+      </c>
+      <c r="AN36">
+        <v>1.44</v>
+      </c>
+      <c r="AO36">
+        <v>2.75</v>
+      </c>
+      <c r="AP36"/>
+      <c r="AQ36"/>
+      <c r="AR36">
+        <v>1.44</v>
+      </c>
+      <c r="AS36">
+        <v>2.75</v>
+      </c>
+      <c r="AT36">
+        <v>1.43</v>
+      </c>
+      <c r="AU36">
+        <v>2.68</v>
+      </c>
+      <c r="AV36">
+        <v>1.49</v>
+      </c>
+      <c r="AW36">
+        <v>2.94</v>
+      </c>
+      <c r="AX36">
+        <v>0.5</v>
+      </c>
+      <c r="AY36">
+        <v>1.98</v>
+      </c>
+      <c r="AZ36">
+        <v>1.88</v>
+      </c>
+      <c r="BA36"/>
+      <c r="BB36"/>
+      <c r="BC36">
+        <v>1.98</v>
+      </c>
+      <c r="BD36">
+        <v>1.88</v>
+      </c>
+      <c r="BE36">
+        <v>1.9</v>
+      </c>
+      <c r="BF36">
+        <v>1.82</v>
+      </c>
+      <c r="BG36">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BH36">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D37" t="s">
+        <v>162</v>
+      </c>
+      <c r="E37" t="s">
+        <v>175</v>
+      </c>
+      <c r="F37"/>
+      <c r="G37">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="H37">
+        <v>3.6</v>
+      </c>
+      <c r="I37">
+        <v>2.75</v>
+      </c>
+      <c r="J37">
+        <v>2.4</v>
+      </c>
+      <c r="K37">
+        <v>3.75</v>
+      </c>
+      <c r="L37">
+        <v>2.6</v>
+      </c>
+      <c r="M37">
+        <v>2.33</v>
+      </c>
+      <c r="N37">
+        <v>3.6</v>
+      </c>
+      <c r="O37">
+        <v>2.5</v>
+      </c>
+      <c r="P37">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Q37">
+        <v>3.7</v>
+      </c>
+      <c r="R37">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="S37">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="T37">
+        <v>3.8</v>
+      </c>
+      <c r="U37">
+        <v>2.6</v>
+      </c>
+      <c r="V37">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="W37">
+        <v>3.8</v>
+      </c>
+      <c r="X37">
+        <v>2.6</v>
+      </c>
+      <c r="Y37">
+        <v>2.4</v>
+      </c>
+      <c r="Z37">
+        <v>3.75</v>
+      </c>
+      <c r="AA37">
+        <v>2.6</v>
+      </c>
+      <c r="AB37"/>
+      <c r="AC37"/>
+      <c r="AD37"/>
+      <c r="AE37">
+        <v>2.5</v>
+      </c>
+      <c r="AF37">
+        <v>3.8</v>
+      </c>
+      <c r="AG37">
+        <v>2.8</v>
+      </c>
+      <c r="AH37">
+        <v>2.39</v>
+      </c>
+      <c r="AI37">
+        <v>3.71</v>
+      </c>
+      <c r="AJ37">
+        <v>2.58</v>
+      </c>
+      <c r="AK37">
+        <v>2.48</v>
+      </c>
+      <c r="AL37">
+        <v>4</v>
+      </c>
+      <c r="AM37">
+        <v>2.82</v>
+      </c>
+      <c r="AN37">
+        <v>1.5</v>
+      </c>
+      <c r="AO37">
+        <v>2.63</v>
+      </c>
+      <c r="AP37"/>
+      <c r="AQ37"/>
+      <c r="AR37">
+        <v>1.5</v>
+      </c>
+      <c r="AS37">
+        <v>2.75</v>
+      </c>
+      <c r="AT37">
+        <v>1.45</v>
+      </c>
+      <c r="AU37">
+        <v>2.63</v>
+      </c>
+      <c r="AV37">
+        <v>1.52</v>
+      </c>
+      <c r="AW37">
+        <v>2.76</v>
+      </c>
+      <c r="AX37">
+        <v>0</v>
+      </c>
+      <c r="AY37">
+        <v>1.8</v>
+      </c>
+      <c r="AZ37">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BA37"/>
+      <c r="BB37"/>
+      <c r="BC37">
+        <v>1.8</v>
+      </c>
+      <c r="BD37">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BE37">
+        <v>1.77</v>
+      </c>
+      <c r="BF37">
+        <v>1.97</v>
+      </c>
+      <c r="BG37">
+        <v>1.86</v>
+      </c>
+      <c r="BH37">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D38" t="s">
+        <v>201</v>
+      </c>
+      <c r="E38" t="s">
+        <v>190</v>
+      </c>
+      <c r="F38"/>
+      <c r="G38">
+        <v>1.81</v>
+      </c>
+      <c r="H38">
+        <v>3.9</v>
+      </c>
+      <c r="I38">
+        <v>3.75</v>
+      </c>
+      <c r="J38">
+        <v>1.83</v>
+      </c>
+      <c r="K38">
+        <v>3.75</v>
+      </c>
+      <c r="L38">
+        <v>3.6</v>
+      </c>
+      <c r="M38">
+        <v>1.8</v>
+      </c>
+      <c r="N38">
+        <v>3.6</v>
+      </c>
+      <c r="O38">
+        <v>3.9</v>
+      </c>
+      <c r="P38">
+        <v>1.8</v>
+      </c>
+      <c r="Q38">
+        <v>3.6</v>
+      </c>
+      <c r="R38">
+        <v>3.75</v>
+      </c>
+      <c r="S38">
+        <v>1.78</v>
+      </c>
+      <c r="T38">
+        <v>3.6</v>
+      </c>
+      <c r="U38">
+        <v>3.8</v>
+      </c>
+      <c r="V38">
+        <v>1.75</v>
+      </c>
+      <c r="W38">
+        <v>3.5</v>
+      </c>
+      <c r="X38">
+        <v>3.7</v>
+      </c>
+      <c r="Y38">
+        <v>1.75</v>
+      </c>
+      <c r="Z38">
+        <v>3.5</v>
+      </c>
+      <c r="AA38">
+        <v>3.7</v>
+      </c>
+      <c r="AB38"/>
+      <c r="AC38"/>
+      <c r="AD38"/>
+      <c r="AE38">
+        <v>1.85</v>
+      </c>
+      <c r="AF38">
+        <v>4</v>
+      </c>
+      <c r="AG38">
+        <v>3.9</v>
+      </c>
+      <c r="AH38">
+        <v>1.79</v>
+      </c>
+      <c r="AI38">
+        <v>3.67</v>
+      </c>
+      <c r="AJ38">
+        <v>3.72</v>
+      </c>
+      <c r="AK38">
+        <v>1.83</v>
+      </c>
+      <c r="AL38">
+        <v>3.8</v>
+      </c>
+      <c r="AM38">
+        <v>3.9</v>
+      </c>
+      <c r="AN38">
+        <v>1.67</v>
+      </c>
+      <c r="AO38">
+        <v>2.15</v>
+      </c>
+      <c r="AP38"/>
+      <c r="AQ38"/>
+      <c r="AR38">
+        <v>1.71</v>
+      </c>
+      <c r="AS38">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AT38">
+        <v>1.66</v>
+      </c>
+      <c r="AU38">
+        <v>2.1</v>
+      </c>
+      <c r="AV38">
+        <v>1.58</v>
+      </c>
+      <c r="AW38">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AX38">
+        <v>-0.5</v>
+      </c>
+      <c r="AY38">
+        <v>1.85</v>
+      </c>
+      <c r="AZ38">
+        <v>1.95</v>
+      </c>
+      <c r="BA38"/>
+      <c r="BB38"/>
+      <c r="BC38">
+        <v>1.85</v>
+      </c>
+      <c r="BD38">
+        <v>1.95</v>
+      </c>
+      <c r="BE38">
+        <v>1.78</v>
+      </c>
+      <c r="BF38">
+        <v>1.92</v>
+      </c>
+      <c r="BG38"/>
+      <c r="BH38"/>
+    </row>
+    <row r="39" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E39" t="s">
+        <v>183</v>
+      </c>
+      <c r="F39"/>
+      <c r="G39">
+        <v>1.49</v>
+      </c>
+      <c r="H39">
+        <v>4.75</v>
+      </c>
+      <c r="I39">
+        <v>5.25</v>
+      </c>
+      <c r="J39">
+        <v>1.5</v>
+      </c>
+      <c r="K39">
+        <v>4.33</v>
+      </c>
+      <c r="L39">
+        <v>5.5</v>
+      </c>
+      <c r="M39">
+        <v>1.46</v>
+      </c>
+      <c r="N39">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O39">
+        <v>5.8</v>
+      </c>
+      <c r="P39">
+        <v>1.45</v>
+      </c>
+      <c r="Q39">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R39">
+        <v>5.5</v>
+      </c>
+      <c r="S39">
+        <v>1.5</v>
+      </c>
+      <c r="T39">
+        <v>4.33</v>
+      </c>
+      <c r="U39">
+        <v>5.25</v>
+      </c>
+      <c r="V39">
+        <v>1.48</v>
+      </c>
+      <c r="W39">
+        <v>4.2</v>
+      </c>
+      <c r="X39">
+        <v>5</v>
+      </c>
+      <c r="Y39">
+        <v>1.48</v>
+      </c>
+      <c r="Z39">
+        <v>4.2</v>
+      </c>
+      <c r="AA39">
+        <v>5</v>
+      </c>
+      <c r="AB39"/>
+      <c r="AC39"/>
+      <c r="AD39"/>
+      <c r="AE39">
+        <v>1.5</v>
+      </c>
+      <c r="AF39">
+        <v>4.75</v>
+      </c>
+      <c r="AG39">
+        <v>5.8</v>
+      </c>
+      <c r="AH39">
+        <v>1.47</v>
+      </c>
+      <c r="AI39">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="AJ39">
+        <v>5.41</v>
+      </c>
+      <c r="AK39">
+        <v>1.54</v>
+      </c>
+      <c r="AL39">
+        <v>4.7</v>
+      </c>
+      <c r="AM39">
+        <v>5.7</v>
+      </c>
+      <c r="AN39">
+        <v>1.5</v>
+      </c>
+      <c r="AO39">
+        <v>2.5</v>
+      </c>
+      <c r="AP39"/>
+      <c r="AQ39"/>
+      <c r="AR39">
+        <v>1.52</v>
+      </c>
+      <c r="AS39">
+        <v>2.63</v>
+      </c>
+      <c r="AT39">
+        <v>1.5</v>
+      </c>
+      <c r="AU39">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="AV39">
+        <v>1.51</v>
+      </c>
+      <c r="AW39">
+        <v>2.66</v>
+      </c>
+      <c r="AX39">
+        <v>-1</v>
+      </c>
+      <c r="AY39">
+        <v>1.8</v>
+      </c>
+      <c r="AZ39">
+        <v>2</v>
+      </c>
+      <c r="BA39"/>
+      <c r="BB39"/>
+      <c r="BC39">
+        <v>1.8</v>
+      </c>
+      <c r="BD39">
+        <v>2</v>
+      </c>
+      <c r="BE39">
+        <v>1.76</v>
+      </c>
+      <c r="BF39">
+        <v>1.96</v>
+      </c>
+      <c r="BG39"/>
+      <c r="BH39"/>
+    </row>
+    <row r="40" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D40" t="s">
+        <v>192</v>
+      </c>
+      <c r="E40" t="s">
+        <v>195</v>
+      </c>
+      <c r="F40"/>
+      <c r="G40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H40">
+        <v>3.25</v>
+      </c>
+      <c r="I40">
+        <v>3.1</v>
+      </c>
+      <c r="J40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K40">
+        <v>3.3</v>
+      </c>
+      <c r="L40">
+        <v>2.88</v>
+      </c>
+      <c r="M40">
+        <v>2.17</v>
+      </c>
+      <c r="N40">
+        <v>3.35</v>
+      </c>
+      <c r="O40">
+        <v>3.05</v>
+      </c>
+      <c r="P40">
+        <v>2.25</v>
+      </c>
+      <c r="Q40">
+        <v>3.3</v>
+      </c>
+      <c r="R40">
+        <v>2.88</v>
+      </c>
+      <c r="S40">
+        <v>2.25</v>
+      </c>
+      <c r="T40">
+        <v>3.25</v>
+      </c>
+      <c r="U40">
+        <v>2.9</v>
+      </c>
+      <c r="V40"/>
+      <c r="W40"/>
+      <c r="X40"/>
+      <c r="Y40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Z40">
+        <v>3.2</v>
+      </c>
+      <c r="AA40">
+        <v>2.87</v>
+      </c>
+      <c r="AB40"/>
+      <c r="AC40"/>
+      <c r="AD40"/>
+      <c r="AE40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AF40">
+        <v>3.35</v>
+      </c>
+      <c r="AG40">
+        <v>3.25</v>
+      </c>
+      <c r="AH40">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AI40">
+        <v>3.24</v>
+      </c>
+      <c r="AJ40">
+        <v>2.96</v>
+      </c>
+      <c r="AK40">
+        <v>2.5</v>
+      </c>
+      <c r="AL40">
+        <v>3.3</v>
+      </c>
+      <c r="AM40">
+        <v>3.2</v>
+      </c>
+      <c r="AN40">
+        <v>1.9</v>
+      </c>
+      <c r="AO40">
+        <v>1.9</v>
+      </c>
+      <c r="AP40"/>
+      <c r="AQ40"/>
+      <c r="AR40">
+        <v>1.91</v>
+      </c>
+      <c r="AS40">
+        <v>1.91</v>
+      </c>
+      <c r="AT40">
+        <v>1.85</v>
+      </c>
+      <c r="AU40">
+        <v>1.85</v>
+      </c>
+      <c r="AV40">
+        <v>2.08</v>
+      </c>
+      <c r="AW40">
+        <v>1.89</v>
+      </c>
+      <c r="AX40">
+        <v>-0.25</v>
+      </c>
+      <c r="AY40">
+        <v>2</v>
+      </c>
+      <c r="AZ40">
+        <v>1.8</v>
+      </c>
+      <c r="BA40"/>
+      <c r="BB40"/>
+      <c r="BC40">
+        <v>2</v>
+      </c>
+      <c r="BD40">
+        <v>1.8</v>
+      </c>
+      <c r="BE40">
+        <v>1.93</v>
+      </c>
+      <c r="BF40">
+        <v>1.78</v>
+      </c>
+      <c r="BG40"/>
+      <c r="BH40"/>
+    </row>
+    <row r="41" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C41" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D41" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41" t="s">
+        <v>180</v>
+      </c>
+      <c r="F41"/>
+      <c r="G41">
+        <v>3.2</v>
+      </c>
+      <c r="H41">
+        <v>3.1</v>
+      </c>
+      <c r="I41">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J41">
+        <v>2.88</v>
+      </c>
+      <c r="K41">
+        <v>3.1</v>
+      </c>
+      <c r="L41">
+        <v>2.4</v>
+      </c>
+      <c r="M41">
+        <v>2.8</v>
+      </c>
+      <c r="N41">
+        <v>3.05</v>
+      </c>
+      <c r="O41">
+        <v>2.48</v>
+      </c>
+      <c r="P41">
+        <v>2.9</v>
+      </c>
+      <c r="Q41">
+        <v>3</v>
+      </c>
+      <c r="R41">
+        <v>2.38</v>
+      </c>
+      <c r="S41">
+        <v>2.9</v>
+      </c>
+      <c r="T41">
+        <v>3.1</v>
+      </c>
+      <c r="U41">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+      <c r="Y41">
+        <v>2.87</v>
+      </c>
+      <c r="Z41">
+        <v>3.1</v>
+      </c>
+      <c r="AA41">
+        <v>2.25</v>
+      </c>
+      <c r="AB41"/>
+      <c r="AC41"/>
+      <c r="AD41"/>
+      <c r="AE41">
+        <v>3.2</v>
+      </c>
+      <c r="AF41">
+        <v>3.1</v>
+      </c>
+      <c r="AG41">
+        <v>2.5</v>
+      </c>
+      <c r="AH41">
+        <v>2.87</v>
+      </c>
+      <c r="AI41">
+        <v>3.03</v>
+      </c>
+      <c r="AJ41">
+        <v>2.37</v>
+      </c>
+      <c r="AK41">
+        <v>3.2</v>
+      </c>
+      <c r="AL41">
+        <v>3.1</v>
+      </c>
+      <c r="AM41">
+        <v>2.46</v>
+      </c>
+      <c r="AN41">
+        <v>2.35</v>
+      </c>
+      <c r="AO41">
+        <v>1.57</v>
+      </c>
+      <c r="AP41"/>
+      <c r="AQ41"/>
+      <c r="AR41">
+        <v>2.4</v>
+      </c>
+      <c r="AS41">
+        <v>1.57</v>
+      </c>
+      <c r="AT41">
+        <v>2.31</v>
+      </c>
+      <c r="AU41">
+        <v>1.55</v>
+      </c>
+      <c r="AV41">
+        <v>2.46</v>
+      </c>
+      <c r="AW41">
+        <v>1.61</v>
+      </c>
+      <c r="AX41">
+        <v>0.25</v>
+      </c>
+      <c r="AY41">
+        <v>1.75</v>
+      </c>
+      <c r="AZ41">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BA41"/>
+      <c r="BB41"/>
+      <c r="BC41">
+        <v>1.75</v>
+      </c>
+      <c r="BD41">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BE41">
+        <v>1.71</v>
+      </c>
+      <c r="BF41">
+        <v>2.02</v>
+      </c>
+      <c r="BG41"/>
+      <c r="BH41"/>
+    </row>
+    <row r="42" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C42" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D42" t="s">
+        <v>187</v>
+      </c>
+      <c r="E42" t="s">
+        <v>199</v>
+      </c>
+      <c r="F42"/>
+      <c r="G42">
+        <v>1.68</v>
+      </c>
+      <c r="H42">
+        <v>4.2</v>
+      </c>
+      <c r="I42">
+        <v>4.2</v>
+      </c>
+      <c r="J42">
+        <v>1.7</v>
+      </c>
+      <c r="K42">
+        <v>3.75</v>
+      </c>
+      <c r="L42">
+        <v>4.33</v>
+      </c>
+      <c r="M42">
+        <v>1.71</v>
+      </c>
+      <c r="N42">
+        <v>3.6</v>
+      </c>
+      <c r="O42">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P42">
+        <v>1.67</v>
+      </c>
+      <c r="Q42">
+        <v>3.7</v>
+      </c>
+      <c r="R42">
+        <v>4.5</v>
+      </c>
+      <c r="S42">
+        <v>1.7</v>
+      </c>
+      <c r="T42">
+        <v>3.6</v>
+      </c>
+      <c r="U42">
+        <v>4.33</v>
+      </c>
+      <c r="V42"/>
+      <c r="W42"/>
+      <c r="X42"/>
+      <c r="Y42">
+        <v>1.7</v>
+      </c>
+      <c r="Z42">
+        <v>3.5</v>
+      </c>
+      <c r="AA42">
+        <v>4.2</v>
+      </c>
+      <c r="AB42"/>
+      <c r="AC42"/>
+      <c r="AD42"/>
+      <c r="AE42">
+        <v>1.71</v>
+      </c>
+      <c r="AF42">
+        <v>4.2</v>
+      </c>
+      <c r="AG42">
+        <v>4.5</v>
+      </c>
+      <c r="AH42">
+        <v>1.68</v>
+      </c>
+      <c r="AI42">
+        <v>3.71</v>
+      </c>
+      <c r="AJ42">
+        <v>4.29</v>
+      </c>
+      <c r="AK42">
+        <v>1.76</v>
+      </c>
+      <c r="AL42">
+        <v>3.95</v>
+      </c>
+      <c r="AM42">
+        <v>4.5</v>
+      </c>
+      <c r="AN42">
+        <v>1.8</v>
+      </c>
+      <c r="AO42">
+        <v>2</v>
+      </c>
+      <c r="AP42"/>
+      <c r="AQ42"/>
+      <c r="AR42">
+        <v>1.8</v>
+      </c>
+      <c r="AS42">
+        <v>2</v>
+      </c>
+      <c r="AT42">
+        <v>1.77</v>
+      </c>
+      <c r="AU42">
+        <v>1.94</v>
+      </c>
+      <c r="AV42">
+        <v>1.8</v>
+      </c>
+      <c r="AW42">
+        <v>2.06</v>
+      </c>
+      <c r="AX42">
+        <v>-0.75</v>
+      </c>
+      <c r="AY42">
+        <v>1.93</v>
+      </c>
+      <c r="AZ42">
+        <v>1.88</v>
+      </c>
+      <c r="BA42"/>
+      <c r="BB42"/>
+      <c r="BC42">
+        <v>1.93</v>
+      </c>
+      <c r="BD42">
+        <v>1.88</v>
+      </c>
+      <c r="BE42">
+        <v>1.87</v>
+      </c>
+      <c r="BF42">
+        <v>1.84</v>
+      </c>
+      <c r="BG42"/>
+      <c r="BH42"/>
+    </row>
+    <row r="43" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C43" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D43" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" t="s">
+        <v>185</v>
+      </c>
+      <c r="F43"/>
+      <c r="G43">
+        <v>5</v>
+      </c>
+      <c r="H43">
+        <v>3.8</v>
+      </c>
+      <c r="I43">
+        <v>1.61</v>
+      </c>
+      <c r="J43">
+        <v>4.33</v>
+      </c>
+      <c r="K43">
+        <v>3.75</v>
+      </c>
+      <c r="L43">
+        <v>1.67</v>
+      </c>
+      <c r="M43">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="N43">
+        <v>3.65</v>
+      </c>
+      <c r="O43">
+        <v>1.71</v>
+      </c>
+      <c r="P43">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q43">
+        <v>3.9</v>
+      </c>
+      <c r="R43">
+        <v>1.62</v>
+      </c>
+      <c r="S43">
+        <v>4.2</v>
+      </c>
+      <c r="T43">
+        <v>3.9</v>
+      </c>
+      <c r="U43">
+        <v>1.65</v>
+      </c>
+      <c r="V43"/>
+      <c r="W43"/>
+      <c r="X43"/>
+      <c r="Y43">
+        <v>4</v>
+      </c>
+      <c r="Z43">
+        <v>3.8</v>
+      </c>
+      <c r="AA43">
+        <v>1.65</v>
+      </c>
+      <c r="AB43"/>
+      <c r="AC43"/>
+      <c r="AD43"/>
+      <c r="AE43">
+        <v>5</v>
+      </c>
+      <c r="AF43">
+        <v>4</v>
+      </c>
+      <c r="AG43">
+        <v>1.71</v>
+      </c>
+      <c r="AH43">
+        <v>4.34</v>
+      </c>
+      <c r="AI43">
+        <v>3.79</v>
+      </c>
+      <c r="AJ43">
+        <v>1.66</v>
+      </c>
+      <c r="AK43">
+        <v>5</v>
+      </c>
+      <c r="AL43">
+        <v>4.2</v>
+      </c>
+      <c r="AM43">
+        <v>1.66</v>
+      </c>
+      <c r="AN43">
+        <v>1.67</v>
+      </c>
+      <c r="AO43">
+        <v>2.15</v>
+      </c>
+      <c r="AP43"/>
+      <c r="AQ43"/>
+      <c r="AR43">
+        <v>1.76</v>
+      </c>
+      <c r="AS43">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AT43">
+        <v>1.67</v>
+      </c>
+      <c r="AU43">
+        <v>2.09</v>
+      </c>
+      <c r="AV43">
+        <v>1.68</v>
+      </c>
+      <c r="AW43">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AX43">
+        <v>0.75</v>
+      </c>
+      <c r="AY43">
+        <v>1.98</v>
+      </c>
+      <c r="AZ43">
+        <v>1.83</v>
+      </c>
+      <c r="BA43"/>
+      <c r="BB43"/>
+      <c r="BC43">
+        <v>1.98</v>
+      </c>
+      <c r="BD43">
+        <v>1.83</v>
+      </c>
+      <c r="BE43">
+        <v>1.91</v>
+      </c>
+      <c r="BF43">
+        <v>1.8</v>
+      </c>
+      <c r="BG43"/>
+      <c r="BH43"/>
+    </row>
+    <row r="44" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C44" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D44" t="s">
+        <v>196</v>
+      </c>
+      <c r="E44" t="s">
+        <v>191</v>
+      </c>
+      <c r="F44"/>
+      <c r="G44">
+        <v>1.41</v>
+      </c>
+      <c r="H44">
+        <v>4.33</v>
+      </c>
+      <c r="I44">
+        <v>7</v>
+      </c>
+      <c r="J44">
+        <v>1.4</v>
+      </c>
+      <c r="K44">
+        <v>4.2</v>
+      </c>
+      <c r="L44">
+        <v>7</v>
+      </c>
+      <c r="M44">
+        <v>1.42</v>
+      </c>
+      <c r="N44">
+        <v>4.25</v>
+      </c>
+      <c r="O44">
+        <v>6.75</v>
+      </c>
+      <c r="P44">
+        <v>1.4</v>
+      </c>
+      <c r="Q44">
+        <v>4.2</v>
+      </c>
+      <c r="R44">
+        <v>7</v>
+      </c>
+      <c r="S44">
+        <v>1.43</v>
+      </c>
+      <c r="T44">
+        <v>4.33</v>
+      </c>
+      <c r="U44">
+        <v>6.25</v>
+      </c>
+      <c r="V44"/>
+      <c r="W44"/>
+      <c r="X44"/>
+      <c r="Y44">
+        <v>1.4</v>
+      </c>
+      <c r="Z44">
+        <v>4.2</v>
+      </c>
+      <c r="AA44">
+        <v>6</v>
+      </c>
+      <c r="AB44"/>
+      <c r="AC44"/>
+      <c r="AD44"/>
+      <c r="AE44">
+        <v>1.43</v>
+      </c>
+      <c r="AF44">
+        <v>4.75</v>
+      </c>
+      <c r="AG44">
+        <v>7.5</v>
+      </c>
+      <c r="AH44">
+        <v>1.4</v>
+      </c>
+      <c r="AI44">
+        <v>4.25</v>
+      </c>
+      <c r="AJ44">
+        <v>6.73</v>
+      </c>
+      <c r="AK44">
+        <v>1.44</v>
+      </c>
+      <c r="AL44">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AM44">
+        <v>8.4</v>
+      </c>
+      <c r="AN44">
+        <v>1.8</v>
+      </c>
+      <c r="AO44">
+        <v>2</v>
+      </c>
+      <c r="AP44"/>
+      <c r="AQ44"/>
+      <c r="AR44">
+        <v>1.8</v>
+      </c>
+      <c r="AS44">
+        <v>2.02</v>
+      </c>
+      <c r="AT44">
+        <v>1.73</v>
+      </c>
+      <c r="AU44">
+        <v>2</v>
+      </c>
+      <c r="AV44">
+        <v>1.83</v>
+      </c>
+      <c r="AW44">
+        <v>2.06</v>
+      </c>
+      <c r="AX44">
+        <v>-1.25</v>
+      </c>
+      <c r="AY44">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ44">
+        <v>1.78</v>
+      </c>
+      <c r="BA44"/>
+      <c r="BB44"/>
+      <c r="BC44">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD44">
+        <v>1.86</v>
+      </c>
+      <c r="BE44">
+        <v>1.92</v>
+      </c>
+      <c r="BF44">
+        <v>1.79</v>
+      </c>
+      <c r="BG44"/>
+      <c r="BH44"/>
+    </row>
+    <row r="45" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C45" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D45" t="s">
+        <v>186</v>
+      </c>
+      <c r="E45" t="s">
+        <v>184</v>
+      </c>
+      <c r="F45"/>
+      <c r="G45">
+        <v>1.61</v>
+      </c>
+      <c r="H45">
+        <v>4.5</v>
+      </c>
+      <c r="I45">
+        <v>4.2</v>
+      </c>
+      <c r="J45">
+        <v>1.62</v>
+      </c>
+      <c r="K45">
+        <v>4.33</v>
+      </c>
+      <c r="L45">
+        <v>4.2</v>
+      </c>
+      <c r="M45">
+        <v>1.61</v>
+      </c>
+      <c r="N45">
+        <v>4.2</v>
+      </c>
+      <c r="O45">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P45">
+        <v>1.6</v>
+      </c>
+      <c r="Q45">
+        <v>4.2</v>
+      </c>
+      <c r="R45">
+        <v>4.33</v>
+      </c>
+      <c r="S45">
+        <v>1.62</v>
+      </c>
+      <c r="T45">
+        <v>4.2</v>
+      </c>
+      <c r="U45">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="V45"/>
+      <c r="W45"/>
+      <c r="X45"/>
+      <c r="Y45">
+        <v>1.61</v>
+      </c>
+      <c r="Z45">
+        <v>4</v>
+      </c>
+      <c r="AA45">
+        <v>4</v>
+      </c>
+      <c r="AB45"/>
+      <c r="AC45"/>
+      <c r="AD45"/>
+      <c r="AE45">
+        <v>1.62</v>
+      </c>
+      <c r="AF45">
+        <v>4.5</v>
+      </c>
+      <c r="AG45">
+        <v>4.75</v>
+      </c>
+      <c r="AH45">
+        <v>1.6</v>
+      </c>
+      <c r="AI45">
+        <v>4.21</v>
+      </c>
+      <c r="AJ45">
+        <v>4.24</v>
+      </c>
+      <c r="AK45">
+        <v>1.69</v>
+      </c>
+      <c r="AL45">
+        <v>4.7</v>
+      </c>
+      <c r="AM45">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AN45">
+        <v>1.4</v>
+      </c>
+      <c r="AO45">
+        <v>2.88</v>
+      </c>
+      <c r="AP45"/>
+      <c r="AQ45"/>
+      <c r="AR45">
+        <v>1.4</v>
+      </c>
+      <c r="AS45">
+        <v>3.1</v>
+      </c>
+      <c r="AT45">
+        <v>1.36</v>
+      </c>
+      <c r="AU45">
+        <v>2.92</v>
+      </c>
+      <c r="AV45">
+        <v>1.42</v>
+      </c>
+      <c r="AW45">
+        <v>3.1</v>
+      </c>
+      <c r="AX45">
+        <v>-0.75</v>
+      </c>
+      <c r="AY45">
+        <v>1.8</v>
+      </c>
+      <c r="AZ45">
+        <v>2</v>
+      </c>
+      <c r="BA45"/>
+      <c r="BB45"/>
+      <c r="BC45">
+        <v>1.8</v>
+      </c>
+      <c r="BD45">
+        <v>2</v>
+      </c>
+      <c r="BE45">
+        <v>1.74</v>
+      </c>
+      <c r="BF45">
+        <v>1.98</v>
+      </c>
+      <c r="BG45"/>
+      <c r="BH45"/>
+    </row>
+    <row r="46" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D46" t="s">
+        <v>193</v>
+      </c>
+      <c r="E46" t="s">
+        <v>188</v>
+      </c>
+      <c r="F46"/>
+      <c r="G46">
+        <v>1.57</v>
+      </c>
+      <c r="H46">
+        <v>4</v>
+      </c>
+      <c r="I46">
+        <v>5.25</v>
+      </c>
+      <c r="J46">
+        <v>1.6</v>
+      </c>
+      <c r="K46">
+        <v>4</v>
+      </c>
+      <c r="L46">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="M46">
+        <v>1.6</v>
+      </c>
+      <c r="N46">
+        <v>3.8</v>
+      </c>
+      <c r="O46">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="P46">
+        <v>1.57</v>
+      </c>
+      <c r="Q46">
+        <v>3.9</v>
+      </c>
+      <c r="R46">
+        <v>5</v>
+      </c>
+      <c r="S46">
+        <v>1.58</v>
+      </c>
+      <c r="T46">
+        <v>4</v>
+      </c>
+      <c r="U46">
+        <v>4.75</v>
+      </c>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+      <c r="Y46">
+        <v>1.57</v>
+      </c>
+      <c r="Z46">
+        <v>3.8</v>
+      </c>
+      <c r="AA46">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB46"/>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46">
+        <v>1.6</v>
+      </c>
+      <c r="AF46">
+        <v>4.5</v>
+      </c>
+      <c r="AG46">
+        <v>5.25</v>
+      </c>
+      <c r="AH46">
+        <v>1.57</v>
+      </c>
+      <c r="AI46">
+        <v>3.92</v>
+      </c>
+      <c r="AJ46">
+        <v>4.91</v>
+      </c>
+      <c r="AK46">
+        <v>1.64</v>
+      </c>
+      <c r="AL46">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AM46">
+        <v>5.6</v>
+      </c>
+      <c r="AN46">
+        <v>1.73</v>
+      </c>
+      <c r="AO46">
+        <v>2.08</v>
+      </c>
+      <c r="AP46"/>
+      <c r="AQ46"/>
+      <c r="AR46">
+        <v>1.8</v>
+      </c>
+      <c r="AS46">
+        <v>2.12</v>
+      </c>
+      <c r="AT46">
+        <v>1.7</v>
+      </c>
+      <c r="AU46">
+        <v>2.04</v>
+      </c>
+      <c r="AV46">
+        <v>1.73</v>
+      </c>
+      <c r="AW46">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="AX46">
+        <v>-1</v>
+      </c>
+      <c r="AY46">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ46">
+        <v>1.78</v>
+      </c>
+      <c r="BA46"/>
+      <c r="BB46"/>
+      <c r="BC46">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BD46">
+        <v>1.83</v>
+      </c>
+      <c r="BE46">
+        <v>1.95</v>
+      </c>
+      <c r="BF46">
+        <v>1.76</v>
+      </c>
+      <c r="BG46"/>
+      <c r="BH46"/>
+    </row>
+    <row r="47" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C47" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D47" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" t="s">
+        <v>200</v>
+      </c>
+      <c r="F47"/>
+      <c r="G47">
+        <v>4.33</v>
+      </c>
+      <c r="H47">
+        <v>4</v>
+      </c>
+      <c r="I47">
+        <v>1.68</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
+      <c r="K47">
+        <v>4</v>
+      </c>
+      <c r="L47">
+        <v>1.7</v>
+      </c>
+      <c r="M47">
+        <v>4.3</v>
+      </c>
+      <c r="N47">
+        <v>3.9</v>
+      </c>
+      <c r="O47">
+        <v>1.67</v>
+      </c>
+      <c r="P47">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q47">
+        <v>3.9</v>
+      </c>
+      <c r="R47">
+        <v>1.67</v>
+      </c>
+      <c r="S47">
+        <v>3.8</v>
+      </c>
+      <c r="T47">
+        <v>3.75</v>
+      </c>
+      <c r="U47">
+        <v>1.75</v>
+      </c>
+      <c r="V47"/>
+      <c r="W47"/>
+      <c r="X47"/>
+      <c r="Y47">
+        <v>3.7</v>
+      </c>
+      <c r="Z47">
+        <v>3.7</v>
+      </c>
+      <c r="AA47">
+        <v>1.73</v>
+      </c>
+      <c r="AB47"/>
+      <c r="AC47"/>
+      <c r="AD47"/>
+      <c r="AE47">
+        <v>4.33</v>
+      </c>
+      <c r="AF47">
+        <v>4.2</v>
+      </c>
+      <c r="AG47">
+        <v>1.75</v>
+      </c>
+      <c r="AH47">
+        <v>4.01</v>
+      </c>
+      <c r="AI47">
+        <v>3.89</v>
+      </c>
+      <c r="AJ47">
+        <v>1.68</v>
+      </c>
+      <c r="AK47">
+        <v>4.3</v>
+      </c>
+      <c r="AL47">
+        <v>4.2</v>
+      </c>
+      <c r="AM47">
+        <v>1.76</v>
+      </c>
+      <c r="AN47">
+        <v>1.53</v>
+      </c>
+      <c r="AO47">
+        <v>2.4</v>
+      </c>
+      <c r="AP47"/>
+      <c r="AQ47"/>
+      <c r="AR47">
+        <v>1.57</v>
+      </c>
+      <c r="AS47">
+        <v>2.5</v>
+      </c>
+      <c r="AT47">
+        <v>1.53</v>
+      </c>
+      <c r="AU47">
+        <v>2.38</v>
+      </c>
+      <c r="AV47">
+        <v>1.56</v>
+      </c>
+      <c r="AW47">
+        <v>2.58</v>
+      </c>
+      <c r="AX47">
+        <v>0.75</v>
+      </c>
+      <c r="AY47">
+        <v>1.9</v>
+      </c>
+      <c r="AZ47">
+        <v>1.9</v>
+      </c>
+      <c r="BA47"/>
+      <c r="BB47"/>
+      <c r="BC47">
+        <v>1.9</v>
+      </c>
+      <c r="BD47">
+        <v>1.9</v>
+      </c>
+      <c r="BE47">
+        <v>1.84</v>
+      </c>
+      <c r="BF47">
+        <v>1.86</v>
+      </c>
+      <c r="BG47"/>
+      <c r="BH47"/>
+    </row>
+    <row r="48" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C48" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D48" t="s">
+        <v>182</v>
+      </c>
+      <c r="E48" t="s">
+        <v>189</v>
+      </c>
+      <c r="F48"/>
+      <c r="G48">
+        <v>5.25</v>
+      </c>
+      <c r="H48">
+        <v>3.9</v>
+      </c>
+      <c r="I48">
+        <v>1.57</v>
+      </c>
+      <c r="J48">
+        <v>5</v>
+      </c>
+      <c r="K48">
+        <v>3.75</v>
+      </c>
+      <c r="L48">
+        <v>1.6</v>
+      </c>
+      <c r="M48">
+        <v>5</v>
+      </c>
+      <c r="N48">
+        <v>3.65</v>
+      </c>
+      <c r="O48">
+        <v>1.64</v>
+      </c>
+      <c r="P48">
+        <v>5.25</v>
+      </c>
+      <c r="Q48">
+        <v>3.8</v>
+      </c>
+      <c r="R48">
+        <v>1.55</v>
+      </c>
+      <c r="S48">
+        <v>5</v>
+      </c>
+      <c r="T48">
+        <v>3.9</v>
+      </c>
+      <c r="U48">
+        <v>1.57</v>
+      </c>
+      <c r="V48"/>
+      <c r="W48"/>
+      <c r="X48"/>
+      <c r="Y48">
+        <v>4.8</v>
+      </c>
+      <c r="Z48">
+        <v>3.8</v>
+      </c>
+      <c r="AA48">
+        <v>1.55</v>
+      </c>
+      <c r="AB48"/>
+      <c r="AC48"/>
+      <c r="AD48"/>
+      <c r="AE48">
+        <v>5.5</v>
+      </c>
+      <c r="AF48">
+        <v>4</v>
+      </c>
+      <c r="AG48">
+        <v>1.64</v>
+      </c>
+      <c r="AH48">
+        <v>5.03</v>
+      </c>
+      <c r="AI48">
+        <v>3.78</v>
+      </c>
+      <c r="AJ48">
+        <v>1.57</v>
+      </c>
+      <c r="AK48">
+        <v>5.5</v>
+      </c>
+      <c r="AL48">
+        <v>4</v>
+      </c>
+      <c r="AM48">
+        <v>1.62</v>
+      </c>
+      <c r="AN48">
+        <v>1.83</v>
+      </c>
+      <c r="AO48">
+        <v>1.98</v>
+      </c>
+      <c r="AP48"/>
+      <c r="AQ48"/>
+      <c r="AR48">
+        <v>1.87</v>
+      </c>
+      <c r="AS48">
+        <v>2</v>
+      </c>
+      <c r="AT48">
+        <v>1.79</v>
+      </c>
+      <c r="AU48">
+        <v>1.93</v>
+      </c>
+      <c r="AV48">
+        <v>1.89</v>
+      </c>
+      <c r="AW48">
+        <v>1.96</v>
+      </c>
+      <c r="AX48">
+        <v>0.75</v>
+      </c>
+      <c r="AY48">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AZ48">
+        <v>1.78</v>
+      </c>
+      <c r="BA48"/>
+      <c r="BB48"/>
+      <c r="BC48">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="BD48">
+        <v>1.78</v>
+      </c>
+      <c r="BE48">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="BF48">
+        <v>1.71</v>
+      </c>
+      <c r="BG48"/>
+      <c r="BH48"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:DJ12">
-    <sortCondition ref="A2:A12"/>
-    <sortCondition ref="B2:B12"/>
-    <sortCondition ref="C2:C12"/>
-    <sortCondition ref="D2:D12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:DJ48">
+    <sortCondition ref="A2:A48"/>
+    <sortCondition ref="B2:B48"/>
+    <sortCondition ref="C2:C48"/>
+    <sortCondition ref="D2:D48"/>
   </sortState>
   <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/fixtures.xlsx
+++ b/fixtures.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee16c21b72f3fde9/Documents/Football Fortunes/All data/Data/Riku/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{0D4F0985-98F8-4C11-BB58-CB9BCCF568EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF71EAE0-A0D3-436C-85C0-B9CA74F8ECFC}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{0D4F0985-98F8-4C11-BB58-CB9BCCF568EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A034C566-D408-4DC8-9EB6-5C34010B4132}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="601">
   <si>
     <t>Div</t>
   </si>
@@ -1792,6 +1792,48 @@
   </si>
   <si>
     <t>Ascoli</t>
+  </si>
+  <si>
+    <t>Boreham Wood</t>
+  </si>
+  <si>
+    <t>Boston Utd</t>
+  </si>
+  <si>
+    <t>J O'Connor</t>
+  </si>
+  <si>
+    <t>D Watson</t>
+  </si>
+  <si>
+    <t>A Merchant</t>
+  </si>
+  <si>
+    <t>R Aspinall</t>
+  </si>
+  <si>
+    <t>J Oldham</t>
+  </si>
+  <si>
+    <t>P Marsden</t>
+  </si>
+  <si>
+    <t>S Morland</t>
+  </si>
+  <si>
+    <t>C Walchester</t>
+  </si>
+  <si>
+    <t>L Smith</t>
+  </si>
+  <si>
+    <t>B Atkinson</t>
+  </si>
+  <si>
+    <t>M Scholes</t>
+  </si>
+  <si>
+    <t>A Miller</t>
   </si>
 </sst>
 </file>
@@ -3319,7 +3361,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64032AAF-94ED-49C7-B015-7ECD08F95F34}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:CP198"/>
+  <dimension ref="A1:CP210"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.1796875" style="4" bestFit="1" customWidth="1"/>
@@ -33185,6 +33227,1826 @@
       <c r="AW198"/>
       <c r="AX198"/>
     </row>
+    <row r="199" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A199" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B199" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C199" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D199" t="s">
+        <v>588</v>
+      </c>
+      <c r="E199" t="s">
+        <v>557</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="G199">
+        <v>1.95</v>
+      </c>
+      <c r="H199">
+        <v>3.5</v>
+      </c>
+      <c r="I199">
+        <v>3.4</v>
+      </c>
+      <c r="J199">
+        <v>2</v>
+      </c>
+      <c r="K199">
+        <v>3.4</v>
+      </c>
+      <c r="L199">
+        <v>3.4</v>
+      </c>
+      <c r="M199">
+        <v>1.95</v>
+      </c>
+      <c r="N199">
+        <v>3.4</v>
+      </c>
+      <c r="O199">
+        <v>3.5</v>
+      </c>
+      <c r="P199">
+        <v>1.95</v>
+      </c>
+      <c r="Q199">
+        <v>3.25</v>
+      </c>
+      <c r="R199">
+        <v>3.3</v>
+      </c>
+      <c r="S199">
+        <v>1.95</v>
+      </c>
+      <c r="T199">
+        <v>3.4</v>
+      </c>
+      <c r="U199">
+        <v>3.3</v>
+      </c>
+      <c r="V199">
+        <v>1.95</v>
+      </c>
+      <c r="W199">
+        <v>3.4</v>
+      </c>
+      <c r="X199">
+        <v>3.1</v>
+      </c>
+      <c r="Y199">
+        <v>2.08</v>
+      </c>
+      <c r="Z199">
+        <v>3.55</v>
+      </c>
+      <c r="AA199">
+        <v>3.9</v>
+      </c>
+      <c r="AB199">
+        <v>1.97</v>
+      </c>
+      <c r="AC199">
+        <v>3.39</v>
+      </c>
+      <c r="AD199">
+        <v>3.46</v>
+      </c>
+      <c r="AE199">
+        <v>2.08</v>
+      </c>
+      <c r="AF199">
+        <v>3.35</v>
+      </c>
+      <c r="AG199">
+        <v>3.65</v>
+      </c>
+      <c r="AH199">
+        <v>1.9</v>
+      </c>
+      <c r="AI199">
+        <v>1.9</v>
+      </c>
+      <c r="AJ199">
+        <v>1.98</v>
+      </c>
+      <c r="AK199">
+        <v>1.9</v>
+      </c>
+      <c r="AL199">
+        <v>1.86</v>
+      </c>
+      <c r="AM199">
+        <v>1.85</v>
+      </c>
+      <c r="AN199">
+        <v>1.97</v>
+      </c>
+      <c r="AO199">
+        <v>1.87</v>
+      </c>
+      <c r="AP199">
+        <v>-0.5</v>
+      </c>
+      <c r="AQ199">
+        <v>1.98</v>
+      </c>
+      <c r="AR199">
+        <v>1.83</v>
+      </c>
+      <c r="AS199">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="AT199">
+        <v>1.83</v>
+      </c>
+      <c r="AU199">
+        <v>1.98</v>
+      </c>
+      <c r="AV199">
+        <v>1.77</v>
+      </c>
+      <c r="AW199">
+        <v>2.08</v>
+      </c>
+      <c r="AX199">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="200" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A200" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B200" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C200" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D200" t="s">
+        <v>303</v>
+      </c>
+      <c r="E200" t="s">
+        <v>300</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="G200">
+        <v>1.67</v>
+      </c>
+      <c r="H200">
+        <v>3.8</v>
+      </c>
+      <c r="I200">
+        <v>4.2</v>
+      </c>
+      <c r="J200">
+        <v>1.73</v>
+      </c>
+      <c r="K200">
+        <v>3.75</v>
+      </c>
+      <c r="L200">
+        <v>4</v>
+      </c>
+      <c r="M200">
+        <v>1.7</v>
+      </c>
+      <c r="N200">
+        <v>3.8</v>
+      </c>
+      <c r="O200">
+        <v>4.2</v>
+      </c>
+      <c r="P200">
+        <v>1.68</v>
+      </c>
+      <c r="Q200">
+        <v>3.75</v>
+      </c>
+      <c r="R200">
+        <v>3.9</v>
+      </c>
+      <c r="S200">
+        <v>1.67</v>
+      </c>
+      <c r="T200">
+        <v>3.8</v>
+      </c>
+      <c r="U200">
+        <v>4</v>
+      </c>
+      <c r="V200">
+        <v>1.67</v>
+      </c>
+      <c r="W200">
+        <v>3.75</v>
+      </c>
+      <c r="X200">
+        <v>3.9</v>
+      </c>
+      <c r="Y200">
+        <v>1.74</v>
+      </c>
+      <c r="Z200">
+        <v>3.94</v>
+      </c>
+      <c r="AA200">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="AB200">
+        <v>1.7</v>
+      </c>
+      <c r="AC200">
+        <v>3.79</v>
+      </c>
+      <c r="AD200">
+        <v>4.16</v>
+      </c>
+      <c r="AE200">
+        <v>1.75</v>
+      </c>
+      <c r="AF200">
+        <v>3.65</v>
+      </c>
+      <c r="AG200">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AH200">
+        <v>1.62</v>
+      </c>
+      <c r="AI200">
+        <v>2.25</v>
+      </c>
+      <c r="AJ200">
+        <v>1.67</v>
+      </c>
+      <c r="AK200">
+        <v>2.25</v>
+      </c>
+      <c r="AL200">
+        <v>1.61</v>
+      </c>
+      <c r="AM200">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AN200">
+        <v>1.66</v>
+      </c>
+      <c r="AO200">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AP200">
+        <v>-0.75</v>
+      </c>
+      <c r="AQ200">
+        <v>1.9</v>
+      </c>
+      <c r="AR200">
+        <v>1.9</v>
+      </c>
+      <c r="AS200">
+        <v>1.95</v>
+      </c>
+      <c r="AT200">
+        <v>1.9</v>
+      </c>
+      <c r="AU200">
+        <v>1.9</v>
+      </c>
+      <c r="AV200">
+        <v>1.86</v>
+      </c>
+      <c r="AW200">
+        <v>1.96</v>
+      </c>
+      <c r="AX200">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="201" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A201" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B201" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C201" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D201" t="s">
+        <v>293</v>
+      </c>
+      <c r="E201" t="s">
+        <v>291</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="G201">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H201">
+        <v>3.5</v>
+      </c>
+      <c r="I201">
+        <v>2.8</v>
+      </c>
+      <c r="J201">
+        <v>2.25</v>
+      </c>
+      <c r="K201">
+        <v>3.6</v>
+      </c>
+      <c r="L201">
+        <v>2.75</v>
+      </c>
+      <c r="M201">
+        <v>2.25</v>
+      </c>
+      <c r="N201">
+        <v>3.5</v>
+      </c>
+      <c r="O201">
+        <v>2.75</v>
+      </c>
+      <c r="P201">
+        <v>2.15</v>
+      </c>
+      <c r="Q201">
+        <v>3.4</v>
+      </c>
+      <c r="R201">
+        <v>2.7</v>
+      </c>
+      <c r="S201">
+        <v>2.25</v>
+      </c>
+      <c r="T201">
+        <v>3.3</v>
+      </c>
+      <c r="U201">
+        <v>2.75</v>
+      </c>
+      <c r="V201">
+        <v>2.25</v>
+      </c>
+      <c r="W201">
+        <v>3.25</v>
+      </c>
+      <c r="X201">
+        <v>2.7</v>
+      </c>
+      <c r="Y201">
+        <v>2.34</v>
+      </c>
+      <c r="Z201">
+        <v>3.8</v>
+      </c>
+      <c r="AA201">
+        <v>3</v>
+      </c>
+      <c r="AB201">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AC201">
+        <v>3.53</v>
+      </c>
+      <c r="AD201">
+        <v>2.76</v>
+      </c>
+      <c r="AE201">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="AF201">
+        <v>3.7</v>
+      </c>
+      <c r="AG201">
+        <v>2.82</v>
+      </c>
+      <c r="AH201">
+        <v>1.62</v>
+      </c>
+      <c r="AI201">
+        <v>2.25</v>
+      </c>
+      <c r="AJ201">
+        <v>1.72</v>
+      </c>
+      <c r="AK201">
+        <v>2.25</v>
+      </c>
+      <c r="AL201">
+        <v>1.64</v>
+      </c>
+      <c r="AM201">
+        <v>2.16</v>
+      </c>
+      <c r="AN201">
+        <v>1.68</v>
+      </c>
+      <c r="AO201">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AP201">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ201">
+        <v>1.98</v>
+      </c>
+      <c r="AR201">
+        <v>1.83</v>
+      </c>
+      <c r="AS201">
+        <v>2.04</v>
+      </c>
+      <c r="AT201">
+        <v>1.83</v>
+      </c>
+      <c r="AU201">
+        <v>1.97</v>
+      </c>
+      <c r="AV201">
+        <v>1.79</v>
+      </c>
+      <c r="AW201">
+        <v>2.04</v>
+      </c>
+      <c r="AX201">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A202" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B202" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C202" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D202" t="s">
+        <v>298</v>
+      </c>
+      <c r="E202" t="s">
+        <v>290</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="G202">
+        <v>1.53</v>
+      </c>
+      <c r="H202">
+        <v>4.33</v>
+      </c>
+      <c r="I202">
+        <v>4.75</v>
+      </c>
+      <c r="J202">
+        <v>1.57</v>
+      </c>
+      <c r="K202">
+        <v>4.2</v>
+      </c>
+      <c r="L202">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="M202">
+        <v>1.55</v>
+      </c>
+      <c r="N202">
+        <v>4.2</v>
+      </c>
+      <c r="O202">
+        <v>4.8</v>
+      </c>
+      <c r="P202">
+        <v>1.55</v>
+      </c>
+      <c r="Q202">
+        <v>4</v>
+      </c>
+      <c r="R202">
+        <v>4.5</v>
+      </c>
+      <c r="S202">
+        <v>1.53</v>
+      </c>
+      <c r="T202">
+        <v>4.2</v>
+      </c>
+      <c r="U202">
+        <v>4.75</v>
+      </c>
+      <c r="V202">
+        <v>1.53</v>
+      </c>
+      <c r="W202">
+        <v>4</v>
+      </c>
+      <c r="X202">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Y202">
+        <v>1.6</v>
+      </c>
+      <c r="Z202">
+        <v>4.47</v>
+      </c>
+      <c r="AA202">
+        <v>5.75</v>
+      </c>
+      <c r="AB202">
+        <v>1.55</v>
+      </c>
+      <c r="AC202">
+        <v>4.25</v>
+      </c>
+      <c r="AD202">
+        <v>4.78</v>
+      </c>
+      <c r="AE202">
+        <v>1.57</v>
+      </c>
+      <c r="AF202">
+        <v>4</v>
+      </c>
+      <c r="AG202">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AH202">
+        <v>1.44</v>
+      </c>
+      <c r="AI202">
+        <v>2.7</v>
+      </c>
+      <c r="AJ202">
+        <v>1.5</v>
+      </c>
+      <c r="AK202">
+        <v>2.7</v>
+      </c>
+      <c r="AL202">
+        <v>1.47</v>
+      </c>
+      <c r="AM202">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="AN202">
+        <v>1.37</v>
+      </c>
+      <c r="AO202">
+        <v>2.68</v>
+      </c>
+      <c r="AP202">
+        <v>-1</v>
+      </c>
+      <c r="AQ202">
+        <v>1.93</v>
+      </c>
+      <c r="AR202">
+        <v>1.88</v>
+      </c>
+      <c r="AS202">
+        <v>1.96</v>
+      </c>
+      <c r="AT202">
+        <v>1.9</v>
+      </c>
+      <c r="AU202">
+        <v>1.92</v>
+      </c>
+      <c r="AV202">
+        <v>1.84</v>
+      </c>
+      <c r="AW202">
+        <v>1.94</v>
+      </c>
+      <c r="AX202">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="203" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B203" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C203" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D203" t="s">
+        <v>185</v>
+      </c>
+      <c r="E203" t="s">
+        <v>295</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G203">
+        <v>1.55</v>
+      </c>
+      <c r="H203">
+        <v>4.2</v>
+      </c>
+      <c r="I203">
+        <v>4.75</v>
+      </c>
+      <c r="J203">
+        <v>1.57</v>
+      </c>
+      <c r="K203">
+        <v>4.2</v>
+      </c>
+      <c r="L203">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="M203">
+        <v>1.55</v>
+      </c>
+      <c r="N203">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O203">
+        <v>4.8</v>
+      </c>
+      <c r="P203">
+        <v>1.55</v>
+      </c>
+      <c r="Q203">
+        <v>4</v>
+      </c>
+      <c r="R203">
+        <v>4.5</v>
+      </c>
+      <c r="S203">
+        <v>1.53</v>
+      </c>
+      <c r="T203">
+        <v>4.2</v>
+      </c>
+      <c r="U203">
+        <v>4.75</v>
+      </c>
+      <c r="V203">
+        <v>1.53</v>
+      </c>
+      <c r="W203">
+        <v>4</v>
+      </c>
+      <c r="X203">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Y203">
+        <v>1.63</v>
+      </c>
+      <c r="Z203">
+        <v>4.28</v>
+      </c>
+      <c r="AA203">
+        <v>4.87</v>
+      </c>
+      <c r="AB203">
+        <v>1.57</v>
+      </c>
+      <c r="AC203">
+        <v>4.12</v>
+      </c>
+      <c r="AD203">
+        <v>4.71</v>
+      </c>
+      <c r="AE203">
+        <v>1.59</v>
+      </c>
+      <c r="AF203">
+        <v>3.95</v>
+      </c>
+      <c r="AG203">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AH203">
+        <v>1.5</v>
+      </c>
+      <c r="AI203">
+        <v>2.5</v>
+      </c>
+      <c r="AJ203">
+        <v>1.54</v>
+      </c>
+      <c r="AK203">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AL203">
+        <v>1.48</v>
+      </c>
+      <c r="AM203">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="AN203">
+        <v>1.44</v>
+      </c>
+      <c r="AO203">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AP203">
+        <v>-1</v>
+      </c>
+      <c r="AQ203">
+        <v>1.95</v>
+      </c>
+      <c r="AR203">
+        <v>1.85</v>
+      </c>
+      <c r="AS203">
+        <v>2.02</v>
+      </c>
+      <c r="AT203">
+        <v>1.85</v>
+      </c>
+      <c r="AU203">
+        <v>1.95</v>
+      </c>
+      <c r="AV203">
+        <v>1.8</v>
+      </c>
+      <c r="AW203">
+        <v>1.9</v>
+      </c>
+      <c r="AX203">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="204" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A204" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B204" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C204" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D204" t="s">
+        <v>558</v>
+      </c>
+      <c r="E204" t="s">
+        <v>189</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="G204">
+        <v>2.38</v>
+      </c>
+      <c r="H204">
+        <v>3.4</v>
+      </c>
+      <c r="I204">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="J204">
+        <v>2.4</v>
+      </c>
+      <c r="K204">
+        <v>3.4</v>
+      </c>
+      <c r="L204">
+        <v>2.6</v>
+      </c>
+      <c r="M204">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="N204">
+        <v>3.3</v>
+      </c>
+      <c r="O204">
+        <v>2.6</v>
+      </c>
+      <c r="P204">
+        <v>2.4</v>
+      </c>
+      <c r="Q204">
+        <v>3.2</v>
+      </c>
+      <c r="R204">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="S204">
+        <v>2.4</v>
+      </c>
+      <c r="T204">
+        <v>3.3</v>
+      </c>
+      <c r="U204">
+        <v>2.5</v>
+      </c>
+      <c r="V204">
+        <v>2.4</v>
+      </c>
+      <c r="W204">
+        <v>3.25</v>
+      </c>
+      <c r="X204">
+        <v>2.5</v>
+      </c>
+      <c r="Y204">
+        <v>2.5</v>
+      </c>
+      <c r="Z204">
+        <v>3.4</v>
+      </c>
+      <c r="AA204">
+        <v>2.83</v>
+      </c>
+      <c r="AB204">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="AC204">
+        <v>3.3</v>
+      </c>
+      <c r="AD204">
+        <v>2.62</v>
+      </c>
+      <c r="AE204">
+        <v>2.48</v>
+      </c>
+      <c r="AF204">
+        <v>3.5</v>
+      </c>
+      <c r="AG204">
+        <v>2.82</v>
+      </c>
+      <c r="AH204">
+        <v>1.85</v>
+      </c>
+      <c r="AI204">
+        <v>1.95</v>
+      </c>
+      <c r="AJ204">
+        <v>1.92</v>
+      </c>
+      <c r="AK204">
+        <v>2</v>
+      </c>
+      <c r="AL204">
+        <v>1.82</v>
+      </c>
+      <c r="AM204">
+        <v>1.91</v>
+      </c>
+      <c r="AN204">
+        <v>1.44</v>
+      </c>
+      <c r="AO204">
+        <v>1.96</v>
+      </c>
+      <c r="AP204">
+        <v>0</v>
+      </c>
+      <c r="AQ204">
+        <v>1.8</v>
+      </c>
+      <c r="AR204">
+        <v>2</v>
+      </c>
+      <c r="AS204">
+        <v>1.81</v>
+      </c>
+      <c r="AT204">
+        <v>2.04</v>
+      </c>
+      <c r="AU204">
+        <v>1.79</v>
+      </c>
+      <c r="AV204">
+        <v>1.96</v>
+      </c>
+      <c r="AW204">
+        <v>1.8</v>
+      </c>
+      <c r="AX204">
+        <v>2.0699999999999998</v>
+      </c>
+    </row>
+    <row r="205" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A205" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B205" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C205" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D205" t="s">
+        <v>297</v>
+      </c>
+      <c r="E205" t="s">
+        <v>555</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="G205">
+        <v>2.4</v>
+      </c>
+      <c r="H205">
+        <v>3.6</v>
+      </c>
+      <c r="I205">
+        <v>2.5</v>
+      </c>
+      <c r="J205">
+        <v>2.4</v>
+      </c>
+      <c r="K205">
+        <v>3.75</v>
+      </c>
+      <c r="L205">
+        <v>2.5</v>
+      </c>
+      <c r="M205">
+        <v>2.4</v>
+      </c>
+      <c r="N205">
+        <v>3.6</v>
+      </c>
+      <c r="O205">
+        <v>2.5</v>
+      </c>
+      <c r="P205">
+        <v>2.35</v>
+      </c>
+      <c r="Q205">
+        <v>3.4</v>
+      </c>
+      <c r="R205">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="S205">
+        <v>2.4</v>
+      </c>
+      <c r="T205">
+        <v>3.6</v>
+      </c>
+      <c r="U205">
+        <v>2.4</v>
+      </c>
+      <c r="V205">
+        <v>2.38</v>
+      </c>
+      <c r="W205">
+        <v>3.5</v>
+      </c>
+      <c r="X205">
+        <v>2.38</v>
+      </c>
+      <c r="Y205">
+        <v>2.59</v>
+      </c>
+      <c r="Z205">
+        <v>3.81</v>
+      </c>
+      <c r="AA205">
+        <v>2.6</v>
+      </c>
+      <c r="AB205">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="AC205">
+        <v>3.62</v>
+      </c>
+      <c r="AD205">
+        <v>2.48</v>
+      </c>
+      <c r="AE205">
+        <v>2.62</v>
+      </c>
+      <c r="AF205">
+        <v>3.85</v>
+      </c>
+      <c r="AG205">
+        <v>2.5</v>
+      </c>
+      <c r="AH205">
+        <v>1.53</v>
+      </c>
+      <c r="AI205">
+        <v>2.4</v>
+      </c>
+      <c r="AJ205">
+        <v>1.6</v>
+      </c>
+      <c r="AK205">
+        <v>2.44</v>
+      </c>
+      <c r="AL205">
+        <v>1.53</v>
+      </c>
+      <c r="AM205">
+        <v>2.36</v>
+      </c>
+      <c r="AN205">
+        <v>1.58</v>
+      </c>
+      <c r="AO205">
+        <v>2.48</v>
+      </c>
+      <c r="AP205">
+        <v>0</v>
+      </c>
+      <c r="AQ205">
+        <v>1.85</v>
+      </c>
+      <c r="AR205">
+        <v>1.95</v>
+      </c>
+      <c r="AS205">
+        <v>1.93</v>
+      </c>
+      <c r="AT205">
+        <v>1.95</v>
+      </c>
+      <c r="AU205">
+        <v>1.85</v>
+      </c>
+      <c r="AV205">
+        <v>1.9</v>
+      </c>
+      <c r="AW205">
+        <v>1.97</v>
+      </c>
+      <c r="AX205">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="206" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A206" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B206" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C206" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D206" t="s">
+        <v>307</v>
+      </c>
+      <c r="E206" t="s">
+        <v>301</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="G206">
+        <v>1.85</v>
+      </c>
+      <c r="H206">
+        <v>3.6</v>
+      </c>
+      <c r="I206">
+        <v>3.6</v>
+      </c>
+      <c r="J206">
+        <v>1.9</v>
+      </c>
+      <c r="K206">
+        <v>3.6</v>
+      </c>
+      <c r="L206">
+        <v>3.5</v>
+      </c>
+      <c r="M206">
+        <v>1.87</v>
+      </c>
+      <c r="N206">
+        <v>3.5</v>
+      </c>
+      <c r="O206">
+        <v>3.6</v>
+      </c>
+      <c r="P206">
+        <v>1.87</v>
+      </c>
+      <c r="Q206">
+        <v>3.4</v>
+      </c>
+      <c r="R206">
+        <v>3.4</v>
+      </c>
+      <c r="S206">
+        <v>1.85</v>
+      </c>
+      <c r="T206">
+        <v>3.6</v>
+      </c>
+      <c r="U206">
+        <v>3.6</v>
+      </c>
+      <c r="V206">
+        <v>1.83</v>
+      </c>
+      <c r="W206">
+        <v>3.5</v>
+      </c>
+      <c r="X206">
+        <v>3.5</v>
+      </c>
+      <c r="Y206">
+        <v>1.97</v>
+      </c>
+      <c r="Z206">
+        <v>3.83</v>
+      </c>
+      <c r="AA206">
+        <v>3.66</v>
+      </c>
+      <c r="AB206">
+        <v>1.89</v>
+      </c>
+      <c r="AC206">
+        <v>3.61</v>
+      </c>
+      <c r="AD206">
+        <v>3.53</v>
+      </c>
+      <c r="AE206">
+        <v>1.96</v>
+      </c>
+      <c r="AF206">
+        <v>3.85</v>
+      </c>
+      <c r="AG206">
+        <v>3.85</v>
+      </c>
+      <c r="AH206">
+        <v>1.73</v>
+      </c>
+      <c r="AI206">
+        <v>2.08</v>
+      </c>
+      <c r="AJ206">
+        <v>1.78</v>
+      </c>
+      <c r="AK206">
+        <v>2.1</v>
+      </c>
+      <c r="AL206">
+        <v>1.7</v>
+      </c>
+      <c r="AM206">
+        <v>2.06</v>
+      </c>
+      <c r="AN206">
+        <v>1.79</v>
+      </c>
+      <c r="AO206">
+        <v>2.08</v>
+      </c>
+      <c r="AP206">
+        <v>-0.5</v>
+      </c>
+      <c r="AQ206">
+        <v>1.9</v>
+      </c>
+      <c r="AR206">
+        <v>1.9</v>
+      </c>
+      <c r="AS206">
+        <v>1.96</v>
+      </c>
+      <c r="AT206">
+        <v>1.9</v>
+      </c>
+      <c r="AU206">
+        <v>1.87</v>
+      </c>
+      <c r="AV206">
+        <v>1.86</v>
+      </c>
+      <c r="AW206">
+        <v>1.97</v>
+      </c>
+      <c r="AX206">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="207" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A207" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B207" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C207" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D207" t="s">
+        <v>302</v>
+      </c>
+      <c r="E207" t="s">
+        <v>296</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="G207">
+        <v>3.4</v>
+      </c>
+      <c r="H207">
+        <v>3.5</v>
+      </c>
+      <c r="I207">
+        <v>1.95</v>
+      </c>
+      <c r="J207">
+        <v>3.2</v>
+      </c>
+      <c r="K207">
+        <v>3.5</v>
+      </c>
+      <c r="L207">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="M207">
+        <v>3.2</v>
+      </c>
+      <c r="N207">
+        <v>3.4</v>
+      </c>
+      <c r="O207">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P207">
+        <v>3.1</v>
+      </c>
+      <c r="Q207">
+        <v>3.3</v>
+      </c>
+      <c r="R207">
+        <v>2</v>
+      </c>
+      <c r="S207">
+        <v>3.1</v>
+      </c>
+      <c r="T207">
+        <v>3.5</v>
+      </c>
+      <c r="U207">
+        <v>2</v>
+      </c>
+      <c r="V207">
+        <v>3.1</v>
+      </c>
+      <c r="W207">
+        <v>3.4</v>
+      </c>
+      <c r="X207">
+        <v>2</v>
+      </c>
+      <c r="Y207">
+        <v>3.65</v>
+      </c>
+      <c r="Z207">
+        <v>3.55</v>
+      </c>
+      <c r="AA207">
+        <v>2.17</v>
+      </c>
+      <c r="AB207">
+        <v>3.25</v>
+      </c>
+      <c r="AC207">
+        <v>3.45</v>
+      </c>
+      <c r="AD207">
+        <v>2.04</v>
+      </c>
+      <c r="AE207">
+        <v>3.4</v>
+      </c>
+      <c r="AF207">
+        <v>3.55</v>
+      </c>
+      <c r="AG207">
+        <v>2.14</v>
+      </c>
+      <c r="AH207">
+        <v>1.8</v>
+      </c>
+      <c r="AI207">
+        <v>2</v>
+      </c>
+      <c r="AJ207">
+        <v>1.84</v>
+      </c>
+      <c r="AK207">
+        <v>2.14</v>
+      </c>
+      <c r="AL207">
+        <v>1.77</v>
+      </c>
+      <c r="AM207">
+        <v>1.97</v>
+      </c>
+      <c r="AN207">
+        <v>1.83</v>
+      </c>
+      <c r="AO207">
+        <v>1.98</v>
+      </c>
+      <c r="AP207">
+        <v>0.25</v>
+      </c>
+      <c r="AQ207">
+        <v>2</v>
+      </c>
+      <c r="AR207">
+        <v>1.8</v>
+      </c>
+      <c r="AS207">
+        <v>2</v>
+      </c>
+      <c r="AT207">
+        <v>1.87</v>
+      </c>
+      <c r="AU207">
+        <v>1.95</v>
+      </c>
+      <c r="AV207">
+        <v>1.81</v>
+      </c>
+      <c r="AW207">
+        <v>2.09</v>
+      </c>
+      <c r="AX207">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="208" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A208" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B208" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C208" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D208" t="s">
+        <v>556</v>
+      </c>
+      <c r="E208" t="s">
+        <v>587</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="G208">
+        <v>4.2</v>
+      </c>
+      <c r="H208">
+        <v>4.2</v>
+      </c>
+      <c r="I208">
+        <v>1.62</v>
+      </c>
+      <c r="J208">
+        <v>4.33</v>
+      </c>
+      <c r="K208">
+        <v>4.2</v>
+      </c>
+      <c r="L208">
+        <v>1.62</v>
+      </c>
+      <c r="M208">
+        <v>4.33</v>
+      </c>
+      <c r="N208">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O208">
+        <v>1.62</v>
+      </c>
+      <c r="P208">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q208">
+        <v>3.9</v>
+      </c>
+      <c r="R208">
+        <v>1.62</v>
+      </c>
+      <c r="S208">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="T208">
+        <v>4</v>
+      </c>
+      <c r="U208">
+        <v>1.6</v>
+      </c>
+      <c r="V208">
+        <v>4.2</v>
+      </c>
+      <c r="W208">
+        <v>3.9</v>
+      </c>
+      <c r="X208">
+        <v>1.6</v>
+      </c>
+      <c r="Y208">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Z208">
+        <v>4.42</v>
+      </c>
+      <c r="AA208">
+        <v>1.69</v>
+      </c>
+      <c r="AB208">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="AC208">
+        <v>4.13</v>
+      </c>
+      <c r="AD208">
+        <v>1.63</v>
+      </c>
+      <c r="AE208">
+        <v>4.5</v>
+      </c>
+      <c r="AF208">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AG208">
+        <v>1.67</v>
+      </c>
+      <c r="AH208">
+        <v>1.48</v>
+      </c>
+      <c r="AI208">
+        <v>2.6</v>
+      </c>
+      <c r="AJ208">
+        <v>1.52</v>
+      </c>
+      <c r="AK208">
+        <v>2.63</v>
+      </c>
+      <c r="AL208">
+        <v>1.47</v>
+      </c>
+      <c r="AM208">
+        <v>2.52</v>
+      </c>
+      <c r="AN208">
+        <v>1.49</v>
+      </c>
+      <c r="AO208">
+        <v>2.66</v>
+      </c>
+      <c r="AP208">
+        <v>0.75</v>
+      </c>
+      <c r="AQ208">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AR208">
+        <v>1.78</v>
+      </c>
+      <c r="AS208">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AT208">
+        <v>1.85</v>
+      </c>
+      <c r="AU208">
+        <v>1.95</v>
+      </c>
+      <c r="AV208">
+        <v>1.79</v>
+      </c>
+      <c r="AW208">
+        <v>2.02</v>
+      </c>
+      <c r="AX208">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="209" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A209" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B209" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C209" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="D209" t="s">
+        <v>304</v>
+      </c>
+      <c r="E209" t="s">
+        <v>299</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="G209">
+        <v>2.1</v>
+      </c>
+      <c r="H209">
+        <v>3.5</v>
+      </c>
+      <c r="I209">
+        <v>3</v>
+      </c>
+      <c r="J209">
+        <v>2.15</v>
+      </c>
+      <c r="K209">
+        <v>3.6</v>
+      </c>
+      <c r="L209">
+        <v>2.88</v>
+      </c>
+      <c r="M209">
+        <v>2.1</v>
+      </c>
+      <c r="N209">
+        <v>3.5</v>
+      </c>
+      <c r="O209">
+        <v>3</v>
+      </c>
+      <c r="P209">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="Q209">
+        <v>3.4</v>
+      </c>
+      <c r="R209">
+        <v>2.87</v>
+      </c>
+      <c r="S209">
+        <v>2.1</v>
+      </c>
+      <c r="T209">
+        <v>3.5</v>
+      </c>
+      <c r="U209">
+        <v>2.9</v>
+      </c>
+      <c r="V209">
+        <v>2.1</v>
+      </c>
+      <c r="W209">
+        <v>3.4</v>
+      </c>
+      <c r="X209">
+        <v>2.88</v>
+      </c>
+      <c r="Y209">
+        <v>2.23</v>
+      </c>
+      <c r="Z209">
+        <v>3.75</v>
+      </c>
+      <c r="AA209">
+        <v>3.13</v>
+      </c>
+      <c r="AB209">
+        <v>2.13</v>
+      </c>
+      <c r="AC209">
+        <v>3.55</v>
+      </c>
+      <c r="AD209">
+        <v>2.97</v>
+      </c>
+      <c r="AE209">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AF209">
+        <v>3.75</v>
+      </c>
+      <c r="AG209">
+        <v>3.2</v>
+      </c>
+      <c r="AH209">
+        <v>1.65</v>
+      </c>
+      <c r="AI209">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AJ209">
+        <v>1.68</v>
+      </c>
+      <c r="AK209">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AL209">
+        <v>1.65</v>
+      </c>
+      <c r="AM209">
+        <v>2.14</v>
+      </c>
+      <c r="AN209">
+        <v>1.68</v>
+      </c>
+      <c r="AO209">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AP209">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ209">
+        <v>1.85</v>
+      </c>
+      <c r="AR209">
+        <v>1.95</v>
+      </c>
+      <c r="AS209">
+        <v>1.9</v>
+      </c>
+      <c r="AT209">
+        <v>1.96</v>
+      </c>
+      <c r="AU209">
+        <v>1.85</v>
+      </c>
+      <c r="AV209">
+        <v>1.91</v>
+      </c>
+      <c r="AW209">
+        <v>1.91</v>
+      </c>
+      <c r="AX209">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="210" spans="1:50" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A210" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B210" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C210" s="3">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D210" t="s">
+        <v>294</v>
+      </c>
+      <c r="E210" t="s">
+        <v>305</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="G210">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="H210">
+        <v>3.4</v>
+      </c>
+      <c r="I210">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="J210">
+        <v>2.5</v>
+      </c>
+      <c r="K210">
+        <v>3.4</v>
+      </c>
+      <c r="L210">
+        <v>2.5</v>
+      </c>
+      <c r="M210">
+        <v>2.5</v>
+      </c>
+      <c r="N210">
+        <v>3.3</v>
+      </c>
+      <c r="O210">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="P210">
+        <v>2.5</v>
+      </c>
+      <c r="Q210">
+        <v>3.25</v>
+      </c>
+      <c r="R210">
+        <v>2.5</v>
+      </c>
+      <c r="S210">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="T210">
+        <v>3.4</v>
+      </c>
+      <c r="U210">
+        <v>2.5</v>
+      </c>
+      <c r="V210">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="W210">
+        <v>3.3</v>
+      </c>
+      <c r="X210">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Y210">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="Z210">
+        <v>3.52</v>
+      </c>
+      <c r="AA210">
+        <v>2.88</v>
+      </c>
+      <c r="AB210">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="AC210">
+        <v>3.4</v>
+      </c>
+      <c r="AD210">
+        <v>2.56</v>
+      </c>
+      <c r="AE210">
+        <v>2.56</v>
+      </c>
+      <c r="AF210">
+        <v>3.4</v>
+      </c>
+      <c r="AG210">
+        <v>2.6</v>
+      </c>
+      <c r="AH210">
+        <v>1.85</v>
+      </c>
+      <c r="AI210">
+        <v>1.95</v>
+      </c>
+      <c r="AJ210">
+        <v>1.85</v>
+      </c>
+      <c r="AK210">
+        <v>1.97</v>
+      </c>
+      <c r="AL210">
+        <v>1.8</v>
+      </c>
+      <c r="AM210">
+        <v>1.93</v>
+      </c>
+      <c r="AN210">
+        <v>1.82</v>
+      </c>
+      <c r="AO210">
+        <v>1.96</v>
+      </c>
+      <c r="AP210">
+        <v>0</v>
+      </c>
+      <c r="AQ210">
+        <v>1.85</v>
+      </c>
+      <c r="AR210">
+        <v>1.95</v>
+      </c>
+      <c r="AS210">
+        <v>1.9</v>
+      </c>
+      <c r="AT210">
+        <v>1.95</v>
+      </c>
+      <c r="AU210">
+        <v>1.86</v>
+      </c>
+      <c r="AV210">
+        <v>1.92</v>
+      </c>
+      <c r="AW210"/>
+      <c r="AX210"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CP198">
     <sortCondition ref="A2:A198"/>
